--- a/tables/before_table.xlsx
+++ b/tables/before_table.xlsx
@@ -34,14 +34,14 @@
       <sz val="10"/>
     </font>
     <font>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -55,12 +55,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
+        <fgColor rgb="00D5E8D4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EBF5FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -90,19 +95,25 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -470,10 +481,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -892,137 +903,7306 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Continuous variables</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>623</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>5285157</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>289</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>793857</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>505</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>1207020</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>566907</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>1427</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>3488225</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>701755</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>254</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>765610</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>518</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>1397488</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>12928318</v>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>albumin_bld</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>17974</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>3583</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>32360</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>61223</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>3796</v>
+        <v>24</v>
       </c>
       <c r="U6" s="5" t="n">
-        <v>27134337</v>
+        <v>115140</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
+          <t>albumin_creatinine</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>5927</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>23162</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" s="7" t="n">
+        <v>4810</v>
+      </c>
+      <c r="P7" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="7" t="n">
+        <v>45400</v>
+      </c>
+      <c r="R7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="U7" s="5" t="n">
+        <v>79299</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>albumin_urine</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>19036</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>5930</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>96443</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>23161</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>15128</v>
+      </c>
+      <c r="P8" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q8" s="7" t="n">
+        <v>48594</v>
+      </c>
+      <c r="R8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="U8" s="5" t="n">
+        <v>208292</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>48863</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" s="5" t="n">
+        <v>48863</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>alcohol_servings</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>70762</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>77508</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>13255</v>
+      </c>
+      <c r="P10" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q10" s="7" t="n">
+        <v>77728</v>
+      </c>
+      <c r="R10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" s="7" t="n">
+        <v>480675</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="U10" s="5" t="n">
+        <v>719928</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>alt_sgpt</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>61921</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="U11" s="5" t="n">
+        <v>61921</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>apnea_hypop_index</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>196</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>204354</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>6355</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>22317</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="U12" s="5" t="n">
+        <v>233026</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>ast_sgot</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>3581</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>60437</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="U13" s="5" t="n">
+        <v>64018</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>basophil_ct</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>53587</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" s="5" t="n">
+        <v>53587</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>basophil_ncnc_bld</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>340</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>32540</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>22894</v>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="7" t="n">
+        <v>3126</v>
+      </c>
+      <c r="R15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U15" s="5" t="n">
+        <v>58900</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>bdy_hgt</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>95859</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>40007</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>34019</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>64251</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>282446</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>33201</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>40969</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q16" s="7" t="n">
+        <v>68674</v>
+      </c>
+      <c r="R16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="S16" s="7" t="n">
+        <v>1852916</v>
+      </c>
+      <c r="T16" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="U16" s="5" t="n">
+        <v>2512342</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>bdy_temp</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" s="7" t="n">
+        <v>7647</v>
+      </c>
+      <c r="R17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" s="5" t="n">
+        <v>7647</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>bdy_wgt</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>63657</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>36242</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>57898</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>64250</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>239196</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>42107</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <v>23318</v>
+      </c>
+      <c r="P18" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q18" s="7" t="n">
+        <v>41958</v>
+      </c>
+      <c r="R18" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="S18" s="7" t="n">
+        <v>2297360</v>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="U18" s="5" t="n">
+        <v>2865986</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>bilirubin_con</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>16127</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" s="5" t="n">
+        <v>16127</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>bilirubin_tot</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>3583</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>61431</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="U20" s="5" t="n">
+        <v>65014</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>blood_pressure</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>115</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>1003408</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>7596</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>130363</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>84438</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>156</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>408522</v>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>35476</v>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="O21" s="7" t="n">
+        <v>97134</v>
+      </c>
+      <c r="P21" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q21" s="7" t="n">
+        <v>89867</v>
+      </c>
+      <c r="R21" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="S21" s="7" t="n">
+        <v>3726863</v>
+      </c>
+      <c r="T21" s="5" t="n">
+        <v>391</v>
+      </c>
+      <c r="U21" s="5" t="n">
+        <v>5583667</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>bmi</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>15611</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>20435</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>33989</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>64250</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>214420</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>23629</v>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="O22" s="7" t="n">
+        <v>19440</v>
+      </c>
+      <c r="P22" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q22" s="7" t="n">
+        <v>59750</v>
+      </c>
+      <c r="R22" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" s="7" t="n">
+        <v>1849280</v>
+      </c>
+      <c r="T22" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="U22" s="5" t="n">
+        <v>2300804</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>bnp</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>39457</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>1177</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>11965</v>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" s="7" t="n">
+        <v>3544</v>
+      </c>
+      <c r="P23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S23" s="7" t="n">
+        <v>7028</v>
+      </c>
+      <c r="T23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="U23" s="5" t="n">
+        <v>63171</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>bun</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>14918</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>40549</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="7" t="n">
+        <v>2773</v>
+      </c>
+      <c r="P24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" s="7" t="n">
+        <v>5928</v>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U24" s="5" t="n">
+        <v>64168</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>cac_score</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>17133</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>12170</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>36330</v>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="7" t="n">
+        <v>2144</v>
+      </c>
+      <c r="P25" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q25" s="7" t="n">
+        <v>185186</v>
+      </c>
+      <c r="R25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="U25" s="5" t="n">
+        <v>252963</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>cac_volume</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>2851</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>145982</v>
+      </c>
+      <c r="R26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="U26" s="5" t="n">
+        <v>148833</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>carotid_imt</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>340092</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>59398</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>20515</v>
+      </c>
+      <c r="L27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="O27" s="7" t="n">
+        <v>19862</v>
+      </c>
+      <c r="P27" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="7" t="n">
+        <v>13345</v>
+      </c>
+      <c r="R27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="U27" s="5" t="n">
+        <v>453212</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>carotid_sten_left</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>165</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>15520</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" s="7" t="n">
+        <v>10779</v>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>12791</v>
+      </c>
+      <c r="R28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="U28" s="5" t="n">
+        <v>39255</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>carotid_sten_right</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>162</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>15537</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>10786</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" s="7" t="n">
+        <v>12791</v>
+      </c>
+      <c r="R29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="U29" s="5" t="n">
+        <v>39276</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>cd40</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>7393</v>
+      </c>
+      <c r="R30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" s="5" t="n">
+        <v>7393</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>cesd_score</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>27247</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>8987</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>144</v>
+      </c>
+      <c r="L31" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>23495</v>
+      </c>
+      <c r="N31" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" s="7" t="n">
+        <v>6423</v>
+      </c>
+      <c r="P31" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>47837</v>
+      </c>
+      <c r="R31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="U31" s="5" t="n">
+        <v>114133</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>chloride_bld</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>5827</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>19616</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>3839</v>
+      </c>
+      <c r="P32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>6129</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="U32" s="5" t="n">
+        <v>35411</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>cig_smok</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>173641</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>5084</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>84173</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>66043</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>225600</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>28449</v>
+      </c>
+      <c r="N33" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O33" s="7" t="n">
+        <v>12859</v>
+      </c>
+      <c r="P33" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>87578</v>
+      </c>
+      <c r="R33" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" s="7" t="n">
+        <v>141363</v>
+      </c>
+      <c r="T33" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="U33" s="5" t="n">
+        <v>824790</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>creat_bld</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>220393</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>6451</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="K34" s="7" t="n">
+        <v>159845</v>
+      </c>
+      <c r="L34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>23654</v>
+      </c>
+      <c r="N34" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="O34" s="7" t="n">
+        <v>23763</v>
+      </c>
+      <c r="P34" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q34" s="7" t="n">
+        <v>9186</v>
+      </c>
+      <c r="R34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" s="7" t="n">
+        <v>5987</v>
+      </c>
+      <c r="T34" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="U34" s="5" t="n">
+        <v>449279</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>creat_urin</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>8779</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>6591</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>87104</v>
+      </c>
+      <c r="L35" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>23618</v>
+      </c>
+      <c r="N35" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="O35" s="7" t="n">
+        <v>23244</v>
+      </c>
+      <c r="P35" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q35" s="7" t="n">
+        <v>48092</v>
+      </c>
+      <c r="R35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="U35" s="5" t="n">
+        <v>197428</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>crp</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>20542</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>9585</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>20288</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>109598</v>
+      </c>
+      <c r="L36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>23651</v>
+      </c>
+      <c r="N36" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="O36" s="7" t="n">
+        <v>27442</v>
+      </c>
+      <c r="P36" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q36" s="7" t="n">
+        <v>23290</v>
+      </c>
+      <c r="R36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="U36" s="5" t="n">
+        <v>234396</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>cysc_bld</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>69181</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>4417</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>10725</v>
+      </c>
+      <c r="L37" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" s="7" t="n">
+        <v>23569</v>
+      </c>
+      <c r="N37" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" s="7" t="n">
+        <v>3783</v>
+      </c>
+      <c r="P37" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q37" s="7" t="n">
+        <v>21600</v>
+      </c>
+      <c r="R37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="U37" s="5" t="n">
+        <v>133275</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>d_dimer</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>12422</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>10710</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" s="7" t="n">
+        <v>10868</v>
+      </c>
+      <c r="L38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q38" s="7" t="n">
+        <v>22453</v>
+      </c>
+      <c r="R38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="U38" s="5" t="n">
+        <v>56453</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>edu_lvl</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>5515</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" s="5" t="n">
+        <v>5515</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>egfr</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>209569</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M40" s="7" t="n">
+        <v>34095</v>
+      </c>
+      <c r="N40" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O40" s="7" t="n">
+        <v>11561</v>
+      </c>
+      <c r="P40" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q40" s="7" t="n">
+        <v>69891</v>
+      </c>
+      <c r="R40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="U40" s="5" t="n">
+        <v>325116</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>eosinophil_ct</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>53588</v>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" s="5" t="n">
+        <v>53588</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>eosinophil_ncnc_bld</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>372</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" s="7" t="n">
+        <v>32540</v>
+      </c>
+      <c r="L42" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M42" s="7" t="n">
+        <v>22910</v>
+      </c>
+      <c r="N42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" s="7" t="n">
+        <v>3196</v>
+      </c>
+      <c r="R42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U42" s="5" t="n">
+        <v>59018</v>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>eselectin</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>7783</v>
+      </c>
+      <c r="L43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O43" s="7" t="n">
+        <v>5581</v>
+      </c>
+      <c r="P43" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q43" s="7" t="n">
+        <v>13840</v>
+      </c>
+      <c r="R43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="U43" s="5" t="n">
+        <v>27204</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>factor_7</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>15472</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>4636</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>25635</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K44" s="7" t="n">
+        <v>27175</v>
+      </c>
+      <c r="L44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S44" s="7" t="n">
+        <v>61040</v>
+      </c>
+      <c r="T44" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="U44" s="5" t="n">
+        <v>133958</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>factor_8</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>14793</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>2989</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>4817</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="7" t="n">
+        <v>20145</v>
+      </c>
+      <c r="R45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="U45" s="5" t="n">
+        <v>42744</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>fam_income</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>27593</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>9471</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K46" s="7" t="n">
+        <v>49939</v>
+      </c>
+      <c r="L46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="U46" s="5" t="n">
+        <v>87003</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>fast_gluc_bld</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>65854</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>7205</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="K47" s="7" t="n">
+        <v>83472</v>
+      </c>
+      <c r="L47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="O47" s="7" t="n">
+        <v>17868</v>
+      </c>
+      <c r="P47" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q47" s="7" t="n">
+        <v>68476</v>
+      </c>
+      <c r="R47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="U47" s="5" t="n">
+        <v>249309</v>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>fasting_blood_gluc</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M48" s="7" t="n">
+        <v>23653</v>
+      </c>
+      <c r="N48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" s="5" t="n">
+        <v>23653</v>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>ferritin</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M49" s="7" t="n">
+        <v>23448</v>
+      </c>
+      <c r="N49" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" s="7" t="n">
+        <v>3811</v>
+      </c>
+      <c r="P49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" s="5" t="n">
+        <v>27259</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>fibrin</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>15767</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>10916</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>25124</v>
+      </c>
+      <c r="H50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K50" s="7" t="n">
+        <v>53858</v>
+      </c>
+      <c r="L50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q50" s="7" t="n">
+        <v>21121</v>
+      </c>
+      <c r="R50" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S50" s="7" t="n">
+        <v>46006</v>
+      </c>
+      <c r="T50" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="U50" s="5" t="n">
+        <v>172792</v>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>fruit_serving</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>175886</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>40644</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" s="7" t="n">
+        <v>5690</v>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="7" t="n">
+        <v>130</v>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>375548</v>
+      </c>
+      <c r="L51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q51" s="7" t="n">
+        <v>8534</v>
+      </c>
+      <c r="R51" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S51" s="7" t="n">
+        <v>1018181</v>
+      </c>
+      <c r="T51" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="U51" s="5" t="n">
+        <v>1624483</v>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>glucose_bld</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>211779</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>6763</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>25155</v>
+      </c>
+      <c r="H52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="7" t="n">
+        <v>102</v>
+      </c>
+      <c r="K52" s="7" t="n">
+        <v>292594</v>
+      </c>
+      <c r="L52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O52" s="7" t="n">
+        <v>10187</v>
+      </c>
+      <c r="P52" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q52" s="7" t="n">
+        <v>358</v>
+      </c>
+      <c r="R52" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S52" s="7" t="n">
+        <v>46598</v>
+      </c>
+      <c r="T52" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="U52" s="5" t="n">
+        <v>593434</v>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>hdl</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>282573</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>16570</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>29869</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>148153</v>
+      </c>
+      <c r="L53" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" s="7" t="n">
+        <v>23652</v>
+      </c>
+      <c r="N53" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="O53" s="7" t="n">
+        <v>32797</v>
+      </c>
+      <c r="P53" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q53" s="7" t="n">
+        <v>74205</v>
+      </c>
+      <c r="R53" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S53" s="7" t="n">
+        <v>46573</v>
+      </c>
+      <c r="T53" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="U53" s="5" t="n">
+        <v>654392</v>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>hemat</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>61658</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>3582</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>25115</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>53674</v>
+      </c>
+      <c r="J54" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="K54" s="7" t="n">
+        <v>154499</v>
+      </c>
+      <c r="L54" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" s="7" t="n">
+        <v>23567</v>
+      </c>
+      <c r="N54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" s="7" t="n">
+        <v>3746</v>
+      </c>
+      <c r="P54" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q54" s="7" t="n">
+        <v>3656</v>
+      </c>
+      <c r="R54" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S54" s="7" t="n">
+        <v>629273</v>
+      </c>
+      <c r="T54" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="U54" s="5" t="n">
+        <v>958770</v>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>hemo</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>64879</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>3582</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>25115</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>53674</v>
+      </c>
+      <c r="J55" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K55" s="7" t="n">
+        <v>102103</v>
+      </c>
+      <c r="L55" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M55" s="7" t="n">
+        <v>23567</v>
+      </c>
+      <c r="N55" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" s="7" t="n">
+        <v>3746</v>
+      </c>
+      <c r="P55" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q55" s="7" t="n">
+        <v>3655</v>
+      </c>
+      <c r="R55" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S55" s="7" t="n">
+        <v>629314</v>
+      </c>
+      <c r="T55" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="U55" s="5" t="n">
+        <v>909635</v>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>hemo_a1c</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>8841</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K56" s="7" t="n">
+        <v>55340</v>
+      </c>
+      <c r="L56" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>23612</v>
+      </c>
+      <c r="N56" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="O56" s="7" t="n">
+        <v>28547</v>
+      </c>
+      <c r="P56" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q56" s="7" t="n">
+        <v>20878</v>
+      </c>
+      <c r="R56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="U56" s="5" t="n">
+        <v>137218</v>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>hip_circ</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>54020</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>33281</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>30339</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="K57" s="7" t="n">
+        <v>126492</v>
+      </c>
+      <c r="L57" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M57" s="7" t="n">
+        <v>23627</v>
+      </c>
+      <c r="N57" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="O57" s="7" t="n">
+        <v>17671</v>
+      </c>
+      <c r="P57" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q57" s="7" t="n">
+        <v>56541</v>
+      </c>
+      <c r="R57" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S57" s="7" t="n">
+        <v>1610762</v>
+      </c>
+      <c r="T57" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="U57" s="5" t="n">
+        <v>1952733</v>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>hrt_rt</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>64245</v>
+      </c>
+      <c r="J58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" s="5" t="n">
+        <v>64245</v>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>hrtrt</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>439669</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>60109</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>87</v>
+      </c>
+      <c r="G59" s="7" t="n">
+        <v>252223</v>
+      </c>
+      <c r="H59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="K59" s="7" t="n">
+        <v>185296</v>
+      </c>
+      <c r="L59" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M59" s="7" t="n">
+        <v>35266</v>
+      </c>
+      <c r="N59" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="O59" s="7" t="n">
+        <v>35238</v>
+      </c>
+      <c r="P59" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q59" s="7" t="n">
+        <v>154242</v>
+      </c>
+      <c r="R59" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S59" s="7" t="n">
+        <v>506519</v>
+      </c>
+      <c r="T59" s="5" t="n">
+        <v>288</v>
+      </c>
+      <c r="U59" s="5" t="n">
+        <v>1668562</v>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>icam</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>2669</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>7663</v>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q60" s="7" t="n">
+        <v>15379</v>
+      </c>
+      <c r="R60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U60" s="5" t="n">
+        <v>25711</v>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>il10</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q61" s="7" t="n">
+        <v>943</v>
+      </c>
+      <c r="R61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" s="5" t="n">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>il18</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K62" s="7" t="n">
+        <v>38307</v>
+      </c>
+      <c r="L62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" s="5" t="n">
+        <v>38307</v>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>il6</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="7" t="n">
+        <v>689</v>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="7" t="n">
+        <v>10594</v>
+      </c>
+      <c r="H63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q63" s="7" t="n">
+        <v>17277</v>
+      </c>
+      <c r="R63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U63" s="5" t="n">
+        <v>28560</v>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>insulin_blood</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>56942</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>9647</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>25071</v>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M64" s="7" t="n">
+        <v>23618</v>
+      </c>
+      <c r="N64" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O64" s="7" t="n">
+        <v>6587</v>
+      </c>
+      <c r="P64" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q64" s="7" t="n">
+        <v>25329</v>
+      </c>
+      <c r="R64" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S64" s="7" t="n">
+        <v>43342</v>
+      </c>
+      <c r="T64" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="U64" s="5" t="n">
+        <v>190536</v>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>insulin_in_blood</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K65" s="7" t="n">
+        <v>74472</v>
+      </c>
+      <c r="L65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U65" s="5" t="n">
+        <v>74472</v>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>isoprostane_8_epi_pgf2a</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>2720</v>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q66" s="7" t="n">
+        <v>6805</v>
+      </c>
+      <c r="R66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" s="5" t="n">
+        <v>9525</v>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>lactate</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K67" s="7" t="n">
+        <v>26148</v>
+      </c>
+      <c r="L67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U67" s="5" t="n">
+        <v>26148</v>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>lactate_dehyd</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K68" s="7" t="n">
+        <v>3530</v>
+      </c>
+      <c r="L68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" s="5" t="n">
+        <v>3530</v>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>ldl</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>173272</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" s="7" t="n">
+        <v>16477</v>
+      </c>
+      <c r="F69" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>25015</v>
+      </c>
+      <c r="H69" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="K69" s="7" t="n">
+        <v>123639</v>
+      </c>
+      <c r="L69" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M69" s="7" t="n">
+        <v>23409</v>
+      </c>
+      <c r="N69" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="O69" s="7" t="n">
+        <v>43886</v>
+      </c>
+      <c r="P69" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q69" s="7" t="n">
+        <v>68027</v>
+      </c>
+      <c r="R69" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S69" s="7" t="n">
+        <v>46331</v>
+      </c>
+      <c r="T69" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="U69" s="5" t="n">
+        <v>520056</v>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>lppla2_act</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>10910</v>
+      </c>
+      <c r="H70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="7" t="n">
+        <v>5122</v>
+      </c>
+      <c r="R70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" s="5" t="n">
+        <v>16032</v>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>lppla2_mass</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" s="7" t="n">
+        <v>10923</v>
+      </c>
+      <c r="H71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="7" t="n">
+        <v>5042</v>
+      </c>
+      <c r="R71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" s="5" t="n">
+        <v>15965</v>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>lympho_ct</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>5706</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>3968</v>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M72" s="7" t="n">
+        <v>22908</v>
+      </c>
+      <c r="N72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="7" t="n">
+        <v>2338</v>
+      </c>
+      <c r="R72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U72" s="5" t="n">
+        <v>34920</v>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>lympho_pct</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>24362</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K73" s="7" t="n">
+        <v>12638</v>
+      </c>
+      <c r="L73" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M73" s="7" t="n">
+        <v>22908</v>
+      </c>
+      <c r="N73" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O73" s="7" t="n">
+        <v>3362</v>
+      </c>
+      <c r="P73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="U73" s="5" t="n">
+        <v>63270</v>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>lymphocyte_ct</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>53590</v>
+      </c>
+      <c r="J74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U74" s="5" t="n">
+        <v>53590</v>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>mch</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>12069</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>7165</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I75" s="7" t="n">
+        <v>53674</v>
+      </c>
+      <c r="J75" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K75" s="7" t="n">
+        <v>54003</v>
+      </c>
+      <c r="L75" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M75" s="7" t="n">
+        <v>23567</v>
+      </c>
+      <c r="N75" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" s="7" t="n">
+        <v>3376</v>
+      </c>
+      <c r="P75" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" s="7" t="n">
+        <v>2756</v>
+      </c>
+      <c r="R75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="U75" s="5" t="n">
+        <v>156610</v>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>mchc</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>8408</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>53674</v>
+      </c>
+      <c r="J76" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K76" s="7" t="n">
+        <v>39615</v>
+      </c>
+      <c r="L76" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M76" s="7" t="n">
+        <v>23567</v>
+      </c>
+      <c r="N76" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" s="7" t="n">
+        <v>3377</v>
+      </c>
+      <c r="P76" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" s="7" t="n">
+        <v>2756</v>
+      </c>
+      <c r="R76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="U76" s="5" t="n">
+        <v>131397</v>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>mcv</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>28238</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <v>53674</v>
+      </c>
+      <c r="J77" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K77" s="7" t="n">
+        <v>39615</v>
+      </c>
+      <c r="L77" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M77" s="7" t="n">
+        <v>23567</v>
+      </c>
+      <c r="N77" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" s="7" t="n">
+        <v>3377</v>
+      </c>
+      <c r="P77" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q77" s="7" t="n">
+        <v>2756</v>
+      </c>
+      <c r="R77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="U77" s="5" t="n">
+        <v>151227</v>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>mean_art_press</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K78" s="7" t="n">
+        <v>50002</v>
+      </c>
+      <c r="L78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U78" s="5" t="n">
+        <v>50002</v>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>mmp9</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q79" s="7" t="n">
+        <v>7393</v>
+      </c>
+      <c r="R79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" s="5" t="n">
+        <v>7393</v>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>mn_art_pres</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>24769</v>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="7" t="n">
+        <v>18383</v>
+      </c>
+      <c r="R80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U80" s="5" t="n">
+        <v>43170</v>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>monocyte_ct</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I81" s="7" t="n">
+        <v>53588</v>
+      </c>
+      <c r="J81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" s="5" t="n">
+        <v>53588</v>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>monocyte_ncnc_bld</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>5706</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>384</v>
+      </c>
+      <c r="F82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K82" s="7" t="n">
+        <v>32540</v>
+      </c>
+      <c r="L82" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M82" s="7" t="n">
+        <v>22913</v>
+      </c>
+      <c r="N82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q82" s="7" t="n">
+        <v>3231</v>
+      </c>
+      <c r="R82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="U82" s="5" t="n">
+        <v>64774</v>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>neutro_ct</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" s="7" t="n">
+        <v>324</v>
+      </c>
+      <c r="F83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M83" s="7" t="n">
+        <v>22909</v>
+      </c>
+      <c r="N83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q83" s="7" t="n">
+        <v>2338</v>
+      </c>
+      <c r="R83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U83" s="5" t="n">
+        <v>25571</v>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>neutro_pct</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>18618</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="7" t="n">
+        <v>2407</v>
+      </c>
+      <c r="F84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M84" s="7" t="n">
+        <v>22908</v>
+      </c>
+      <c r="N84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U84" s="5" t="n">
+        <v>43933</v>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>neutrophil_ct</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I85" s="7" t="n">
+        <v>53590</v>
+      </c>
+      <c r="J85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U85" s="5" t="n">
+        <v>53590</v>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>nt_bnp</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>47302</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K86" s="7" t="n">
+        <v>19114</v>
+      </c>
+      <c r="L86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q86" s="7" t="n">
+        <v>10090</v>
+      </c>
+      <c r="R86" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S86" s="7" t="n">
+        <v>1802</v>
+      </c>
+      <c r="T86" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="U86" s="5" t="n">
+        <v>78308</v>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>pacem_stat</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>13110</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M87" s="7" t="n">
+        <v>11848</v>
+      </c>
+      <c r="N87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q87" s="7" t="n">
+        <v>12922</v>
+      </c>
+      <c r="R87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="U87" s="5" t="n">
+        <v>37880</v>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>platelet_ct</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C88" s="7" t="n">
+        <v>37442</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="7" t="n">
+        <v>3581</v>
+      </c>
+      <c r="F88" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G88" s="7" t="n">
+        <v>25046</v>
+      </c>
+      <c r="H88" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I88" s="7" t="n">
+        <v>53654</v>
+      </c>
+      <c r="J88" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="K88" s="7" t="n">
+        <v>35931</v>
+      </c>
+      <c r="L88" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M88" s="7" t="n">
+        <v>23560</v>
+      </c>
+      <c r="N88" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" s="7" t="n">
+        <v>3749</v>
+      </c>
+      <c r="P88" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q88" s="7" t="n">
+        <v>3644</v>
+      </c>
+      <c r="R88" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S88" s="7" t="n">
+        <v>623065</v>
+      </c>
+      <c r="T88" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="U88" s="5" t="n">
+        <v>809672</v>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>pmv</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" s="7" t="n">
+        <v>5707</v>
+      </c>
+      <c r="D89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K89" s="7" t="n">
+        <v>32540</v>
+      </c>
+      <c r="L89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O89" s="7" t="n">
+        <v>3376</v>
+      </c>
+      <c r="P89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="U89" s="5" t="n">
+        <v>41623</v>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>potassium</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C90" s="7" t="n">
+        <v>37384</v>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" s="7" t="n">
+        <v>6310</v>
+      </c>
+      <c r="F90" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G90" s="7" t="n">
+        <v>25155</v>
+      </c>
+      <c r="H90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" s="7" t="n">
+        <v>3839</v>
+      </c>
+      <c r="P90" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q90" s="7" t="n">
+        <v>18964</v>
+      </c>
+      <c r="R90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="U90" s="5" t="n">
+        <v>91652</v>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>pr_ekg</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>59015</v>
+      </c>
+      <c r="D91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M91" s="7" t="n">
+        <v>23526</v>
+      </c>
+      <c r="N91" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="O91" s="7" t="n">
+        <v>78673</v>
+      </c>
+      <c r="P91" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q91" s="7" t="n">
+        <v>22435</v>
+      </c>
+      <c r="R91" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S91" s="7" t="n">
+        <v>500439</v>
+      </c>
+      <c r="T91" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="U91" s="5" t="n">
+        <v>684088</v>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>pr_qrs_qt</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K92" s="7" t="n">
+        <v>66296</v>
+      </c>
+      <c r="L92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U92" s="5" t="n">
+        <v>66296</v>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>pselectin</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E93" s="7" t="n">
+        <v>326</v>
+      </c>
+      <c r="F93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O93" s="7" t="n">
+        <v>8299</v>
+      </c>
+      <c r="P93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U93" s="5" t="n">
+        <v>8625</v>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>qrs_ekg</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C94" s="7" t="n">
+        <v>274284</v>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G94" s="7" t="n">
+        <v>43430</v>
+      </c>
+      <c r="H94" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="K94" s="7" t="n">
+        <v>202581</v>
+      </c>
+      <c r="L94" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M94" s="7" t="n">
+        <v>23558</v>
+      </c>
+      <c r="N94" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="O94" s="7" t="n">
+        <v>65524</v>
+      </c>
+      <c r="P94" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="7" t="n">
+        <v>22514</v>
+      </c>
+      <c r="R94" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S94" s="7" t="n">
+        <v>500439</v>
+      </c>
+      <c r="T94" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="U94" s="5" t="n">
+        <v>1132330</v>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>qt_ekg</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C95" s="7" t="n">
+        <v>61199</v>
+      </c>
+      <c r="D95" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="K95" s="7" t="n">
+        <v>90128</v>
+      </c>
+      <c r="L95" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M95" s="7" t="n">
+        <v>35283</v>
+      </c>
+      <c r="N95" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="O95" s="7" t="n">
+        <v>46378</v>
+      </c>
+      <c r="P95" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q95" s="7" t="n">
+        <v>22514</v>
+      </c>
+      <c r="R95" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S95" s="7" t="n">
+        <v>500439</v>
+      </c>
+      <c r="T95" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="U95" s="5" t="n">
+        <v>755941</v>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>rbc</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I96" s="7" t="n">
+        <v>53674</v>
+      </c>
+      <c r="J96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U96" s="5" t="n">
+        <v>53674</v>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>rdbld_ct</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C97" s="7" t="n">
+        <v>14728</v>
+      </c>
+      <c r="D97" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>3583</v>
+      </c>
+      <c r="F97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K97" s="7" t="n">
+        <v>59154</v>
+      </c>
+      <c r="L97" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M97" s="7" t="n">
+        <v>23567</v>
+      </c>
+      <c r="N97" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O97" s="7" t="n">
+        <v>3377</v>
+      </c>
+      <c r="P97" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q97" s="7" t="n">
+        <v>3656</v>
+      </c>
+      <c r="R97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="U97" s="5" t="n">
+        <v>108065</v>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>rdw</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C98" s="7" t="n">
+        <v>12016</v>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K98" s="7" t="n">
+        <v>32543</v>
+      </c>
+      <c r="L98" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M98" s="7" t="n">
+        <v>23566</v>
+      </c>
+      <c r="N98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U98" s="5" t="n">
+        <v>68125</v>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>sleep_duration_daily</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" s="7" t="n">
+        <v>5925</v>
+      </c>
+      <c r="D99" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E99" s="7" t="n">
+        <v>3529</v>
+      </c>
+      <c r="F99" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G99" s="7" t="n">
+        <v>13853</v>
+      </c>
+      <c r="H99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="K99" s="7" t="n">
+        <v>129670</v>
+      </c>
+      <c r="L99" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M99" s="7" t="n">
+        <v>23080</v>
+      </c>
+      <c r="N99" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O99" s="7" t="n">
+        <v>6955</v>
+      </c>
+      <c r="P99" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q99" s="7" t="n">
+        <v>10941</v>
+      </c>
+      <c r="R99" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="S99" s="7" t="n">
+        <v>626832</v>
+      </c>
+      <c r="T99" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="U99" s="5" t="n">
+        <v>820785</v>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>sodium_blood</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C100" s="7" t="n">
+        <v>52984</v>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K100" s="7" t="n">
+        <v>17171</v>
+      </c>
+      <c r="L100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O100" s="7" t="n">
+        <v>3839</v>
+      </c>
+      <c r="P100" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q100" s="7" t="n">
+        <v>6129</v>
+      </c>
+      <c r="R100" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S100" s="7" t="n">
+        <v>5721</v>
+      </c>
+      <c r="T100" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U100" s="5" t="n">
+        <v>85844</v>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>sodium_intak</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C101" s="7" t="n">
+        <v>28614</v>
+      </c>
+      <c r="D101" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E101" s="7" t="n">
+        <v>16962</v>
+      </c>
+      <c r="F101" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G101" s="7" t="n">
+        <v>12180</v>
+      </c>
+      <c r="H101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K101" s="7" t="n">
+        <v>82860</v>
+      </c>
+      <c r="L101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q101" s="7" t="n">
+        <v>4252</v>
+      </c>
+      <c r="R101" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S101" s="7" t="n">
+        <v>338044</v>
+      </c>
+      <c r="T101" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="U101" s="5" t="n">
+        <v>482912</v>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>spirometry</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="C102" s="7" t="n">
+        <v>226242</v>
+      </c>
+      <c r="D102" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="E102" s="7" t="n">
+        <v>118442</v>
+      </c>
+      <c r="F102" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="G102" s="7" t="n">
+        <v>77987</v>
+      </c>
+      <c r="H102" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="I102" s="7" t="n">
+        <v>264146</v>
+      </c>
+      <c r="J102" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="K102" s="7" t="n">
+        <v>186708</v>
+      </c>
+      <c r="L102" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="M102" s="7" t="n">
+        <v>79778</v>
+      </c>
+      <c r="N102" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="O102" s="7" t="n">
+        <v>44329</v>
+      </c>
+      <c r="P102" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q102" s="7" t="n">
+        <v>28584</v>
+      </c>
+      <c r="R102" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" s="5" t="n">
+        <v>211</v>
+      </c>
+      <c r="U102" s="5" t="n">
+        <v>1026216</v>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>spo2</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G103" s="7" t="n">
+        <v>10480</v>
+      </c>
+      <c r="H103" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I103" s="7" t="n">
+        <v>64224</v>
+      </c>
+      <c r="J103" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" s="7" t="n">
+        <v>715</v>
+      </c>
+      <c r="L103" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M103" s="7" t="n">
+        <v>22347</v>
+      </c>
+      <c r="N103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="U103" s="5" t="n">
+        <v>97766</v>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>tnfa</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q104" s="7" t="n">
+        <v>6524</v>
+      </c>
+      <c r="R104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U104" s="5" t="n">
+        <v>6524</v>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>tnfa_r1</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q105" s="7" t="n">
+        <v>9242</v>
+      </c>
+      <c r="R105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U105" s="5" t="n">
+        <v>9242</v>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>tot_chol_bld</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="C106" s="7" t="n">
+        <v>245458</v>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E106" s="7" t="n">
+        <v>6897</v>
+      </c>
+      <c r="F106" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G106" s="7" t="n">
+        <v>11010</v>
+      </c>
+      <c r="H106" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="K106" s="7" t="n">
+        <v>218271</v>
+      </c>
+      <c r="L106" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M106" s="7" t="n">
+        <v>23653</v>
+      </c>
+      <c r="N106" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="O106" s="7" t="n">
+        <v>31460</v>
+      </c>
+      <c r="P106" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q106" s="7" t="n">
+        <v>68149</v>
+      </c>
+      <c r="R106" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S106" s="7" t="n">
+        <v>46610</v>
+      </c>
+      <c r="T106" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="U106" s="5" t="n">
+        <v>651508</v>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>triglyc_bld</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C107" s="7" t="n">
+        <v>167017</v>
+      </c>
+      <c r="D107" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E107" s="7" t="n">
+        <v>16569</v>
+      </c>
+      <c r="F107" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G107" s="7" t="n">
+        <v>29264</v>
+      </c>
+      <c r="H107" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="K107" s="7" t="n">
+        <v>168009</v>
+      </c>
+      <c r="L107" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M107" s="7" t="n">
+        <v>23653</v>
+      </c>
+      <c r="N107" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="O107" s="7" t="n">
+        <v>32777</v>
+      </c>
+      <c r="P107" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q107" s="7" t="n">
+        <v>67803</v>
+      </c>
+      <c r="R107" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S107" s="7" t="n">
+        <v>46610</v>
+      </c>
+      <c r="T107" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="U107" s="5" t="n">
+        <v>551702</v>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>troponin</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C108" s="7" t="n">
+        <v>59241</v>
+      </c>
+      <c r="D108" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="F108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K108" s="7" t="n">
+        <v>14391</v>
+      </c>
+      <c r="L108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S108" s="7" t="n">
+        <v>4604</v>
+      </c>
+      <c r="T108" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="U108" s="5" t="n">
+        <v>78313</v>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>vege_serving</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="C109" s="7" t="n">
+        <v>322380</v>
+      </c>
+      <c r="D109" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="E109" s="7" t="n">
+        <v>74514</v>
+      </c>
+      <c r="F109" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G109" s="7" t="n">
+        <v>771</v>
+      </c>
+      <c r="H109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="7" t="n">
+        <v>232</v>
+      </c>
+      <c r="K109" s="7" t="n">
+        <v>638568</v>
+      </c>
+      <c r="L109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O109" s="7" t="n">
+        <v>7594</v>
+      </c>
+      <c r="P109" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q109" s="7" t="n">
+        <v>29869</v>
+      </c>
+      <c r="R109" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S109" s="7" t="n">
+        <v>680137</v>
+      </c>
+      <c r="T109" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="U109" s="5" t="n">
+        <v>1753833</v>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>waist_circ</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C110" s="7" t="n">
+        <v>54019</v>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E110" s="7" t="n">
+        <v>30185</v>
+      </c>
+      <c r="F110" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G110" s="7" t="n">
+        <v>43939</v>
+      </c>
+      <c r="H110" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I110" s="7" t="n">
+        <v>53850</v>
+      </c>
+      <c r="J110" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="K110" s="7" t="n">
+        <v>175209</v>
+      </c>
+      <c r="L110" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M110" s="7" t="n">
+        <v>23633</v>
+      </c>
+      <c r="N110" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="O110" s="7" t="n">
+        <v>25409</v>
+      </c>
+      <c r="P110" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q110" s="7" t="n">
+        <v>56543</v>
+      </c>
+      <c r="R110" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S110" s="7" t="n">
+        <v>1619039</v>
+      </c>
+      <c r="T110" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="U110" s="5" t="n">
+        <v>2081826</v>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>waist_hip</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C111" s="7" t="n">
+        <v>106654</v>
+      </c>
+      <c r="D111" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" s="7" t="n">
+        <v>388</v>
+      </c>
+      <c r="F111" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M111" s="7" t="n">
+        <v>23626</v>
+      </c>
+      <c r="N111" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="O111" s="7" t="n">
+        <v>23478</v>
+      </c>
+      <c r="P111" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q111" s="7" t="n">
+        <v>89497</v>
+      </c>
+      <c r="R111" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S111" s="7" t="n">
+        <v>1610605</v>
+      </c>
+      <c r="T111" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="U111" s="5" t="n">
+        <v>1854248</v>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>whtbld_ct</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C112" s="7" t="n">
+        <v>43076</v>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="7" t="n">
+        <v>3583</v>
+      </c>
+      <c r="F112" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G112" s="7" t="n">
+        <v>10978</v>
+      </c>
+      <c r="H112" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I112" s="7" t="n">
+        <v>53674</v>
+      </c>
+      <c r="J112" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K112" s="7" t="n">
+        <v>60160</v>
+      </c>
+      <c r="L112" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M112" s="7" t="n">
+        <v>22911</v>
+      </c>
+      <c r="N112" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O112" s="7" t="n">
+        <v>3377</v>
+      </c>
+      <c r="P112" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q112" s="7" t="n">
+        <v>3656</v>
+      </c>
+      <c r="R112" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S112" s="7" t="n">
+        <v>623680</v>
+      </c>
+      <c r="T112" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="U112" s="5" t="n">
+        <v>825095</v>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>willeb_fac</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" s="7" t="n">
+        <v>14801</v>
+      </c>
+      <c r="D113" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E113" s="7" t="n">
+        <v>6928</v>
+      </c>
+      <c r="F113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K113" s="7" t="n">
+        <v>12072</v>
+      </c>
+      <c r="L113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q113" s="7" t="n">
+        <v>7391</v>
+      </c>
+      <c r="R113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U113" s="5" t="n">
+        <v>41192</v>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>1097</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>10820149</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>553</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>1023563</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>1235</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>3710632</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>68</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>1153694</v>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>2537</v>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>5829880</v>
-      </c>
-      <c r="L7" s="7" t="n">
-        <v>117</v>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>1204144</v>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>410</v>
-      </c>
-      <c r="O7" s="7" t="n">
-        <v>1437744</v>
-      </c>
-      <c r="P7" s="7" t="n">
-        <v>945</v>
-      </c>
-      <c r="Q7" s="7" t="n">
-        <v>3009733</v>
-      </c>
-      <c r="R7" s="7" t="n">
-        <v>322</v>
-      </c>
-      <c r="S7" s="7" t="n">
-        <v>24270315</v>
-      </c>
-      <c r="T7" s="7" t="n">
-        <v>7284</v>
-      </c>
-      <c r="U7" s="7" t="n">
-        <v>52459854</v>
+      <c r="B114" s="9" t="n">
+        <v>1178</v>
+      </c>
+      <c r="C114" s="9" t="n">
+        <v>11553653</v>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>565</v>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>1035671</v>
+      </c>
+      <c r="F114" s="9" t="n">
+        <v>1349</v>
+      </c>
+      <c r="G114" s="9" t="n">
+        <v>4161858</v>
+      </c>
+      <c r="H114" s="9" t="n">
+        <v>112</v>
+      </c>
+      <c r="I114" s="9" t="n">
+        <v>2122662</v>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>3087</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>9071383</v>
+      </c>
+      <c r="L114" s="9" t="n">
+        <v>165</v>
+      </c>
+      <c r="M114" s="9" t="n">
+        <v>1772032</v>
+      </c>
+      <c r="N114" s="9" t="n">
+        <v>477</v>
+      </c>
+      <c r="O114" s="9" t="n">
+        <v>1643015</v>
+      </c>
+      <c r="P114" s="9" t="n">
+        <v>1196</v>
+      </c>
+      <c r="Q114" s="9" t="n">
+        <v>3908574</v>
+      </c>
+      <c r="R114" s="9" t="n">
+        <v>360</v>
+      </c>
+      <c r="S114" s="9" t="n">
+        <v>34121402</v>
+      </c>
+      <c r="T114" s="9" t="n">
+        <v>8489</v>
+      </c>
+      <c r="U114" s="9" t="n">
+        <v>69390250</v>
       </c>
     </row>
   </sheetData>

--- a/tables/before_table.xlsx
+++ b/tables/before_table.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U114"/>
+  <dimension ref="A1:U104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1106,7 +1106,7 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>alcohol_servings</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
@@ -1116,16 +1116,16 @@
         <v>0</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0</v>
+        <v>70762</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0</v>
+        <v>77508</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>3</v>
@@ -1146,34 +1146,34 @@
         <v>0</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>0</v>
+        <v>13255</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>0</v>
+        <v>77728</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>0</v>
+        <v>480675</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v>48863</v>
+        <v>768791</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>alcohol_servings</t>
+          <t>alt_sgpt</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
@@ -1183,16 +1183,16 @@
         <v>0</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>70762</v>
+        <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>77508</v>
+        <v>0</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>0</v>
@@ -1201,10 +1201,10 @@
         <v>0</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0</v>
+        <v>61921</v>
       </c>
       <c r="L10" s="7" t="n">
         <v>0</v>
@@ -1213,34 +1213,34 @@
         <v>0</v>
       </c>
       <c r="N10" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>13255</v>
+        <v>0</v>
       </c>
       <c r="P10" s="7" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>77728</v>
+        <v>0</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>480675</v>
+        <v>0</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>719928</v>
+        <v>61921</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>alt_sgpt</t>
+          <t>apnea_hypop_index</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
@@ -1256,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0</v>
+        <v>204354</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0</v>
@@ -1268,16 +1268,16 @@
         <v>0</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>61921</v>
+        <v>6355</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0</v>
+        <v>22317</v>
       </c>
       <c r="N11" s="7" t="n">
         <v>0</v>
@@ -1298,16 +1298,16 @@
         <v>0</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>12</v>
+        <v>203</v>
       </c>
       <c r="U11" s="5" t="n">
-        <v>61921</v>
+        <v>233026</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>apnea_hypop_index</t>
+          <t>ast_sgot</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
@@ -1317,16 +1317,16 @@
         <v>0</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0</v>
+        <v>3581</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>204354</v>
+        <v>0</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>0</v>
@@ -1335,16 +1335,16 @@
         <v>0</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>6355</v>
+        <v>60437</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>22317</v>
+        <v>0</v>
       </c>
       <c r="N12" s="7" t="n">
         <v>0</v>
@@ -1365,16 +1365,16 @@
         <v>0</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>203</v>
+        <v>12</v>
       </c>
       <c r="U12" s="5" t="n">
-        <v>233026</v>
+        <v>64018</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>ast_sgot</t>
+          <t>basophil_ncnc_bld</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
@@ -1384,10 +1384,10 @@
         <v>0</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>3581</v>
+        <v>340</v>
       </c>
       <c r="F13" s="7" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>0</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>0</v>
+        <v>53587</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>60437</v>
+        <v>32540</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0</v>
+        <v>22894</v>
       </c>
       <c r="N13" s="7" t="n">
         <v>0</v>
@@ -1420,10 +1420,10 @@
         <v>0</v>
       </c>
       <c r="P13" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>0</v>
+        <v>3126</v>
       </c>
       <c r="R13" s="7" t="n">
         <v>0</v>
@@ -1432,83 +1432,83 @@
         <v>0</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U13" s="5" t="n">
-        <v>64018</v>
+        <v>112487</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>basophil_ct</t>
+          <t>bdy_hgt</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>0</v>
+        <v>95859</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0</v>
+        <v>40007</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0</v>
+        <v>34019</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>3</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>53587</v>
+        <v>64251</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0</v>
+        <v>282446</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0</v>
+        <v>33201</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>0</v>
+        <v>40969</v>
       </c>
       <c r="P14" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>0</v>
+        <v>68674</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>0</v>
+        <v>1852916</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>53587</v>
+        <v>2512342</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>basophil_ncnc_bld</t>
+          <t>bdy_temp</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
@@ -1518,10 +1518,10 @@
         <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>0</v>
@@ -1536,16 +1536,16 @@
         <v>0</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>32540</v>
+        <v>0</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>22894</v>
+        <v>0</v>
       </c>
       <c r="N15" s="7" t="n">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>2</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>3126</v>
+        <v>7647</v>
       </c>
       <c r="R15" s="7" t="n">
         <v>0</v>
@@ -1566,83 +1566,83 @@
         <v>0</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="U15" s="5" t="n">
-        <v>58900</v>
+        <v>7647</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>bdy_hgt</t>
+          <t>bdy_wgt</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>95859</v>
+        <v>63657</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>40007</v>
+        <v>36242</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>34019</v>
+        <v>57898</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>3</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>64251</v>
+        <v>64250</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>282446</v>
+        <v>239196</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>33201</v>
+        <v>42107</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>40969</v>
+        <v>23318</v>
       </c>
       <c r="P16" s="7" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>68674</v>
+        <v>41958</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>1852916</v>
+        <v>2297360</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>200</v>
+        <v>158</v>
       </c>
       <c r="U16" s="5" t="n">
-        <v>2512342</v>
+        <v>2865986</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>bdy_temp</t>
+          <t>bilirubin_con</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
@@ -1670,10 +1670,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0</v>
+        <v>16127</v>
       </c>
       <c r="L17" s="7" t="n">
         <v>0</v>
@@ -1688,10 +1688,10 @@
         <v>0</v>
       </c>
       <c r="P17" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>7647</v>
+        <v>0</v>
       </c>
       <c r="R17" s="7" t="n">
         <v>0</v>
@@ -1703,367 +1703,367 @@
         <v>2</v>
       </c>
       <c r="U17" s="5" t="n">
-        <v>7647</v>
+        <v>16127</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>bdy_wgt</t>
+          <t>bilirubin_tot</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>63657</v>
+        <v>0</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>36242</v>
+        <v>3583</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>57898</v>
+        <v>0</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>64250</v>
+        <v>0</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>239196</v>
+        <v>61431</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>42107</v>
+        <v>0</v>
       </c>
       <c r="N18" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>23318</v>
+        <v>0</v>
       </c>
       <c r="P18" s="7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>41958</v>
+        <v>0</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>2297360</v>
+        <v>0</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>158</v>
+        <v>13</v>
       </c>
       <c r="U18" s="5" t="n">
-        <v>2865986</v>
+        <v>65014</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>bilirubin_con</t>
+          <t>blood_pressure</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>0</v>
+        <v>1003408</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0</v>
+        <v>7596</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0</v>
+        <v>130363</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>0</v>
+        <v>84438</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>2</v>
+        <v>156</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>16127</v>
+        <v>408522</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0</v>
+        <v>35476</v>
       </c>
       <c r="N19" s="7" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>0</v>
+        <v>97134</v>
       </c>
       <c r="P19" s="7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>0</v>
+        <v>89867</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>0</v>
+        <v>3726863</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>2</v>
+        <v>391</v>
       </c>
       <c r="U19" s="5" t="n">
-        <v>16127</v>
+        <v>5583667</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>bilirubin_tot</t>
+          <t>bmi</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>0</v>
+        <v>15611</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>3583</v>
+        <v>20435</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0</v>
+        <v>33989</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>0</v>
+        <v>64250</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>61431</v>
+        <v>214420</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0</v>
+        <v>23629</v>
       </c>
       <c r="N20" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>0</v>
+        <v>19440</v>
       </c>
       <c r="P20" s="7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>0</v>
+        <v>59750</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>0</v>
+        <v>1849280</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="U20" s="5" t="n">
-        <v>65014</v>
+        <v>2300804</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>blood_pressure</t>
+          <t>bnp</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>1003408</v>
+        <v>39457</v>
       </c>
       <c r="D21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>1177</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="7" t="n">
-        <v>7596</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>130363</v>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>84438</v>
-      </c>
-      <c r="J21" s="7" t="n">
-        <v>156</v>
-      </c>
       <c r="K21" s="7" t="n">
-        <v>408522</v>
+        <v>11965</v>
       </c>
       <c r="L21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="7" t="n">
+        <v>3544</v>
+      </c>
+      <c r="P21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="M21" s="7" t="n">
-        <v>35476</v>
-      </c>
-      <c r="N21" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="O21" s="7" t="n">
-        <v>97134</v>
-      </c>
-      <c r="P21" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q21" s="7" t="n">
-        <v>89867</v>
-      </c>
-      <c r="R21" s="7" t="n">
-        <v>12</v>
-      </c>
       <c r="S21" s="7" t="n">
-        <v>3726863</v>
+        <v>7028</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>391</v>
+        <v>19</v>
       </c>
       <c r="U21" s="5" t="n">
-        <v>5583667</v>
+        <v>63171</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>bmi</t>
+          <t>bun</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>15611</v>
+        <v>14918</v>
       </c>
       <c r="D22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="E22" s="7" t="n">
-        <v>20435</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>33989</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>64250</v>
-      </c>
-      <c r="J22" s="7" t="n">
-        <v>75</v>
-      </c>
       <c r="K22" s="7" t="n">
-        <v>214420</v>
+        <v>40549</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>23629</v>
+        <v>0</v>
       </c>
       <c r="N22" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>19440</v>
+        <v>2773</v>
       </c>
       <c r="P22" s="7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>59750</v>
+        <v>0</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>1849280</v>
+        <v>5928</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="U22" s="5" t="n">
-        <v>2300804</v>
+        <v>64168</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>bnp</t>
+          <t>cac_score</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>39457</v>
+        <v>0</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>1177</v>
+        <v>17133</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0</v>
+        <v>12170</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>0</v>
@@ -2072,10 +2072,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>11965</v>
+        <v>36330</v>
       </c>
       <c r="L23" s="7" t="n">
         <v>0</v>
@@ -2087,62 +2087,62 @@
         <v>1</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>3544</v>
+        <v>2144</v>
       </c>
       <c r="P23" s="7" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>0</v>
+        <v>185186</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>7028</v>
+        <v>0</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="U23" s="5" t="n">
-        <v>63171</v>
+        <v>252963</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>bun</t>
+          <t>cac_volume</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="7" t="n">
-        <v>14918</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="7" t="n">
-        <v>8</v>
-      </c>
       <c r="K24" s="7" t="n">
-        <v>40549</v>
+        <v>2851</v>
       </c>
       <c r="L24" s="7" t="n">
         <v>0</v>
@@ -2151,53 +2151,53 @@
         <v>0</v>
       </c>
       <c r="N24" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>2773</v>
+        <v>0</v>
       </c>
       <c r="P24" s="7" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>0</v>
+        <v>145982</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>5928</v>
+        <v>0</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="U24" s="5" t="n">
-        <v>64168</v>
+        <v>148833</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>cac_score</t>
+          <t>carotid_imt</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>0</v>
+        <v>340092</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>17133</v>
+        <v>0</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>12170</v>
+        <v>59398</v>
       </c>
       <c r="H25" s="7" t="n">
         <v>0</v>
@@ -2206,10 +2206,10 @@
         <v>0</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>36330</v>
+        <v>20515</v>
       </c>
       <c r="L25" s="7" t="n">
         <v>0</v>
@@ -2218,16 +2218,16 @@
         <v>0</v>
       </c>
       <c r="N25" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>2144</v>
+        <v>19862</v>
       </c>
       <c r="P25" s="7" t="n">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>185186</v>
+        <v>13345</v>
       </c>
       <c r="R25" s="7" t="n">
         <v>0</v>
@@ -2236,23 +2236,23 @@
         <v>0</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="U25" s="5" t="n">
-        <v>252963</v>
+        <v>453212</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>cac_volume</t>
+          <t>carotid_sten_left</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>0</v>
@@ -2261,10 +2261,10 @@
         <v>0</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>0</v>
+        <v>15520</v>
       </c>
       <c r="H26" s="7" t="n">
         <v>0</v>
@@ -2273,10 +2273,10 @@
         <v>0</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>2851</v>
+        <v>10779</v>
       </c>
       <c r="L26" s="7" t="n">
         <v>0</v>
@@ -2291,10 +2291,10 @@
         <v>0</v>
       </c>
       <c r="P26" s="7" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="7" t="n">
-        <v>145982</v>
+        <v>12791</v>
       </c>
       <c r="R26" s="7" t="n">
         <v>0</v>
@@ -2303,23 +2303,23 @@
         <v>0</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="U26" s="5" t="n">
-        <v>148833</v>
+        <v>39255</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>carotid_imt</t>
+          <t>carotid_sten_right</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>340092</v>
+        <v>162</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
         <v>0</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>59398</v>
+        <v>15537</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>0</v>
@@ -2340,10 +2340,10 @@
         <v>0</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>20515</v>
+        <v>10786</v>
       </c>
       <c r="L27" s="7" t="n">
         <v>0</v>
@@ -2352,16 +2352,16 @@
         <v>0</v>
       </c>
       <c r="N27" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>19862</v>
+        <v>0</v>
       </c>
       <c r="P27" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>13345</v>
+        <v>12791</v>
       </c>
       <c r="R27" s="7" t="n">
         <v>0</v>
@@ -2370,23 +2370,23 @@
         <v>0</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="U27" s="5" t="n">
-        <v>453212</v>
+        <v>39276</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>carotid_sten_left</t>
+          <t>cd40</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>0</v>
@@ -2395,10 +2395,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>15520</v>
+        <v>0</v>
       </c>
       <c r="H28" s="7" t="n">
         <v>0</v>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>10779</v>
+        <v>0</v>
       </c>
       <c r="L28" s="7" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>2</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>12791</v>
+        <v>7393</v>
       </c>
       <c r="R28" s="7" t="n">
         <v>0</v>
@@ -2437,35 +2437,35 @@
         <v>0</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U28" s="5" t="n">
-        <v>39255</v>
+        <v>7393</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>carotid_sten_right</t>
+          <t>cesd_score</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>162</v>
+        <v>27247</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>0</v>
+        <v>8987</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>15537</v>
+        <v>0</v>
       </c>
       <c r="H29" s="7" t="n">
         <v>0</v>
@@ -2477,25 +2477,25 @@
         <v>2</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>10786</v>
+        <v>144</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0</v>
+        <v>23495</v>
       </c>
       <c r="N29" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>0</v>
+        <v>6423</v>
       </c>
       <c r="P29" s="7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>12791</v>
+        <v>47837</v>
       </c>
       <c r="R29" s="7" t="n">
         <v>0</v>
@@ -2504,23 +2504,23 @@
         <v>0</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="U29" s="5" t="n">
-        <v>39276</v>
+        <v>114133</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>cd40</t>
+          <t>chloride_bld</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>0</v>
+        <v>5827</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>0</v>
@@ -2541,10 +2541,10 @@
         <v>0</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0</v>
+        <v>19616</v>
       </c>
       <c r="L30" s="7" t="n">
         <v>0</v>
@@ -2553,16 +2553,16 @@
         <v>0</v>
       </c>
       <c r="N30" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>0</v>
+        <v>3839</v>
       </c>
       <c r="P30" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>7393</v>
+        <v>6129</v>
       </c>
       <c r="R30" s="7" t="n">
         <v>0</v>
@@ -2571,236 +2571,236 @@
         <v>0</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U30" s="5" t="n">
-        <v>7393</v>
+        <v>35411</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>cesd_score</t>
+          <t>cig_smok</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>27247</v>
+        <v>173641</v>
       </c>
       <c r="D31" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>5084</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>84173</v>
+      </c>
+      <c r="H31" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E31" s="7" t="n">
-        <v>8987</v>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="I31" s="7" t="n">
-        <v>0</v>
+        <v>66043</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>144</v>
+        <v>225600</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>23495</v>
+        <v>28449</v>
       </c>
       <c r="N31" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>6423</v>
+        <v>12859</v>
       </c>
       <c r="P31" s="7" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="Q31" s="7" t="n">
-        <v>47837</v>
+        <v>87578</v>
       </c>
       <c r="R31" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="7" t="n">
-        <v>0</v>
+        <v>141363</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="U31" s="5" t="n">
-        <v>114133</v>
+        <v>824790</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>chloride_bld</t>
+          <t>creat_bld</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>220393</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>6451</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>159845</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>23654</v>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>23763</v>
+      </c>
+      <c r="P32" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>9186</v>
+      </c>
+      <c r="R32" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="7" t="n">
-        <v>5827</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>19616</v>
-      </c>
-      <c r="L32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" s="7" t="n">
-        <v>3839</v>
-      </c>
-      <c r="P32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="7" t="n">
-        <v>6129</v>
-      </c>
-      <c r="R32" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" s="7" t="n">
-        <v>0</v>
+        <v>5987</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="U32" s="5" t="n">
-        <v>35411</v>
+        <v>449279</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>cig_smok</t>
+          <t>creat_urin</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>173641</v>
+        <v>8779</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>5084</v>
+        <v>6591</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>84173</v>
+        <v>0</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>66043</v>
+        <v>0</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>225600</v>
+        <v>87104</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>28449</v>
+        <v>23618</v>
       </c>
       <c r="N33" s="7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>12859</v>
+        <v>23244</v>
       </c>
       <c r="P33" s="7" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="Q33" s="7" t="n">
-        <v>87578</v>
+        <v>48092</v>
       </c>
       <c r="R33" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" s="7" t="n">
-        <v>141363</v>
+        <v>0</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="U33" s="5" t="n">
-        <v>824790</v>
+        <v>197428</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>creat_bld</t>
+          <t>crp</t>
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>220393</v>
+        <v>20542</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>6451</v>
+        <v>9585</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>0</v>
+        <v>20288</v>
       </c>
       <c r="H34" s="7" t="n">
         <v>0</v>
@@ -2809,65 +2809,65 @@
         <v>0</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>159845</v>
+        <v>109598</v>
       </c>
       <c r="L34" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>23654</v>
+        <v>23651</v>
       </c>
       <c r="N34" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O34" s="7" t="n">
-        <v>23763</v>
+        <v>27442</v>
       </c>
       <c r="P34" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q34" s="7" t="n">
-        <v>9186</v>
+        <v>23290</v>
       </c>
       <c r="R34" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" s="7" t="n">
-        <v>5987</v>
+        <v>0</v>
       </c>
       <c r="T34" s="5" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="U34" s="5" t="n">
-        <v>449279</v>
+        <v>234396</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>creat_urin</t>
+          <t>cysc_bld</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>8779</v>
+        <v>69181</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>6591</v>
+        <v>0</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>0</v>
+        <v>4417</v>
       </c>
       <c r="H35" s="7" t="n">
         <v>0</v>
@@ -2876,28 +2876,28 @@
         <v>0</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>87104</v>
+        <v>10725</v>
       </c>
       <c r="L35" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>23618</v>
+        <v>23569</v>
       </c>
       <c r="N35" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>23244</v>
+        <v>3783</v>
       </c>
       <c r="P35" s="7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Q35" s="7" t="n">
-        <v>48092</v>
+        <v>21600</v>
       </c>
       <c r="R35" s="7" t="n">
         <v>0</v>
@@ -2906,35 +2906,35 @@
         <v>0</v>
       </c>
       <c r="T35" s="5" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="U35" s="5" t="n">
-        <v>197428</v>
+        <v>133275</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>crp</t>
+          <t>d_dimer</t>
         </is>
       </c>
       <c r="B36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>12422</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C36" s="7" t="n">
-        <v>20542</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>9585</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>6</v>
-      </c>
       <c r="G36" s="7" t="n">
-        <v>20288</v>
+        <v>10710</v>
       </c>
       <c r="H36" s="7" t="n">
         <v>0</v>
@@ -2943,28 +2943,28 @@
         <v>0</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>109598</v>
+        <v>10868</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" s="7" t="n">
-        <v>23651</v>
+        <v>0</v>
       </c>
       <c r="N36" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O36" s="7" t="n">
-        <v>27442</v>
+        <v>0</v>
       </c>
       <c r="P36" s="7" t="n">
         <v>9</v>
       </c>
       <c r="Q36" s="7" t="n">
-        <v>23290</v>
+        <v>22453</v>
       </c>
       <c r="R36" s="7" t="n">
         <v>0</v>
@@ -2973,23 +2973,23 @@
         <v>0</v>
       </c>
       <c r="T36" s="5" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="U36" s="5" t="n">
-        <v>234396</v>
+        <v>56453</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>cysc_bld</t>
+          <t>edu_lvl</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>69181</v>
+        <v>0</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
@@ -2998,10 +2998,10 @@
         <v>0</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>4417</v>
+        <v>5515</v>
       </c>
       <c r="H37" s="7" t="n">
         <v>0</v>
@@ -3010,28 +3010,28 @@
         <v>0</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>10725</v>
+        <v>0</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" s="7" t="n">
-        <v>23569</v>
+        <v>0</v>
       </c>
       <c r="N37" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>3783</v>
+        <v>0</v>
       </c>
       <c r="P37" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="7" t="n">
-        <v>21600</v>
+        <v>0</v>
       </c>
       <c r="R37" s="7" t="n">
         <v>0</v>
@@ -3040,23 +3040,23 @@
         <v>0</v>
       </c>
       <c r="T37" s="5" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="U37" s="5" t="n">
-        <v>133275</v>
+        <v>5515</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>d_dimer</t>
+          <t>egfr</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>12422</v>
+        <v>209569</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>0</v>
@@ -3065,10 +3065,10 @@
         <v>0</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>10710</v>
+        <v>0</v>
       </c>
       <c r="H38" s="7" t="n">
         <v>0</v>
@@ -3077,28 +3077,28 @@
         <v>0</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>10868</v>
+        <v>0</v>
       </c>
       <c r="L38" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" s="7" t="n">
-        <v>0</v>
+        <v>34095</v>
       </c>
       <c r="N38" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O38" s="7" t="n">
-        <v>0</v>
+        <v>11561</v>
       </c>
       <c r="P38" s="7" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="Q38" s="7" t="n">
-        <v>22453</v>
+        <v>69891</v>
       </c>
       <c r="R38" s="7" t="n">
         <v>0</v>
@@ -3107,16 +3107,16 @@
         <v>0</v>
       </c>
       <c r="T38" s="5" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="U38" s="5" t="n">
-        <v>56453</v>
+        <v>325116</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>edu_lvl</t>
+          <t>eosinophil_ncnc_bld</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
@@ -3126,34 +3126,34 @@
         <v>0</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>5515</v>
+        <v>0</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>0</v>
+        <v>53588</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0</v>
+        <v>32540</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" s="7" t="n">
-        <v>0</v>
+        <v>22910</v>
       </c>
       <c r="N39" s="7" t="n">
         <v>0</v>
@@ -3162,10 +3162,10 @@
         <v>0</v>
       </c>
       <c r="P39" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q39" s="7" t="n">
-        <v>0</v>
+        <v>3196</v>
       </c>
       <c r="R39" s="7" t="n">
         <v>0</v>
@@ -3174,23 +3174,23 @@
         <v>0</v>
       </c>
       <c r="T39" s="5" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="U39" s="5" t="n">
-        <v>5515</v>
+        <v>112606</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>egfr</t>
+          <t>eselectin</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>209569</v>
+        <v>0</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>0</v>
@@ -3211,28 +3211,28 @@
         <v>0</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0</v>
+        <v>7783</v>
       </c>
       <c r="L40" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M40" s="7" t="n">
-        <v>34095</v>
+        <v>0</v>
       </c>
       <c r="N40" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O40" s="7" t="n">
-        <v>11561</v>
+        <v>5581</v>
       </c>
       <c r="P40" s="7" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="Q40" s="7" t="n">
-        <v>69891</v>
+        <v>13840</v>
       </c>
       <c r="R40" s="7" t="n">
         <v>0</v>
@@ -3241,47 +3241,47 @@
         <v>0</v>
       </c>
       <c r="T40" s="5" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="U40" s="5" t="n">
-        <v>325116</v>
+        <v>27204</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>eosinophil_ct</t>
+          <t>factor_7</t>
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>0</v>
+        <v>15472</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>0</v>
+        <v>4636</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>0</v>
+        <v>25635</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>53588</v>
+        <v>0</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0</v>
+        <v>27175</v>
       </c>
       <c r="L41" s="7" t="n">
         <v>0</v>
@@ -3302,41 +3302,41 @@
         <v>0</v>
       </c>
       <c r="R41" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S41" s="7" t="n">
-        <v>0</v>
+        <v>61040</v>
       </c>
       <c r="T41" s="5" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="U41" s="5" t="n">
-        <v>53588</v>
+        <v>133958</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>eosinophil_ncnc_bld</t>
+          <t>factor_8</t>
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>0</v>
+        <v>14793</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>372</v>
+        <v>2989</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>0</v>
+        <v>4817</v>
       </c>
       <c r="H42" s="7" t="n">
         <v>0</v>
@@ -3345,16 +3345,16 @@
         <v>0</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>32540</v>
+        <v>0</v>
       </c>
       <c r="L42" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" s="7" t="n">
-        <v>22910</v>
+        <v>0</v>
       </c>
       <c r="N42" s="7" t="n">
         <v>0</v>
@@ -3363,10 +3363,10 @@
         <v>0</v>
       </c>
       <c r="P42" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q42" s="7" t="n">
-        <v>3196</v>
+        <v>20145</v>
       </c>
       <c r="R42" s="7" t="n">
         <v>0</v>
@@ -3375,23 +3375,23 @@
         <v>0</v>
       </c>
       <c r="T42" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U42" s="5" t="n">
-        <v>59018</v>
+        <v>42744</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>eselectin</t>
+          <t>fam_income</t>
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>0</v>
+        <v>27593</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>0</v>
@@ -3400,10 +3400,10 @@
         <v>0</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>0</v>
+        <v>9471</v>
       </c>
       <c r="H43" s="7" t="n">
         <v>0</v>
@@ -3412,10 +3412,10 @@
         <v>0</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>7783</v>
+        <v>49939</v>
       </c>
       <c r="L43" s="7" t="n">
         <v>0</v>
@@ -3424,16 +3424,16 @@
         <v>0</v>
       </c>
       <c r="N43" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O43" s="7" t="n">
-        <v>5581</v>
+        <v>0</v>
       </c>
       <c r="P43" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="7" t="n">
-        <v>13840</v>
+        <v>0</v>
       </c>
       <c r="R43" s="7" t="n">
         <v>0</v>
@@ -3442,35 +3442,35 @@
         <v>0</v>
       </c>
       <c r="T43" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U43" s="5" t="n">
-        <v>27204</v>
+        <v>87003</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>factor_7</t>
+          <t>fast_gluc_bld</t>
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>15472</v>
+        <v>65854</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>4636</v>
+        <v>6434</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>25635</v>
+        <v>7205</v>
       </c>
       <c r="H44" s="7" t="n">
         <v>0</v>
@@ -3479,95 +3479,95 @@
         <v>0</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>27175</v>
+        <v>83472</v>
       </c>
       <c r="L44" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>0</v>
+        <v>23653</v>
       </c>
       <c r="N44" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O44" s="7" t="n">
-        <v>0</v>
+        <v>17868</v>
       </c>
       <c r="P44" s="7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q44" s="7" t="n">
-        <v>0</v>
+        <v>68476</v>
       </c>
       <c r="R44" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S44" s="7" t="n">
-        <v>61040</v>
+        <v>0</v>
       </c>
       <c r="T44" s="5" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="U44" s="5" t="n">
-        <v>133958</v>
+        <v>272962</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>factor_8</t>
+          <t>ferritin</t>
         </is>
       </c>
       <c r="B45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" s="7" t="n">
+        <v>23448</v>
+      </c>
+      <c r="N45" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="7" t="n">
-        <v>14793</v>
-      </c>
-      <c r="D45" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E45" s="7" t="n">
-        <v>2989</v>
-      </c>
-      <c r="F45" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="7" t="n">
-        <v>4817</v>
-      </c>
-      <c r="H45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="O45" s="7" t="n">
-        <v>0</v>
+        <v>3811</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="7" t="n">
-        <v>20145</v>
+        <v>0</v>
       </c>
       <c r="R45" s="7" t="n">
         <v>0</v>
@@ -3576,102 +3576,102 @@
         <v>0</v>
       </c>
       <c r="T45" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U45" s="5" t="n">
-        <v>42744</v>
+        <v>27259</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>fam_income</t>
+          <t>fibrin</t>
         </is>
       </c>
       <c r="B46" s="7" t="n">
         <v>2</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>27593</v>
+        <v>15767</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>0</v>
+        <v>10916</v>
       </c>
       <c r="F46" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>25124</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K46" s="7" t="n">
+        <v>53858</v>
+      </c>
+      <c r="L46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q46" s="7" t="n">
+        <v>21121</v>
+      </c>
+      <c r="R46" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G46" s="7" t="n">
-        <v>9471</v>
-      </c>
-      <c r="H46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>49939</v>
-      </c>
-      <c r="L46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" s="7" t="n">
-        <v>0</v>
+        <v>46006</v>
       </c>
       <c r="T46" s="5" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="U46" s="5" t="n">
-        <v>87003</v>
+        <v>172792</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>fast_gluc_bld</t>
+          <t>fruit_serving</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>65854</v>
+        <v>175886</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>6434</v>
+        <v>40644</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>7205</v>
+        <v>5690</v>
       </c>
       <c r="H47" s="7" t="n">
         <v>0</v>
@@ -3680,10 +3680,10 @@
         <v>0</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>83472</v>
+        <v>375548</v>
       </c>
       <c r="L47" s="7" t="n">
         <v>0</v>
@@ -3692,53 +3692,53 @@
         <v>0</v>
       </c>
       <c r="N47" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O47" s="7" t="n">
-        <v>17868</v>
+        <v>0</v>
       </c>
       <c r="P47" s="7" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="Q47" s="7" t="n">
-        <v>68476</v>
+        <v>8534</v>
       </c>
       <c r="R47" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S47" s="7" t="n">
-        <v>0</v>
+        <v>1018181</v>
       </c>
       <c r="T47" s="5" t="n">
-        <v>59</v>
+        <v>168</v>
       </c>
       <c r="U47" s="5" t="n">
-        <v>249309</v>
+        <v>1624483</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>fasting_blood_gluc</t>
+          <t>glucose_bld</t>
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>0</v>
+        <v>211779</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>0</v>
+        <v>6763</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>0</v>
+        <v>25155</v>
       </c>
       <c r="H48" s="7" t="n">
         <v>0</v>
@@ -3747,65 +3747,65 @@
         <v>0</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>0</v>
+        <v>292594</v>
       </c>
       <c r="L48" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M48" s="7" t="n">
-        <v>23653</v>
+        <v>0</v>
       </c>
       <c r="N48" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O48" s="7" t="n">
-        <v>0</v>
+        <v>10187</v>
       </c>
       <c r="P48" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="7" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="R48" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S48" s="7" t="n">
-        <v>0</v>
+        <v>46598</v>
       </c>
       <c r="T48" s="5" t="n">
-        <v>2</v>
+        <v>139</v>
       </c>
       <c r="U48" s="5" t="n">
-        <v>23653</v>
+        <v>593434</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>ferritin</t>
+          <t>hdl</t>
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>0</v>
+        <v>282573</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>0</v>
+        <v>16570</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0</v>
+        <v>29869</v>
       </c>
       <c r="H49" s="7" t="n">
         <v>0</v>
@@ -3814,199 +3814,199 @@
         <v>0</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0</v>
+        <v>148153</v>
       </c>
       <c r="L49" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>23448</v>
+        <v>23652</v>
       </c>
       <c r="N49" s="7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O49" s="7" t="n">
-        <v>3811</v>
+        <v>32797</v>
       </c>
       <c r="P49" s="7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q49" s="7" t="n">
-        <v>0</v>
+        <v>74205</v>
       </c>
       <c r="R49" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S49" s="7" t="n">
-        <v>0</v>
+        <v>46573</v>
       </c>
       <c r="T49" s="5" t="n">
-        <v>3</v>
+        <v>131</v>
       </c>
       <c r="U49" s="5" t="n">
-        <v>27259</v>
+        <v>654392</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>fibrin</t>
+          <t>hemat</t>
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>15767</v>
+        <v>61658</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>10916</v>
+        <v>3582</v>
       </c>
       <c r="F50" s="7" t="n">
         <v>7</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>25124</v>
+        <v>25115</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>0</v>
+        <v>53674</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>53858</v>
+        <v>154499</v>
       </c>
       <c r="L50" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>0</v>
+        <v>23567</v>
       </c>
       <c r="N50" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" s="7" t="n">
-        <v>0</v>
+        <v>3746</v>
       </c>
       <c r="P50" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q50" s="7" t="n">
-        <v>21121</v>
+        <v>3656</v>
       </c>
       <c r="R50" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S50" s="7" t="n">
-        <v>46006</v>
+        <v>629273</v>
       </c>
       <c r="T50" s="5" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="U50" s="5" t="n">
-        <v>172792</v>
+        <v>958770</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>fruit_serving</t>
+          <t>hemo</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>64879</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>3582</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G51" s="7" t="n">
+        <v>25115</v>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I51" s="7" t="n">
+        <v>53674</v>
+      </c>
+      <c r="J51" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="C51" s="7" t="n">
-        <v>175886</v>
-      </c>
-      <c r="D51" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="E51" s="7" t="n">
-        <v>40644</v>
-      </c>
-      <c r="F51" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G51" s="7" t="n">
-        <v>5690</v>
-      </c>
-      <c r="H51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="7" t="n">
-        <v>130</v>
-      </c>
       <c r="K51" s="7" t="n">
-        <v>375548</v>
+        <v>102103</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>0</v>
+        <v>23567</v>
       </c>
       <c r="N51" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" s="7" t="n">
-        <v>0</v>
+        <v>3746</v>
       </c>
       <c r="P51" s="7" t="n">
         <v>2</v>
       </c>
       <c r="Q51" s="7" t="n">
-        <v>8534</v>
+        <v>3655</v>
       </c>
       <c r="R51" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S51" s="7" t="n">
-        <v>1018181</v>
+        <v>629314</v>
       </c>
       <c r="T51" s="5" t="n">
-        <v>168</v>
+        <v>46</v>
       </c>
       <c r="U51" s="5" t="n">
-        <v>1624483</v>
+        <v>909635</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>glucose_bld</t>
+          <t>hemo_a1c</t>
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>211779</v>
+        <v>8841</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>6763</v>
+        <v>0</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>25155</v>
+        <v>0</v>
       </c>
       <c r="H52" s="7" t="n">
         <v>0</v>
@@ -4015,65 +4015,65 @@
         <v>0</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>292594</v>
+        <v>55340</v>
       </c>
       <c r="L52" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" s="7" t="n">
-        <v>0</v>
+        <v>23612</v>
       </c>
       <c r="N52" s="7" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O52" s="7" t="n">
-        <v>10187</v>
+        <v>28547</v>
       </c>
       <c r="P52" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q52" s="7" t="n">
-        <v>358</v>
+        <v>20878</v>
       </c>
       <c r="R52" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S52" s="7" t="n">
-        <v>46598</v>
+        <v>0</v>
       </c>
       <c r="T52" s="5" t="n">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="U52" s="5" t="n">
-        <v>593434</v>
+        <v>137218</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>hdl</t>
+          <t>hip_circ</t>
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>282573</v>
+        <v>54020</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>16570</v>
+        <v>33281</v>
       </c>
       <c r="F53" s="7" t="n">
         <v>8</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>29869</v>
+        <v>30339</v>
       </c>
       <c r="H53" s="7" t="n">
         <v>0</v>
@@ -4082,187 +4082,187 @@
         <v>0</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>148153</v>
+        <v>126492</v>
       </c>
       <c r="L53" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M53" s="7" t="n">
-        <v>23652</v>
+        <v>23627</v>
       </c>
       <c r="N53" s="7" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O53" s="7" t="n">
-        <v>32797</v>
+        <v>17671</v>
       </c>
       <c r="P53" s="7" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="Q53" s="7" t="n">
-        <v>74205</v>
+        <v>56541</v>
       </c>
       <c r="R53" s="7" t="n">
         <v>3</v>
       </c>
       <c r="S53" s="7" t="n">
-        <v>46573</v>
+        <v>1610762</v>
       </c>
       <c r="T53" s="5" t="n">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="U53" s="5" t="n">
-        <v>654392</v>
+        <v>1952733</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>hemat</t>
+          <t>hrtrt</t>
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>61658</v>
+        <v>439669</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>3582</v>
+        <v>60109</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>25115</v>
+        <v>252223</v>
       </c>
       <c r="H54" s="7" t="n">
         <v>3</v>
       </c>
       <c r="I54" s="7" t="n">
-        <v>53674</v>
+        <v>64245</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>154499</v>
+        <v>185296</v>
       </c>
       <c r="L54" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M54" s="7" t="n">
-        <v>23567</v>
+        <v>35266</v>
       </c>
       <c r="N54" s="7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O54" s="7" t="n">
-        <v>3746</v>
+        <v>35238</v>
       </c>
       <c r="P54" s="7" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="Q54" s="7" t="n">
-        <v>3656</v>
+        <v>154242</v>
       </c>
       <c r="R54" s="7" t="n">
         <v>4</v>
       </c>
       <c r="S54" s="7" t="n">
-        <v>629273</v>
+        <v>506519</v>
       </c>
       <c r="T54" s="5" t="n">
-        <v>67</v>
+        <v>291</v>
       </c>
       <c r="U54" s="5" t="n">
-        <v>958770</v>
+        <v>1732807</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>hemo</t>
+          <t>icam</t>
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>64879</v>
+        <v>0</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>1</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>3582</v>
+        <v>2669</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>25115</v>
+        <v>7663</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I55" s="7" t="n">
-        <v>53674</v>
+        <v>0</v>
       </c>
       <c r="J55" s="7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>102103</v>
+        <v>0</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>23567</v>
+        <v>0</v>
       </c>
       <c r="N55" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" s="7" t="n">
-        <v>3746</v>
+        <v>0</v>
       </c>
       <c r="P55" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q55" s="7" t="n">
-        <v>3655</v>
+        <v>15379</v>
       </c>
       <c r="R55" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S55" s="7" t="n">
-        <v>629314</v>
+        <v>0</v>
       </c>
       <c r="T55" s="5" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="U55" s="5" t="n">
-        <v>909635</v>
+        <v>25711</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>hemo_a1c</t>
+          <t>il10</t>
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>8841</v>
+        <v>0</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>0</v>
@@ -4283,28 +4283,28 @@
         <v>0</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>55340</v>
+        <v>0</v>
       </c>
       <c r="L56" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" s="7" t="n">
-        <v>23612</v>
+        <v>0</v>
       </c>
       <c r="N56" s="7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O56" s="7" t="n">
-        <v>28547</v>
+        <v>0</v>
       </c>
       <c r="P56" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q56" s="7" t="n">
-        <v>20878</v>
+        <v>943</v>
       </c>
       <c r="R56" s="7" t="n">
         <v>0</v>
@@ -4313,35 +4313,35 @@
         <v>0</v>
       </c>
       <c r="T56" s="5" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="U56" s="5" t="n">
-        <v>137218</v>
+        <v>943</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>hip_circ</t>
+          <t>il18</t>
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>54020</v>
+        <v>0</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>33281</v>
+        <v>0</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>30339</v>
+        <v>0</v>
       </c>
       <c r="H57" s="7" t="n">
         <v>0</v>
@@ -4350,46 +4350,46 @@
         <v>0</v>
       </c>
       <c r="J57" s="7" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>126492</v>
+        <v>38307</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M57" s="7" t="n">
-        <v>23627</v>
+        <v>0</v>
       </c>
       <c r="N57" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O57" s="7" t="n">
-        <v>17671</v>
+        <v>0</v>
       </c>
       <c r="P57" s="7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="7" t="n">
-        <v>56541</v>
+        <v>0</v>
       </c>
       <c r="R57" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S57" s="7" t="n">
-        <v>1610762</v>
+        <v>0</v>
       </c>
       <c r="T57" s="5" t="n">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="U57" s="5" t="n">
-        <v>1952733</v>
+        <v>38307</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>hrt_rt</t>
+          <t>il6</t>
         </is>
       </c>
       <c r="B58" s="7" t="n">
@@ -4399,22 +4399,22 @@
         <v>0</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>0</v>
+        <v>689</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>0</v>
+        <v>10594</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I58" s="7" t="n">
-        <v>64245</v>
+        <v>0</v>
       </c>
       <c r="J58" s="7" t="n">
         <v>0</v>
@@ -4435,10 +4435,10 @@
         <v>0</v>
       </c>
       <c r="P58" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q58" s="7" t="n">
-        <v>0</v>
+        <v>17277</v>
       </c>
       <c r="R58" s="7" t="n">
         <v>0</v>
@@ -4447,35 +4447,35 @@
         <v>0</v>
       </c>
       <c r="T58" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U58" s="5" t="n">
-        <v>64245</v>
+        <v>28560</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>hrtrt</t>
+          <t>insulin_blood</t>
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>439669</v>
+        <v>56942</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>60109</v>
+        <v>9647</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>252223</v>
+        <v>25071</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
@@ -4484,46 +4484,46 @@
         <v>0</v>
       </c>
       <c r="J59" s="7" t="n">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>185296</v>
+        <v>74472</v>
       </c>
       <c r="L59" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M59" s="7" t="n">
+        <v>23618</v>
+      </c>
+      <c r="N59" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="M59" s="7" t="n">
-        <v>35266</v>
-      </c>
-      <c r="N59" s="7" t="n">
-        <v>11</v>
-      </c>
       <c r="O59" s="7" t="n">
-        <v>35238</v>
+        <v>6587</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="Q59" s="7" t="n">
-        <v>154242</v>
+        <v>25329</v>
       </c>
       <c r="R59" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S59" s="7" t="n">
-        <v>506519</v>
+        <v>43342</v>
       </c>
       <c r="T59" s="5" t="n">
-        <v>288</v>
+        <v>41</v>
       </c>
       <c r="U59" s="5" t="n">
-        <v>1668562</v>
+        <v>265008</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>icam</t>
+          <t>isoprostane_8_epi_pgf2a</t>
         </is>
       </c>
       <c r="B60" s="7" t="n">
@@ -4536,13 +4536,13 @@
         <v>1</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>2669</v>
+        <v>2720</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>7663</v>
+        <v>0</v>
       </c>
       <c r="H60" s="7" t="n">
         <v>0</v>
@@ -4569,10 +4569,10 @@
         <v>0</v>
       </c>
       <c r="P60" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q60" s="7" t="n">
-        <v>15379</v>
+        <v>6805</v>
       </c>
       <c r="R60" s="7" t="n">
         <v>0</v>
@@ -4581,16 +4581,16 @@
         <v>0</v>
       </c>
       <c r="T60" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U60" s="5" t="n">
-        <v>25711</v>
+        <v>9525</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>il10</t>
+          <t>lactate</t>
         </is>
       </c>
       <c r="B61" s="7" t="n">
@@ -4618,10 +4618,10 @@
         <v>0</v>
       </c>
       <c r="J61" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>0</v>
+        <v>26148</v>
       </c>
       <c r="L61" s="7" t="n">
         <v>0</v>
@@ -4636,10 +4636,10 @@
         <v>0</v>
       </c>
       <c r="P61" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="7" t="n">
-        <v>943</v>
+        <v>0</v>
       </c>
       <c r="R61" s="7" t="n">
         <v>0</v>
@@ -4648,16 +4648,16 @@
         <v>0</v>
       </c>
       <c r="T61" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U61" s="5" t="n">
-        <v>943</v>
+        <v>26148</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>il18</t>
+          <t>lactate_dehyd</t>
         </is>
       </c>
       <c r="B62" s="7" t="n">
@@ -4685,10 +4685,10 @@
         <v>0</v>
       </c>
       <c r="J62" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K62" s="7" t="n">
-        <v>38307</v>
+        <v>3530</v>
       </c>
       <c r="L62" s="7" t="n">
         <v>0</v>
@@ -4715,35 +4715,35 @@
         <v>0</v>
       </c>
       <c r="T62" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U62" s="5" t="n">
-        <v>38307</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>il6</t>
+          <t>ldl</t>
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>0</v>
+        <v>173272</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>689</v>
+        <v>16477</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>10594</v>
+        <v>25015</v>
       </c>
       <c r="H63" s="7" t="n">
         <v>0</v>
@@ -4752,113 +4752,113 @@
         <v>0</v>
       </c>
       <c r="J63" s="7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>0</v>
+        <v>123639</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M63" s="7" t="n">
-        <v>0</v>
+        <v>23409</v>
       </c>
       <c r="N63" s="7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O63" s="7" t="n">
-        <v>0</v>
+        <v>43886</v>
       </c>
       <c r="P63" s="7" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="Q63" s="7" t="n">
-        <v>17277</v>
+        <v>68027</v>
       </c>
       <c r="R63" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S63" s="7" t="n">
-        <v>0</v>
+        <v>46331</v>
       </c>
       <c r="T63" s="5" t="n">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="U63" s="5" t="n">
-        <v>28560</v>
+        <v>520056</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>insulin_blood</t>
+          <t>lppla2_act</t>
         </is>
       </c>
       <c r="B64" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>56942</v>
+        <v>0</v>
       </c>
       <c r="D64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>10910</v>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="7" t="n">
+        <v>5122</v>
+      </c>
+      <c r="R64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E64" s="7" t="n">
-        <v>9647</v>
-      </c>
-      <c r="F64" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G64" s="7" t="n">
-        <v>25071</v>
-      </c>
-      <c r="H64" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M64" s="7" t="n">
-        <v>23618</v>
-      </c>
-      <c r="N64" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="O64" s="7" t="n">
-        <v>6587</v>
-      </c>
-      <c r="P64" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q64" s="7" t="n">
-        <v>25329</v>
-      </c>
-      <c r="R64" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="S64" s="7" t="n">
-        <v>43342</v>
-      </c>
-      <c r="T64" s="5" t="n">
-        <v>30</v>
-      </c>
       <c r="U64" s="5" t="n">
-        <v>190536</v>
+        <v>16032</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>insulin_in_blood</t>
+          <t>lppla2_mass</t>
         </is>
       </c>
       <c r="B65" s="7" t="n">
@@ -4874,10 +4874,10 @@
         <v>0</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>0</v>
+        <v>10923</v>
       </c>
       <c r="H65" s="7" t="n">
         <v>0</v>
@@ -4886,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="J65" s="7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>74472</v>
+        <v>0</v>
       </c>
       <c r="L65" s="7" t="n">
         <v>0</v>
@@ -4904,10 +4904,10 @@
         <v>0</v>
       </c>
       <c r="P65" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" s="7" t="n">
-        <v>0</v>
+        <v>5042</v>
       </c>
       <c r="R65" s="7" t="n">
         <v>0</v>
@@ -4916,65 +4916,65 @@
         <v>0</v>
       </c>
       <c r="T65" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="U65" s="5" t="n">
-        <v>74472</v>
+        <v>15965</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>isoprostane_8_epi_pgf2a</t>
+          <t>lympho_ct</t>
         </is>
       </c>
       <c r="B66" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>0</v>
+        <v>5706</v>
       </c>
       <c r="D66" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>3968</v>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>53590</v>
+      </c>
+      <c r="J66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M66" s="7" t="n">
+        <v>22908</v>
+      </c>
+      <c r="N66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E66" s="7" t="n">
-        <v>2720</v>
-      </c>
-      <c r="F66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="Q66" s="7" t="n">
-        <v>6805</v>
+        <v>2338</v>
       </c>
       <c r="R66" s="7" t="n">
         <v>0</v>
@@ -4983,23 +4983,23 @@
         <v>0</v>
       </c>
       <c r="T66" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U66" s="5" t="n">
-        <v>9525</v>
+        <v>88510</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>lactate</t>
+          <t>lympho_pct</t>
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>0</v>
+        <v>24362</v>
       </c>
       <c r="D67" s="7" t="n">
         <v>0</v>
@@ -5020,22 +5020,22 @@
         <v>0</v>
       </c>
       <c r="J67" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>26148</v>
+        <v>12638</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M67" s="7" t="n">
-        <v>0</v>
+        <v>22908</v>
       </c>
       <c r="N67" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" s="7" t="n">
-        <v>0</v>
+        <v>3362</v>
       </c>
       <c r="P67" s="7" t="n">
         <v>0</v>
@@ -5050,29 +5050,29 @@
         <v>0</v>
       </c>
       <c r="T67" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U67" s="5" t="n">
-        <v>26148</v>
+        <v>63270</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>lactate_dehyd</t>
+          <t>mch</t>
         </is>
       </c>
       <c r="B68" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>0</v>
+        <v>12069</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>0</v>
+        <v>7165</v>
       </c>
       <c r="F68" s="7" t="n">
         <v>0</v>
@@ -5081,34 +5081,34 @@
         <v>0</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I68" s="7" t="n">
-        <v>0</v>
+        <v>53674</v>
       </c>
       <c r="J68" s="7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>3530</v>
+        <v>54003</v>
       </c>
       <c r="L68" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M68" s="7" t="n">
-        <v>0</v>
+        <v>23567</v>
       </c>
       <c r="N68" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" s="7" t="n">
-        <v>0</v>
+        <v>3376</v>
       </c>
       <c r="P68" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q68" s="7" t="n">
-        <v>0</v>
+        <v>2756</v>
       </c>
       <c r="R68" s="7" t="n">
         <v>0</v>
@@ -5117,90 +5117,90 @@
         <v>0</v>
       </c>
       <c r="T68" s="5" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="U68" s="5" t="n">
-        <v>3530</v>
+        <v>156610</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>ldl</t>
+          <t>mchc</t>
         </is>
       </c>
       <c r="B69" s="7" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>173272</v>
+        <v>8408</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>16477</v>
+        <v>0</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>25015</v>
+        <v>0</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>0</v>
+        <v>53674</v>
       </c>
       <c r="J69" s="7" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>123639</v>
+        <v>39615</v>
       </c>
       <c r="L69" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M69" s="7" t="n">
-        <v>23409</v>
+        <v>23567</v>
       </c>
       <c r="N69" s="7" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O69" s="7" t="n">
-        <v>43886</v>
+        <v>3377</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="Q69" s="7" t="n">
-        <v>68027</v>
+        <v>2756</v>
       </c>
       <c r="R69" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S69" s="7" t="n">
-        <v>46331</v>
+        <v>0</v>
       </c>
       <c r="T69" s="5" t="n">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="U69" s="5" t="n">
-        <v>520056</v>
+        <v>131397</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>lppla2_act</t>
+          <t>mcv</t>
         </is>
       </c>
       <c r="B70" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>0</v>
+        <v>28238</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>0</v>
@@ -5209,40 +5209,40 @@
         <v>0</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>10910</v>
+        <v>0</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I70" s="7" t="n">
-        <v>0</v>
+        <v>53674</v>
       </c>
       <c r="J70" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>0</v>
+        <v>39615</v>
       </c>
       <c r="L70" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" s="7" t="n">
-        <v>0</v>
+        <v>23567</v>
       </c>
       <c r="N70" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" s="7" t="n">
-        <v>0</v>
+        <v>3377</v>
       </c>
       <c r="P70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="Q70" s="7" t="n">
-        <v>5122</v>
+        <v>2756</v>
       </c>
       <c r="R70" s="7" t="n">
         <v>0</v>
@@ -5251,16 +5251,16 @@
         <v>0</v>
       </c>
       <c r="T70" s="5" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="U70" s="5" t="n">
-        <v>16032</v>
+        <v>151227</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>lppla2_mass</t>
+          <t>mean_art_press</t>
         </is>
       </c>
       <c r="B71" s="7" t="n">
@@ -5276,10 +5276,10 @@
         <v>0</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>10923</v>
+        <v>0</v>
       </c>
       <c r="H71" s="7" t="n">
         <v>0</v>
@@ -5288,10 +5288,10 @@
         <v>0</v>
       </c>
       <c r="J71" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>0</v>
+        <v>50002</v>
       </c>
       <c r="L71" s="7" t="n">
         <v>0</v>
@@ -5306,10 +5306,10 @@
         <v>0</v>
       </c>
       <c r="P71" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q71" s="7" t="n">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="R71" s="7" t="n">
         <v>0</v>
@@ -5318,29 +5318,29 @@
         <v>0</v>
       </c>
       <c r="T71" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U71" s="5" t="n">
-        <v>15965</v>
+        <v>50002</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>lympho_ct</t>
+          <t>mmp9</t>
         </is>
       </c>
       <c r="B72" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>5706</v>
+        <v>0</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>3968</v>
+        <v>0</v>
       </c>
       <c r="F72" s="7" t="n">
         <v>0</v>
@@ -5361,10 +5361,10 @@
         <v>0</v>
       </c>
       <c r="L72" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" s="7" t="n">
-        <v>22908</v>
+        <v>0</v>
       </c>
       <c r="N72" s="7" t="n">
         <v>0</v>
@@ -5373,10 +5373,10 @@
         <v>0</v>
       </c>
       <c r="P72" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q72" s="7" t="n">
-        <v>2338</v>
+        <v>7393</v>
       </c>
       <c r="R72" s="7" t="n">
         <v>0</v>
@@ -5385,65 +5385,65 @@
         <v>0</v>
       </c>
       <c r="T72" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U72" s="5" t="n">
-        <v>34920</v>
+        <v>7393</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>lympho_pct</t>
+          <t>mn_art_pres</t>
         </is>
       </c>
       <c r="B73" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>24769</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C73" s="7" t="n">
-        <v>24362</v>
-      </c>
-      <c r="D73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K73" s="7" t="n">
-        <v>12638</v>
-      </c>
-      <c r="L73" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M73" s="7" t="n">
-        <v>22908</v>
-      </c>
-      <c r="N73" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O73" s="7" t="n">
-        <v>3362</v>
-      </c>
-      <c r="P73" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="Q73" s="7" t="n">
-        <v>0</v>
+        <v>18383</v>
       </c>
       <c r="R73" s="7" t="n">
         <v>0</v>
@@ -5452,29 +5452,29 @@
         <v>0</v>
       </c>
       <c r="T73" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U73" s="5" t="n">
-        <v>63270</v>
+        <v>43170</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>lymphocyte_ct</t>
+          <t>monocyte_ncnc_bld</t>
         </is>
       </c>
       <c r="B74" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>0</v>
+        <v>5706</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="F74" s="7" t="n">
         <v>0</v>
@@ -5486,19 +5486,19 @@
         <v>3</v>
       </c>
       <c r="I74" s="7" t="n">
-        <v>53590</v>
+        <v>53588</v>
       </c>
       <c r="J74" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K74" s="7" t="n">
-        <v>0</v>
+        <v>32540</v>
       </c>
       <c r="L74" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M74" s="7" t="n">
-        <v>0</v>
+        <v>22913</v>
       </c>
       <c r="N74" s="7" t="n">
         <v>0</v>
@@ -5507,10 +5507,10 @@
         <v>0</v>
       </c>
       <c r="P74" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q74" s="7" t="n">
-        <v>0</v>
+        <v>3231</v>
       </c>
       <c r="R74" s="7" t="n">
         <v>0</v>
@@ -5519,29 +5519,29 @@
         <v>0</v>
       </c>
       <c r="T74" s="5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="U74" s="5" t="n">
-        <v>53590</v>
+        <v>118362</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>mch</t>
+          <t>neutro_pct</t>
         </is>
       </c>
       <c r="B75" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>12069</v>
+        <v>18618</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>7165</v>
+        <v>2407</v>
       </c>
       <c r="F75" s="7" t="n">
         <v>0</v>
@@ -5550,34 +5550,34 @@
         <v>0</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I75" s="7" t="n">
-        <v>53674</v>
+        <v>0</v>
       </c>
       <c r="J75" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>54003</v>
+        <v>0</v>
       </c>
       <c r="L75" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M75" s="7" t="n">
-        <v>23567</v>
+        <v>22908</v>
       </c>
       <c r="N75" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" s="7" t="n">
-        <v>3376</v>
+        <v>0</v>
       </c>
       <c r="P75" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="7" t="n">
-        <v>2756</v>
+        <v>0</v>
       </c>
       <c r="R75" s="7" t="n">
         <v>0</v>
@@ -5586,29 +5586,29 @@
         <v>0</v>
       </c>
       <c r="T75" s="5" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="U75" s="5" t="n">
-        <v>156610</v>
+        <v>43933</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>mchc</t>
+          <t>neutrophil_ct</t>
         </is>
       </c>
       <c r="B76" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>8408</v>
+        <v>0</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="F76" s="7" t="n">
         <v>0</v>
@@ -5620,31 +5620,31 @@
         <v>3</v>
       </c>
       <c r="I76" s="7" t="n">
-        <v>53674</v>
+        <v>53590</v>
       </c>
       <c r="J76" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>39615</v>
+        <v>0</v>
       </c>
       <c r="L76" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M76" s="7" t="n">
-        <v>23567</v>
+        <v>22909</v>
       </c>
       <c r="N76" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" s="7" t="n">
-        <v>3377</v>
+        <v>0</v>
       </c>
       <c r="P76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="Q76" s="7" t="n">
-        <v>2756</v>
+        <v>2338</v>
       </c>
       <c r="R76" s="7" t="n">
         <v>0</v>
@@ -5653,23 +5653,23 @@
         <v>0</v>
       </c>
       <c r="T76" s="5" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="U76" s="5" t="n">
-        <v>131397</v>
+        <v>79161</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>mcv</t>
+          <t>nt_bnp</t>
         </is>
       </c>
       <c r="B77" s="7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>28238</v>
+        <v>47302</v>
       </c>
       <c r="D77" s="7" t="n">
         <v>0</v>
@@ -5684,59 +5684,59 @@
         <v>0</v>
       </c>
       <c r="H77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K77" s="7" t="n">
+        <v>19114</v>
+      </c>
+      <c r="L77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q77" s="7" t="n">
+        <v>10090</v>
+      </c>
+      <c r="R77" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I77" s="7" t="n">
-        <v>53674</v>
-      </c>
-      <c r="J77" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="K77" s="7" t="n">
-        <v>39615</v>
-      </c>
-      <c r="L77" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M77" s="7" t="n">
-        <v>23567</v>
-      </c>
-      <c r="N77" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O77" s="7" t="n">
-        <v>3377</v>
-      </c>
-      <c r="P77" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q77" s="7" t="n">
-        <v>2756</v>
-      </c>
-      <c r="R77" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="S77" s="7" t="n">
-        <v>0</v>
+        <v>1802</v>
       </c>
       <c r="T77" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="U77" s="5" t="n">
-        <v>151227</v>
+        <v>78308</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>mean_art_press</t>
+          <t>pacem_stat</t>
         </is>
       </c>
       <c r="B78" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>0</v>
+        <v>13110</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>0</v>
@@ -5757,16 +5757,16 @@
         <v>0</v>
       </c>
       <c r="J78" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K78" s="7" t="n">
-        <v>50002</v>
+        <v>0</v>
       </c>
       <c r="L78" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" s="7" t="n">
-        <v>0</v>
+        <v>11848</v>
       </c>
       <c r="N78" s="7" t="n">
         <v>0</v>
@@ -5775,10 +5775,10 @@
         <v>0</v>
       </c>
       <c r="P78" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q78" s="7" t="n">
-        <v>0</v>
+        <v>12922</v>
       </c>
       <c r="R78" s="7" t="n">
         <v>0</v>
@@ -5787,132 +5787,132 @@
         <v>0</v>
       </c>
       <c r="T78" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U78" s="5" t="n">
-        <v>50002</v>
+        <v>37880</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>mmp9</t>
+          <t>platelet_ct</t>
         </is>
       </c>
       <c r="B79" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>0</v>
+        <v>37442</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>0</v>
+        <v>3581</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>0</v>
+        <v>25046</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>0</v>
+        <v>53654</v>
       </c>
       <c r="J79" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>0</v>
+        <v>35931</v>
       </c>
       <c r="L79" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M79" s="7" t="n">
-        <v>0</v>
+        <v>23560</v>
       </c>
       <c r="N79" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79" s="7" t="n">
-        <v>0</v>
+        <v>3749</v>
       </c>
       <c r="P79" s="7" t="n">
         <v>2</v>
       </c>
       <c r="Q79" s="7" t="n">
-        <v>7393</v>
+        <v>3644</v>
       </c>
       <c r="R79" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S79" s="7" t="n">
-        <v>0</v>
+        <v>623065</v>
       </c>
       <c r="T79" s="5" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="U79" s="5" t="n">
-        <v>7393</v>
+        <v>809672</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>mn_art_pres</t>
+          <t>pmv</t>
         </is>
       </c>
       <c r="B80" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" s="7" t="n">
+        <v>5707</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K80" s="7" t="n">
+        <v>32540</v>
+      </c>
+      <c r="L80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C80" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="D80" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E80" s="7" t="n">
-        <v>24769</v>
-      </c>
-      <c r="F80" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="O80" s="7" t="n">
-        <v>0</v>
+        <v>3376</v>
       </c>
       <c r="P80" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q80" s="7" t="n">
-        <v>18383</v>
+        <v>0</v>
       </c>
       <c r="R80" s="7" t="n">
         <v>0</v>
@@ -5921,41 +5921,41 @@
         <v>0</v>
       </c>
       <c r="T80" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U80" s="5" t="n">
-        <v>43170</v>
+        <v>41623</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>monocyte_ct</t>
+          <t>potassium</t>
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>0</v>
+        <v>37384</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>0</v>
+        <v>6310</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>0</v>
+        <v>25155</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>53588</v>
+        <v>0</v>
       </c>
       <c r="J81" s="7" t="n">
         <v>0</v>
@@ -5970,16 +5970,16 @@
         <v>0</v>
       </c>
       <c r="N81" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>0</v>
+        <v>3839</v>
       </c>
       <c r="P81" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q81" s="7" t="n">
-        <v>0</v>
+        <v>18964</v>
       </c>
       <c r="R81" s="7" t="n">
         <v>0</v>
@@ -5988,29 +5988,29 @@
         <v>0</v>
       </c>
       <c r="T81" s="5" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="U81" s="5" t="n">
-        <v>53588</v>
+        <v>91652</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>monocyte_ncnc_bld</t>
+          <t>pr_ekg</t>
         </is>
       </c>
       <c r="B82" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>5706</v>
+        <v>59015</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="F82" s="7" t="n">
         <v>0</v>
@@ -6025,46 +6025,46 @@
         <v>0</v>
       </c>
       <c r="J82" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K82" s="7" t="n">
-        <v>32540</v>
+        <v>0</v>
       </c>
       <c r="L82" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M82" s="7" t="n">
-        <v>22913</v>
+        <v>23526</v>
       </c>
       <c r="N82" s="7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O82" s="7" t="n">
-        <v>0</v>
+        <v>78673</v>
       </c>
       <c r="P82" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q82" s="7" t="n">
-        <v>3231</v>
+        <v>22435</v>
       </c>
       <c r="R82" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S82" s="7" t="n">
-        <v>0</v>
+        <v>500439</v>
       </c>
       <c r="T82" s="5" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="U82" s="5" t="n">
-        <v>64774</v>
+        <v>684088</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>neutro_ct</t>
+          <t>pr_qrs_qt</t>
         </is>
       </c>
       <c r="B83" s="7" t="n">
@@ -6074,10 +6074,10 @@
         <v>0</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="F83" s="7" t="n">
         <v>0</v>
@@ -6092,16 +6092,16 @@
         <v>0</v>
       </c>
       <c r="J83" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>0</v>
+        <v>66296</v>
       </c>
       <c r="L83" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>22909</v>
+        <v>0</v>
       </c>
       <c r="N83" s="7" t="n">
         <v>0</v>
@@ -6110,10 +6110,10 @@
         <v>0</v>
       </c>
       <c r="P83" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="7" t="n">
-        <v>2338</v>
+        <v>0</v>
       </c>
       <c r="R83" s="7" t="n">
         <v>0</v>
@@ -6122,29 +6122,29 @@
         <v>0</v>
       </c>
       <c r="T83" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U83" s="5" t="n">
-        <v>25571</v>
+        <v>66296</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>neutro_pct</t>
+          <t>pselectin</t>
         </is>
       </c>
       <c r="B84" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>18618</v>
+        <v>0</v>
       </c>
       <c r="D84" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>2407</v>
+        <v>326</v>
       </c>
       <c r="F84" s="7" t="n">
         <v>0</v>
@@ -6165,16 +6165,16 @@
         <v>0</v>
       </c>
       <c r="L84" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M84" s="7" t="n">
-        <v>22908</v>
+        <v>0</v>
       </c>
       <c r="N84" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O84" s="7" t="n">
-        <v>0</v>
+        <v>8299</v>
       </c>
       <c r="P84" s="7" t="n">
         <v>0</v>
@@ -6192,20 +6192,20 @@
         <v>5</v>
       </c>
       <c r="U84" s="5" t="n">
-        <v>43933</v>
+        <v>8625</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>neutrophil_ct</t>
+          <t>qrs_ekg</t>
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>0</v>
+        <v>274284</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>0</v>
@@ -6214,65 +6214,65 @@
         <v>0</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>0</v>
+        <v>43430</v>
       </c>
       <c r="H85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="K85" s="7" t="n">
+        <v>202581</v>
+      </c>
+      <c r="L85" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M85" s="7" t="n">
+        <v>23558</v>
+      </c>
+      <c r="N85" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="O85" s="7" t="n">
+        <v>65524</v>
+      </c>
+      <c r="P85" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q85" s="7" t="n">
+        <v>22514</v>
+      </c>
+      <c r="R85" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I85" s="7" t="n">
-        <v>53590</v>
-      </c>
-      <c r="J85" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="S85" s="7" t="n">
-        <v>0</v>
+        <v>500439</v>
       </c>
       <c r="T85" s="5" t="n">
-        <v>3</v>
+        <v>139</v>
       </c>
       <c r="U85" s="5" t="n">
-        <v>53590</v>
+        <v>1132330</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>nt_bnp</t>
+          <t>qt_ekg</t>
         </is>
       </c>
       <c r="B86" s="7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>47302</v>
+        <v>61199</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>0</v>
@@ -6293,59 +6293,59 @@
         <v>0</v>
       </c>
       <c r="J86" s="7" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>19114</v>
+        <v>90128</v>
       </c>
       <c r="L86" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M86" s="7" t="n">
-        <v>0</v>
+        <v>35283</v>
       </c>
       <c r="N86" s="7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O86" s="7" t="n">
-        <v>0</v>
+        <v>46378</v>
       </c>
       <c r="P86" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q86" s="7" t="n">
-        <v>10090</v>
+        <v>22514</v>
       </c>
       <c r="R86" s="7" t="n">
         <v>3</v>
       </c>
       <c r="S86" s="7" t="n">
-        <v>1802</v>
+        <v>500439</v>
       </c>
       <c r="T86" s="5" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="U86" s="5" t="n">
-        <v>78308</v>
+        <v>755941</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>pacem_stat</t>
+          <t>rdbld_ct</t>
         </is>
       </c>
       <c r="B87" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>13110</v>
+        <v>14728</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>0</v>
+        <v>3583</v>
       </c>
       <c r="F87" s="7" t="n">
         <v>0</v>
@@ -6354,34 +6354,34 @@
         <v>0</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>0</v>
+        <v>53674</v>
       </c>
       <c r="J87" s="7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>0</v>
+        <v>59154</v>
       </c>
       <c r="L87" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>11848</v>
+        <v>23567</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>0</v>
+        <v>3377</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q87" s="7" t="n">
-        <v>12922</v>
+        <v>3656</v>
       </c>
       <c r="R87" s="7" t="n">
         <v>0</v>
@@ -6390,102 +6390,102 @@
         <v>0</v>
       </c>
       <c r="T87" s="5" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="U87" s="5" t="n">
-        <v>37880</v>
+        <v>161739</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>platelet_ct</t>
+          <t>rdw</t>
         </is>
       </c>
       <c r="B88" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>37442</v>
+        <v>12016</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>3581</v>
+        <v>0</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>25046</v>
+        <v>0</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I88" s="7" t="n">
-        <v>53654</v>
+        <v>0</v>
       </c>
       <c r="J88" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K88" s="7" t="n">
-        <v>35931</v>
+        <v>32543</v>
       </c>
       <c r="L88" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M88" s="7" t="n">
-        <v>23560</v>
+        <v>23566</v>
       </c>
       <c r="N88" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" s="7" t="n">
-        <v>3749</v>
+        <v>0</v>
       </c>
       <c r="P88" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q88" s="7" t="n">
-        <v>3644</v>
+        <v>0</v>
       </c>
       <c r="R88" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S88" s="7" t="n">
-        <v>623065</v>
+        <v>0</v>
       </c>
       <c r="T88" s="5" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="U88" s="5" t="n">
-        <v>809672</v>
+        <v>68125</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>pmv</t>
+          <t>sleep_duration_daily</t>
         </is>
       </c>
       <c r="B89" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>5707</v>
+        <v>5925</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>0</v>
+        <v>3529</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>0</v>
+        <v>13853</v>
       </c>
       <c r="H89" s="7" t="n">
         <v>0</v>
@@ -6494,65 +6494,65 @@
         <v>0</v>
       </c>
       <c r="J89" s="7" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>32540</v>
+        <v>129670</v>
       </c>
       <c r="L89" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M89" s="7" t="n">
-        <v>0</v>
+        <v>23080</v>
       </c>
       <c r="N89" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O89" s="7" t="n">
-        <v>3376</v>
+        <v>6955</v>
       </c>
       <c r="P89" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q89" s="7" t="n">
-        <v>0</v>
+        <v>10941</v>
       </c>
       <c r="R89" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S89" s="7" t="n">
-        <v>0</v>
+        <v>626832</v>
       </c>
       <c r="T89" s="5" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="U89" s="5" t="n">
-        <v>41623</v>
+        <v>820785</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>potassium</t>
+          <t>sodium_blood</t>
         </is>
       </c>
       <c r="B90" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>37384</v>
+        <v>52984</v>
       </c>
       <c r="D90" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>6310</v>
+        <v>0</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>25155</v>
+        <v>0</v>
       </c>
       <c r="H90" s="7" t="n">
         <v>0</v>
@@ -6561,10 +6561,10 @@
         <v>0</v>
       </c>
       <c r="J90" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K90" s="7" t="n">
-        <v>0</v>
+        <v>17171</v>
       </c>
       <c r="L90" s="7" t="n">
         <v>0</v>
@@ -6579,47 +6579,47 @@
         <v>3839</v>
       </c>
       <c r="P90" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q90" s="7" t="n">
-        <v>18964</v>
+        <v>6129</v>
       </c>
       <c r="R90" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S90" s="7" t="n">
-        <v>0</v>
+        <v>5721</v>
       </c>
       <c r="T90" s="5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="U90" s="5" t="n">
-        <v>91652</v>
+        <v>85844</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>pr_ekg</t>
+          <t>sodium_intak</t>
         </is>
       </c>
       <c r="B91" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>28614</v>
+      </c>
+      <c r="D91" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C91" s="7" t="n">
-        <v>59015</v>
-      </c>
-      <c r="D91" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="E91" s="7" t="n">
-        <v>0</v>
+        <v>16962</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>0</v>
+        <v>12180</v>
       </c>
       <c r="H91" s="7" t="n">
         <v>0</v>
@@ -6628,95 +6628,95 @@
         <v>0</v>
       </c>
       <c r="J91" s="7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K91" s="7" t="n">
-        <v>0</v>
+        <v>82860</v>
       </c>
       <c r="L91" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M91" s="7" t="n">
-        <v>23526</v>
+        <v>0</v>
       </c>
       <c r="N91" s="7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O91" s="7" t="n">
-        <v>78673</v>
+        <v>0</v>
       </c>
       <c r="P91" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q91" s="7" t="n">
-        <v>22435</v>
+        <v>4252</v>
       </c>
       <c r="R91" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S91" s="7" t="n">
-        <v>500439</v>
+        <v>338044</v>
       </c>
       <c r="T91" s="5" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="U91" s="5" t="n">
-        <v>684088</v>
+        <v>482912</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>pr_qrs_qt</t>
+          <t>spirometry</t>
         </is>
       </c>
       <c r="B92" s="7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>0</v>
+        <v>226242</v>
       </c>
       <c r="D92" s="7" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>0</v>
+        <v>118442</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>0</v>
+        <v>77987</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I92" s="7" t="n">
-        <v>0</v>
+        <v>264146</v>
       </c>
       <c r="J92" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="K92" s="7" t="n">
+        <v>186708</v>
+      </c>
+      <c r="L92" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="K92" s="7" t="n">
-        <v>66296</v>
-      </c>
-      <c r="L92" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="M92" s="7" t="n">
-        <v>0</v>
+        <v>79778</v>
       </c>
       <c r="N92" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O92" s="7" t="n">
-        <v>0</v>
+        <v>44329</v>
       </c>
       <c r="P92" s="7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q92" s="7" t="n">
-        <v>0</v>
+        <v>28584</v>
       </c>
       <c r="R92" s="7" t="n">
         <v>0</v>
@@ -6725,16 +6725,16 @@
         <v>0</v>
       </c>
       <c r="T92" s="5" t="n">
-        <v>7</v>
+        <v>211</v>
       </c>
       <c r="U92" s="5" t="n">
-        <v>66296</v>
+        <v>1026216</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>pselectin</t>
+          <t>spo2</t>
         </is>
       </c>
       <c r="B93" s="7" t="n">
@@ -6744,40 +6744,40 @@
         <v>0</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>0</v>
+        <v>10480</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>0</v>
+        <v>64224</v>
       </c>
       <c r="J93" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93" s="7" t="n">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="L93" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M93" s="7" t="n">
-        <v>0</v>
+        <v>22347</v>
       </c>
       <c r="N93" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O93" s="7" t="n">
-        <v>8299</v>
+        <v>0</v>
       </c>
       <c r="P93" s="7" t="n">
         <v>0</v>
@@ -6792,23 +6792,23 @@
         <v>0</v>
       </c>
       <c r="T93" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U93" s="5" t="n">
-        <v>8625</v>
+        <v>97766</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>qrs_ekg</t>
+          <t>tnfa</t>
         </is>
       </c>
       <c r="B94" s="7" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>274284</v>
+        <v>0</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>0</v>
@@ -6817,10 +6817,10 @@
         <v>0</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>43430</v>
+        <v>0</v>
       </c>
       <c r="H94" s="7" t="n">
         <v>0</v>
@@ -6829,53 +6829,53 @@
         <v>0</v>
       </c>
       <c r="J94" s="7" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K94" s="7" t="n">
-        <v>202581</v>
+        <v>0</v>
       </c>
       <c r="L94" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M94" s="7" t="n">
-        <v>23558</v>
+        <v>0</v>
       </c>
       <c r="N94" s="7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O94" s="7" t="n">
-        <v>65524</v>
+        <v>0</v>
       </c>
       <c r="P94" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q94" s="7" t="n">
-        <v>22514</v>
+        <v>6524</v>
       </c>
       <c r="R94" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S94" s="7" t="n">
-        <v>500439</v>
+        <v>0</v>
       </c>
       <c r="T94" s="5" t="n">
-        <v>139</v>
+        <v>6</v>
       </c>
       <c r="U94" s="5" t="n">
-        <v>1132330</v>
+        <v>6524</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>qt_ekg</t>
+          <t>tnfa_r1</t>
         </is>
       </c>
       <c r="B95" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>61199</v>
+        <v>0</v>
       </c>
       <c r="D95" s="7" t="n">
         <v>0</v>
@@ -6896,217 +6896,217 @@
         <v>0</v>
       </c>
       <c r="J95" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K95" s="7" t="n">
-        <v>90128</v>
+        <v>0</v>
       </c>
       <c r="L95" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M95" s="7" t="n">
-        <v>35283</v>
+        <v>0</v>
       </c>
       <c r="N95" s="7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O95" s="7" t="n">
-        <v>46378</v>
+        <v>0</v>
       </c>
       <c r="P95" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q95" s="7" t="n">
-        <v>22514</v>
+        <v>9242</v>
       </c>
       <c r="R95" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S95" s="7" t="n">
-        <v>500439</v>
+        <v>0</v>
       </c>
       <c r="T95" s="5" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="U95" s="5" t="n">
-        <v>755941</v>
+        <v>9242</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>rbc</t>
+          <t>tot_chol_bld</t>
         </is>
       </c>
       <c r="B96" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C96" s="7" t="n">
-        <v>0</v>
+        <v>245458</v>
       </c>
       <c r="D96" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E96" s="7" t="n">
-        <v>0</v>
+        <v>6897</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G96" s="7" t="n">
-        <v>0</v>
+        <v>11010</v>
       </c>
       <c r="H96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="K96" s="7" t="n">
+        <v>218271</v>
+      </c>
+      <c r="L96" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M96" s="7" t="n">
+        <v>23653</v>
+      </c>
+      <c r="N96" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="O96" s="7" t="n">
+        <v>31460</v>
+      </c>
+      <c r="P96" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q96" s="7" t="n">
+        <v>68149</v>
+      </c>
+      <c r="R96" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I96" s="7" t="n">
-        <v>53674</v>
-      </c>
-      <c r="J96" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" s="7" t="n">
-        <v>0</v>
+        <v>46610</v>
       </c>
       <c r="T96" s="5" t="n">
-        <v>3</v>
+        <v>131</v>
       </c>
       <c r="U96" s="5" t="n">
-        <v>53674</v>
+        <v>651508</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>rdbld_ct</t>
+          <t>triglyc_bld</t>
         </is>
       </c>
       <c r="B97" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C97" s="7" t="n">
+        <v>167017</v>
+      </c>
+      <c r="D97" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>16569</v>
+      </c>
+      <c r="F97" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G97" s="7" t="n">
+        <v>29264</v>
+      </c>
+      <c r="H97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="K97" s="7" t="n">
+        <v>168009</v>
+      </c>
+      <c r="L97" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M97" s="7" t="n">
+        <v>23653</v>
+      </c>
+      <c r="N97" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="O97" s="7" t="n">
+        <v>32777</v>
+      </c>
+      <c r="P97" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q97" s="7" t="n">
+        <v>67803</v>
+      </c>
+      <c r="R97" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C97" s="7" t="n">
-        <v>14728</v>
-      </c>
-      <c r="D97" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="7" t="n">
-        <v>3583</v>
-      </c>
-      <c r="F97" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="K97" s="7" t="n">
-        <v>59154</v>
-      </c>
-      <c r="L97" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M97" s="7" t="n">
-        <v>23567</v>
-      </c>
-      <c r="N97" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O97" s="7" t="n">
-        <v>3377</v>
-      </c>
-      <c r="P97" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q97" s="7" t="n">
-        <v>3656</v>
-      </c>
-      <c r="R97" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="S97" s="7" t="n">
-        <v>0</v>
+        <v>46610</v>
       </c>
       <c r="T97" s="5" t="n">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="U97" s="5" t="n">
-        <v>108065</v>
+        <v>551702</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>rdw</t>
+          <t>troponin</t>
         </is>
       </c>
       <c r="B98" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C98" s="7" t="n">
+        <v>59241</v>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="F98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C98" s="7" t="n">
-        <v>12016</v>
-      </c>
-      <c r="D98" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="7" t="n">
-        <v>5</v>
-      </c>
       <c r="K98" s="7" t="n">
-        <v>32543</v>
+        <v>14391</v>
       </c>
       <c r="L98" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M98" s="7" t="n">
-        <v>23566</v>
+        <v>0</v>
       </c>
       <c r="N98" s="7" t="n">
         <v>0</v>
@@ -7121,41 +7121,41 @@
         <v>0</v>
       </c>
       <c r="R98" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S98" s="7" t="n">
-        <v>0</v>
+        <v>4604</v>
       </c>
       <c r="T98" s="5" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="U98" s="5" t="n">
-        <v>68125</v>
+        <v>78313</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>sleep_duration_daily</t>
+          <t>vege_serving</t>
         </is>
       </c>
       <c r="B99" s="7" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="C99" s="7" t="n">
-        <v>5925</v>
+        <v>322380</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>3529</v>
+        <v>74514</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>13853</v>
+        <v>771</v>
       </c>
       <c r="H99" s="7" t="n">
         <v>0</v>
@@ -7164,284 +7164,284 @@
         <v>0</v>
       </c>
       <c r="J99" s="7" t="n">
-        <v>31</v>
+        <v>232</v>
       </c>
       <c r="K99" s="7" t="n">
-        <v>129670</v>
+        <v>638568</v>
       </c>
       <c r="L99" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M99" s="7" t="n">
-        <v>23080</v>
+        <v>0</v>
       </c>
       <c r="N99" s="7" t="n">
         <v>2</v>
       </c>
       <c r="O99" s="7" t="n">
-        <v>6955</v>
+        <v>7594</v>
       </c>
       <c r="P99" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q99" s="7" t="n">
-        <v>10941</v>
+        <v>29869</v>
       </c>
       <c r="R99" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S99" s="7" t="n">
-        <v>626832</v>
+        <v>680137</v>
       </c>
       <c r="T99" s="5" t="n">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="U99" s="5" t="n">
-        <v>820785</v>
+        <v>1753833</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>sodium_blood</t>
+          <t>waist_circ</t>
         </is>
       </c>
       <c r="B100" s="7" t="n">
         <v>5</v>
       </c>
       <c r="C100" s="7" t="n">
-        <v>52984</v>
+        <v>54019</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>0</v>
+        <v>30185</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>0</v>
+        <v>43939</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I100" s="7" t="n">
-        <v>0</v>
+        <v>53850</v>
       </c>
       <c r="J100" s="7" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="K100" s="7" t="n">
-        <v>17171</v>
+        <v>175209</v>
       </c>
       <c r="L100" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M100" s="7" t="n">
-        <v>0</v>
+        <v>23633</v>
       </c>
       <c r="N100" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O100" s="7" t="n">
-        <v>3839</v>
+        <v>25409</v>
       </c>
       <c r="P100" s="7" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Q100" s="7" t="n">
-        <v>6129</v>
+        <v>56543</v>
       </c>
       <c r="R100" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S100" s="7" t="n">
-        <v>5721</v>
+        <v>1619039</v>
       </c>
       <c r="T100" s="5" t="n">
-        <v>11</v>
+        <v>112</v>
       </c>
       <c r="U100" s="5" t="n">
-        <v>85844</v>
+        <v>2081826</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>sodium_intak</t>
+          <t>waist_hip</t>
         </is>
       </c>
       <c r="B101" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C101" s="7" t="n">
+        <v>106654</v>
+      </c>
+      <c r="D101" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" s="7" t="n">
+        <v>388</v>
+      </c>
+      <c r="F101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M101" s="7" t="n">
+        <v>23626</v>
+      </c>
+      <c r="N101" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="O101" s="7" t="n">
+        <v>23478</v>
+      </c>
+      <c r="P101" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q101" s="7" t="n">
+        <v>89497</v>
+      </c>
+      <c r="R101" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C101" s="7" t="n">
-        <v>28614</v>
-      </c>
-      <c r="D101" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E101" s="7" t="n">
-        <v>16962</v>
-      </c>
-      <c r="F101" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G101" s="7" t="n">
-        <v>12180</v>
-      </c>
-      <c r="H101" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="K101" s="7" t="n">
-        <v>82860</v>
-      </c>
-      <c r="L101" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q101" s="7" t="n">
-        <v>4252</v>
-      </c>
-      <c r="R101" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="S101" s="7" t="n">
-        <v>338044</v>
+        <v>1610605</v>
       </c>
       <c r="T101" s="5" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="U101" s="5" t="n">
-        <v>482912</v>
+        <v>1854248</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>spirometry</t>
+          <t>whtbld_ct</t>
         </is>
       </c>
       <c r="B102" s="7" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C102" s="7" t="n">
-        <v>226242</v>
+        <v>43076</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>118442</v>
+        <v>3583</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>77987</v>
+        <v>10978</v>
       </c>
       <c r="H102" s="7" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I102" s="7" t="n">
-        <v>264146</v>
+        <v>53674</v>
       </c>
       <c r="J102" s="7" t="n">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="K102" s="7" t="n">
-        <v>186708</v>
+        <v>60160</v>
       </c>
       <c r="L102" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M102" s="7" t="n">
-        <v>79778</v>
+        <v>22911</v>
       </c>
       <c r="N102" s="7" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O102" s="7" t="n">
-        <v>44329</v>
+        <v>3377</v>
       </c>
       <c r="P102" s="7" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="Q102" s="7" t="n">
-        <v>28584</v>
+        <v>3656</v>
       </c>
       <c r="R102" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S102" s="7" t="n">
-        <v>0</v>
+        <v>623680</v>
       </c>
       <c r="T102" s="5" t="n">
-        <v>211</v>
+        <v>32</v>
       </c>
       <c r="U102" s="5" t="n">
-        <v>1026216</v>
+        <v>825095</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>spo2</t>
+          <t>willeb_fac</t>
         </is>
       </c>
       <c r="B103" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C103" s="7" t="n">
-        <v>0</v>
+        <v>14801</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>0</v>
+        <v>6928</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>10480</v>
+        <v>0</v>
       </c>
       <c r="H103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I103" s="7" t="n">
-        <v>64224</v>
-      </c>
-      <c r="J103" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="K103" s="7" t="n">
-        <v>715</v>
+        <v>12072</v>
       </c>
       <c r="L103" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M103" s="7" t="n">
-        <v>22347</v>
+        <v>0</v>
       </c>
       <c r="N103" s="7" t="n">
         <v>0</v>
@@ -7450,10 +7450,10 @@
         <v>0</v>
       </c>
       <c r="P103" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q103" s="7" t="n">
-        <v>0</v>
+        <v>7391</v>
       </c>
       <c r="R103" s="7" t="n">
         <v>0</v>
@@ -7462,746 +7462,76 @@
         <v>0</v>
       </c>
       <c r="T103" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U103" s="5" t="n">
-        <v>97766</v>
+        <v>41192</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>tnfa</t>
-        </is>
-      </c>
-      <c r="B104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q104" s="7" t="n">
-        <v>6524</v>
-      </c>
-      <c r="R104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="U104" s="5" t="n">
-        <v>6524</v>
-      </c>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>tnfa_r1</t>
-        </is>
-      </c>
-      <c r="B105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q105" s="7" t="n">
-        <v>9242</v>
-      </c>
-      <c r="R105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U105" s="5" t="n">
-        <v>9242</v>
-      </c>
-    </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>tot_chol_bld</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="C106" s="7" t="n">
-        <v>245458</v>
-      </c>
-      <c r="D106" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E106" s="7" t="n">
-        <v>6897</v>
-      </c>
-      <c r="F106" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G106" s="7" t="n">
-        <v>11010</v>
-      </c>
-      <c r="H106" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="K106" s="7" t="n">
-        <v>218271</v>
-      </c>
-      <c r="L106" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M106" s="7" t="n">
-        <v>23653</v>
-      </c>
-      <c r="N106" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="O106" s="7" t="n">
-        <v>31460</v>
-      </c>
-      <c r="P106" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q106" s="7" t="n">
-        <v>68149</v>
-      </c>
-      <c r="R106" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="S106" s="7" t="n">
-        <v>46610</v>
-      </c>
-      <c r="T106" s="5" t="n">
-        <v>131</v>
-      </c>
-      <c r="U106" s="5" t="n">
-        <v>651508</v>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>triglyc_bld</t>
-        </is>
-      </c>
-      <c r="B107" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="C107" s="7" t="n">
-        <v>167017</v>
-      </c>
-      <c r="D107" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E107" s="7" t="n">
-        <v>16569</v>
-      </c>
-      <c r="F107" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G107" s="7" t="n">
-        <v>29264</v>
-      </c>
-      <c r="H107" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="K107" s="7" t="n">
-        <v>168009</v>
-      </c>
-      <c r="L107" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M107" s="7" t="n">
-        <v>23653</v>
-      </c>
-      <c r="N107" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="O107" s="7" t="n">
-        <v>32777</v>
-      </c>
-      <c r="P107" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q107" s="7" t="n">
-        <v>67803</v>
-      </c>
-      <c r="R107" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="S107" s="7" t="n">
-        <v>46610</v>
-      </c>
-      <c r="T107" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="U107" s="5" t="n">
-        <v>551702</v>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>troponin</t>
-        </is>
-      </c>
-      <c r="B108" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="C108" s="7" t="n">
-        <v>59241</v>
-      </c>
-      <c r="D108" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E108" s="7" t="n">
-        <v>77</v>
-      </c>
-      <c r="F108" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K108" s="7" t="n">
-        <v>14391</v>
-      </c>
-      <c r="L108" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S108" s="7" t="n">
-        <v>4604</v>
-      </c>
-      <c r="T108" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="U108" s="5" t="n">
-        <v>78313</v>
-      </c>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>vege_serving</t>
-        </is>
-      </c>
-      <c r="B109" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="C109" s="7" t="n">
-        <v>322380</v>
-      </c>
-      <c r="D109" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="E109" s="7" t="n">
-        <v>74514</v>
-      </c>
-      <c r="F109" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G109" s="7" t="n">
-        <v>771</v>
-      </c>
-      <c r="H109" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="7" t="n">
-        <v>232</v>
-      </c>
-      <c r="K109" s="7" t="n">
-        <v>638568</v>
-      </c>
-      <c r="L109" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N109" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O109" s="7" t="n">
-        <v>7594</v>
-      </c>
-      <c r="P109" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q109" s="7" t="n">
-        <v>29869</v>
-      </c>
-      <c r="R109" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S109" s="7" t="n">
-        <v>680137</v>
-      </c>
-      <c r="T109" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="U109" s="5" t="n">
-        <v>1753833</v>
-      </c>
-    </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>waist_circ</t>
-        </is>
-      </c>
-      <c r="B110" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C110" s="7" t="n">
-        <v>54019</v>
-      </c>
-      <c r="D110" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="E110" s="7" t="n">
-        <v>30185</v>
-      </c>
-      <c r="F110" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="G110" s="7" t="n">
-        <v>43939</v>
-      </c>
-      <c r="H110" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I110" s="7" t="n">
-        <v>53850</v>
-      </c>
-      <c r="J110" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="K110" s="7" t="n">
-        <v>175209</v>
-      </c>
-      <c r="L110" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M110" s="7" t="n">
-        <v>23633</v>
-      </c>
-      <c r="N110" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="O110" s="7" t="n">
-        <v>25409</v>
-      </c>
-      <c r="P110" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q110" s="7" t="n">
-        <v>56543</v>
-      </c>
-      <c r="R110" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="S110" s="7" t="n">
-        <v>1619039</v>
-      </c>
-      <c r="T110" s="5" t="n">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="n">
+        <v>1178</v>
+      </c>
+      <c r="C104" s="9" t="n">
+        <v>11553653</v>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>565</v>
+      </c>
+      <c r="E104" s="9" t="n">
+        <v>1035671</v>
+      </c>
+      <c r="F104" s="9" t="n">
+        <v>1349</v>
+      </c>
+      <c r="G104" s="9" t="n">
+        <v>4161858</v>
+      </c>
+      <c r="H104" s="9" t="n">
         <v>112</v>
       </c>
-      <c r="U110" s="5" t="n">
-        <v>2081826</v>
-      </c>
-    </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>waist_hip</t>
-        </is>
-      </c>
-      <c r="B111" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="C111" s="7" t="n">
-        <v>106654</v>
-      </c>
-      <c r="D111" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E111" s="7" t="n">
-        <v>388</v>
-      </c>
-      <c r="F111" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M111" s="7" t="n">
-        <v>23626</v>
-      </c>
-      <c r="N111" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="O111" s="7" t="n">
-        <v>23478</v>
-      </c>
-      <c r="P111" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q111" s="7" t="n">
-        <v>89497</v>
-      </c>
-      <c r="R111" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="S111" s="7" t="n">
-        <v>1610605</v>
-      </c>
-      <c r="T111" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="U111" s="5" t="n">
-        <v>1854248</v>
-      </c>
-    </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>whtbld_ct</t>
-        </is>
-      </c>
-      <c r="B112" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C112" s="7" t="n">
-        <v>43076</v>
-      </c>
-      <c r="D112" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E112" s="7" t="n">
-        <v>3583</v>
-      </c>
-      <c r="F112" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G112" s="7" t="n">
-        <v>10978</v>
-      </c>
-      <c r="H112" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I112" s="7" t="n">
-        <v>53674</v>
-      </c>
-      <c r="J112" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="K112" s="7" t="n">
-        <v>60160</v>
-      </c>
-      <c r="L112" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M112" s="7" t="n">
-        <v>22911</v>
-      </c>
-      <c r="N112" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O112" s="7" t="n">
-        <v>3377</v>
-      </c>
-      <c r="P112" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q112" s="7" t="n">
-        <v>3656</v>
-      </c>
-      <c r="R112" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="S112" s="7" t="n">
-        <v>623680</v>
-      </c>
-      <c r="T112" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="U112" s="5" t="n">
-        <v>825095</v>
-      </c>
-    </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>willeb_fac</t>
-        </is>
-      </c>
-      <c r="B113" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C113" s="7" t="n">
-        <v>14801</v>
-      </c>
-      <c r="D113" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E113" s="7" t="n">
-        <v>6928</v>
-      </c>
-      <c r="F113" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K113" s="7" t="n">
-        <v>12072</v>
-      </c>
-      <c r="L113" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N113" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q113" s="7" t="n">
-        <v>7391</v>
-      </c>
-      <c r="R113" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T113" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="U113" s="5" t="n">
-        <v>41192</v>
-      </c>
-    </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="A114" s="8" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B114" s="9" t="n">
-        <v>1178</v>
-      </c>
-      <c r="C114" s="9" t="n">
-        <v>11553653</v>
-      </c>
-      <c r="D114" s="9" t="n">
-        <v>565</v>
-      </c>
-      <c r="E114" s="9" t="n">
-        <v>1035671</v>
-      </c>
-      <c r="F114" s="9" t="n">
-        <v>1349</v>
-      </c>
-      <c r="G114" s="9" t="n">
-        <v>4161858</v>
-      </c>
-      <c r="H114" s="9" t="n">
-        <v>112</v>
-      </c>
-      <c r="I114" s="9" t="n">
+      <c r="I104" s="9" t="n">
         <v>2122662</v>
       </c>
-      <c r="J114" s="9" t="n">
+      <c r="J104" s="9" t="n">
         <v>3087</v>
       </c>
-      <c r="K114" s="9" t="n">
+      <c r="K104" s="9" t="n">
         <v>9071383</v>
       </c>
-      <c r="L114" s="9" t="n">
+      <c r="L104" s="9" t="n">
         <v>165</v>
       </c>
-      <c r="M114" s="9" t="n">
+      <c r="M104" s="9" t="n">
         <v>1772032</v>
       </c>
-      <c r="N114" s="9" t="n">
+      <c r="N104" s="9" t="n">
         <v>477</v>
       </c>
-      <c r="O114" s="9" t="n">
+      <c r="O104" s="9" t="n">
         <v>1643015</v>
       </c>
-      <c r="P114" s="9" t="n">
+      <c r="P104" s="9" t="n">
         <v>1196</v>
       </c>
-      <c r="Q114" s="9" t="n">
+      <c r="Q104" s="9" t="n">
         <v>3908574</v>
       </c>
-      <c r="R114" s="9" t="n">
+      <c r="R104" s="9" t="n">
         <v>360</v>
       </c>
-      <c r="S114" s="9" t="n">
+      <c r="S104" s="9" t="n">
         <v>34121402</v>
       </c>
-      <c r="T114" s="9" t="n">
+      <c r="T104" s="9" t="n">
         <v>8489</v>
       </c>
-      <c r="U114" s="9" t="n">
+      <c r="U104" s="9" t="n">
         <v>69390250</v>
       </c>
     </row>

--- a/tables/before_table.xlsx
+++ b/tables/before_table.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U104"/>
+  <dimension ref="A1:U106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3585,160 +3585,160 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>fibrin</t>
+          <t>fev1</t>
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>15767</v>
+        <v>87503</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>10916</v>
+        <v>64098</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>25124</v>
+        <v>31282</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>0</v>
+        <v>82063</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>53858</v>
+        <v>124086</v>
       </c>
       <c r="L46" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>0</v>
+        <v>34509</v>
       </c>
       <c r="N46" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O46" s="7" t="n">
-        <v>0</v>
+        <v>14702</v>
       </c>
       <c r="P46" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q46" s="7" t="n">
-        <v>21121</v>
+        <v>12201</v>
       </c>
       <c r="R46" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S46" s="7" t="n">
-        <v>46006</v>
+        <v>0</v>
       </c>
       <c r="T46" s="5" t="n">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="U46" s="5" t="n">
-        <v>172792</v>
+        <v>450444</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>fruit_serving</t>
+          <t>fev1_fvc</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>175886</v>
+        <v>82611</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>40644</v>
+        <v>0</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>5690</v>
+        <v>9673</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>0</v>
+        <v>82063</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>375548</v>
+        <v>111182</v>
       </c>
       <c r="L47" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M47" s="7" t="n">
-        <v>0</v>
+        <v>34422</v>
       </c>
       <c r="N47" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O47" s="7" t="n">
-        <v>0</v>
+        <v>11044</v>
       </c>
       <c r="P47" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q47" s="7" t="n">
-        <v>8534</v>
+        <v>12550</v>
       </c>
       <c r="R47" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S47" s="7" t="n">
-        <v>1018181</v>
+        <v>0</v>
       </c>
       <c r="T47" s="5" t="n">
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="U47" s="5" t="n">
-        <v>1624483</v>
+        <v>343545</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>glucose_bld</t>
+          <t>fibrin</t>
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>211779</v>
+        <v>15767</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>6763</v>
+        <v>10916</v>
       </c>
       <c r="F48" s="7" t="n">
         <v>7</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>25155</v>
+        <v>25124</v>
       </c>
       <c r="H48" s="7" t="n">
         <v>0</v>
@@ -3747,10 +3747,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>292594</v>
+        <v>53858</v>
       </c>
       <c r="L48" s="7" t="n">
         <v>0</v>
@@ -3759,53 +3759,53 @@
         <v>0</v>
       </c>
       <c r="N48" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O48" s="7" t="n">
-        <v>10187</v>
+        <v>0</v>
       </c>
       <c r="P48" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q48" s="7" t="n">
-        <v>358</v>
+        <v>21121</v>
       </c>
       <c r="R48" s="7" t="n">
         <v>3</v>
       </c>
       <c r="S48" s="7" t="n">
-        <v>46598</v>
+        <v>46006</v>
       </c>
       <c r="T48" s="5" t="n">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="U48" s="5" t="n">
-        <v>593434</v>
+        <v>172792</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>hdl</t>
+          <t>fruit_serving</t>
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>282573</v>
+        <v>175886</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>16570</v>
+        <v>40644</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>29869</v>
+        <v>5690</v>
       </c>
       <c r="H49" s="7" t="n">
         <v>0</v>
@@ -3814,199 +3814,199 @@
         <v>0</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>148153</v>
+        <v>375548</v>
       </c>
       <c r="L49" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>23652</v>
+        <v>0</v>
       </c>
       <c r="N49" s="7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O49" s="7" t="n">
-        <v>32797</v>
+        <v>0</v>
       </c>
       <c r="P49" s="7" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Q49" s="7" t="n">
-        <v>74205</v>
+        <v>8534</v>
       </c>
       <c r="R49" s="7" t="n">
         <v>3</v>
       </c>
       <c r="S49" s="7" t="n">
-        <v>46573</v>
+        <v>1018181</v>
       </c>
       <c r="T49" s="5" t="n">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="U49" s="5" t="n">
-        <v>654392</v>
+        <v>1624483</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>hemat</t>
+          <t>fvc</t>
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>61658</v>
+        <v>73309</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>3582</v>
+        <v>57425</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>25115</v>
+        <v>24859</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>53674</v>
+        <v>82067</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>154499</v>
+        <v>127166</v>
       </c>
       <c r="L50" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>23567</v>
+        <v>34509</v>
       </c>
       <c r="N50" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O50" s="7" t="n">
-        <v>3746</v>
+        <v>14700</v>
       </c>
       <c r="P50" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q50" s="7" t="n">
-        <v>3656</v>
+        <v>12216</v>
       </c>
       <c r="R50" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S50" s="7" t="n">
-        <v>629273</v>
+        <v>0</v>
       </c>
       <c r="T50" s="5" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="U50" s="5" t="n">
-        <v>958770</v>
+        <v>426251</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>hemo</t>
+          <t>glucose_bld</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>64879</v>
+        <v>211779</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>3582</v>
+        <v>6763</v>
       </c>
       <c r="F51" s="7" t="n">
         <v>7</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>25115</v>
+        <v>25155</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>53674</v>
+        <v>0</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>102103</v>
+        <v>292594</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>23567</v>
+        <v>0</v>
       </c>
       <c r="N51" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O51" s="7" t="n">
-        <v>3746</v>
+        <v>10187</v>
       </c>
       <c r="P51" s="7" t="n">
         <v>2</v>
       </c>
       <c r="Q51" s="7" t="n">
-        <v>3655</v>
+        <v>358</v>
       </c>
       <c r="R51" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S51" s="7" t="n">
-        <v>629314</v>
+        <v>46598</v>
       </c>
       <c r="T51" s="5" t="n">
-        <v>46</v>
+        <v>139</v>
       </c>
       <c r="U51" s="5" t="n">
-        <v>909635</v>
+        <v>593434</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>hemo_a1c</t>
+          <t>hdl</t>
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>8841</v>
+        <v>282573</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>0</v>
+        <v>16570</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>0</v>
+        <v>29869</v>
       </c>
       <c r="H52" s="7" t="n">
         <v>0</v>
@@ -4015,199 +4015,199 @@
         <v>0</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>55340</v>
+        <v>148153</v>
       </c>
       <c r="L52" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M52" s="7" t="n">
-        <v>23612</v>
+        <v>23652</v>
       </c>
       <c r="N52" s="7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O52" s="7" t="n">
-        <v>28547</v>
+        <v>32797</v>
       </c>
       <c r="P52" s="7" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="Q52" s="7" t="n">
-        <v>20878</v>
+        <v>74205</v>
       </c>
       <c r="R52" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S52" s="7" t="n">
-        <v>0</v>
+        <v>46573</v>
       </c>
       <c r="T52" s="5" t="n">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="U52" s="5" t="n">
-        <v>137218</v>
+        <v>654392</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>hip_circ</t>
+          <t>hemat</t>
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>54020</v>
+        <v>61658</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>33281</v>
+        <v>3582</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>30339</v>
+        <v>25115</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>0</v>
+        <v>53674</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>126492</v>
+        <v>154499</v>
       </c>
       <c r="L53" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M53" s="7" t="n">
-        <v>23627</v>
+        <v>23567</v>
       </c>
       <c r="N53" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O53" s="7" t="n">
-        <v>17671</v>
+        <v>3746</v>
       </c>
       <c r="P53" s="7" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Q53" s="7" t="n">
-        <v>56541</v>
+        <v>3656</v>
       </c>
       <c r="R53" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S53" s="7" t="n">
-        <v>1610762</v>
+        <v>629273</v>
       </c>
       <c r="T53" s="5" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="U53" s="5" t="n">
-        <v>1952733</v>
+        <v>958770</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>hrtrt</t>
+          <t>hemo</t>
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>439669</v>
+        <v>64879</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>60109</v>
+        <v>3582</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>252223</v>
+        <v>25115</v>
       </c>
       <c r="H54" s="7" t="n">
         <v>3</v>
       </c>
       <c r="I54" s="7" t="n">
-        <v>64245</v>
+        <v>53674</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>185296</v>
+        <v>102103</v>
       </c>
       <c r="L54" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M54" s="7" t="n">
-        <v>35266</v>
+        <v>23567</v>
       </c>
       <c r="N54" s="7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O54" s="7" t="n">
-        <v>35238</v>
+        <v>3746</v>
       </c>
       <c r="P54" s="7" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="Q54" s="7" t="n">
-        <v>154242</v>
+        <v>3655</v>
       </c>
       <c r="R54" s="7" t="n">
         <v>4</v>
       </c>
       <c r="S54" s="7" t="n">
-        <v>506519</v>
+        <v>629314</v>
       </c>
       <c r="T54" s="5" t="n">
-        <v>291</v>
+        <v>46</v>
       </c>
       <c r="U54" s="5" t="n">
-        <v>1732807</v>
+        <v>909635</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>icam</t>
+          <t>hemo_a1c</t>
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>0</v>
+        <v>8841</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>2669</v>
+        <v>0</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>7663</v>
+        <v>0</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>0</v>
@@ -4216,28 +4216,28 @@
         <v>0</v>
       </c>
       <c r="J55" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>0</v>
+        <v>55340</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>0</v>
+        <v>23612</v>
       </c>
       <c r="N55" s="7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O55" s="7" t="n">
-        <v>0</v>
+        <v>28547</v>
       </c>
       <c r="P55" s="7" t="n">
         <v>6</v>
       </c>
       <c r="Q55" s="7" t="n">
-        <v>15379</v>
+        <v>20878</v>
       </c>
       <c r="R55" s="7" t="n">
         <v>0</v>
@@ -4246,35 +4246,35 @@
         <v>0</v>
       </c>
       <c r="T55" s="5" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="U55" s="5" t="n">
-        <v>25711</v>
+        <v>137218</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>il10</t>
+          <t>hip_circ</t>
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>0</v>
+        <v>54020</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>0</v>
+        <v>33281</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>0</v>
+        <v>30339</v>
       </c>
       <c r="H56" s="7" t="n">
         <v>0</v>
@@ -4283,113 +4283,113 @@
         <v>0</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>0</v>
+        <v>126492</v>
       </c>
       <c r="L56" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M56" s="7" t="n">
-        <v>0</v>
+        <v>23627</v>
       </c>
       <c r="N56" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O56" s="7" t="n">
-        <v>0</v>
+        <v>17671</v>
       </c>
       <c r="P56" s="7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Q56" s="7" t="n">
-        <v>943</v>
+        <v>56541</v>
       </c>
       <c r="R56" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S56" s="7" t="n">
-        <v>0</v>
+        <v>1610762</v>
       </c>
       <c r="T56" s="5" t="n">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="U56" s="5" t="n">
-        <v>943</v>
+        <v>1952733</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>il18</t>
+          <t>hrtrt</t>
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>0</v>
+        <v>439669</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>0</v>
+        <v>60109</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>0</v>
+        <v>252223</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>0</v>
+        <v>64245</v>
       </c>
       <c r="J57" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="K57" s="7" t="n">
+        <v>185296</v>
+      </c>
+      <c r="L57" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M57" s="7" t="n">
+        <v>35266</v>
+      </c>
+      <c r="N57" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="O57" s="7" t="n">
+        <v>35238</v>
+      </c>
+      <c r="P57" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q57" s="7" t="n">
+        <v>154242</v>
+      </c>
+      <c r="R57" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="K57" s="7" t="n">
-        <v>38307</v>
-      </c>
-      <c r="L57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="S57" s="7" t="n">
-        <v>0</v>
+        <v>506519</v>
       </c>
       <c r="T57" s="5" t="n">
-        <v>4</v>
+        <v>291</v>
       </c>
       <c r="U57" s="5" t="n">
-        <v>38307</v>
+        <v>1732807</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>il6</t>
+          <t>icam</t>
         </is>
       </c>
       <c r="B58" s="7" t="n">
@@ -4402,13 +4402,13 @@
         <v>1</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>689</v>
+        <v>2669</v>
       </c>
       <c r="F58" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>10594</v>
+        <v>7663</v>
       </c>
       <c r="H58" s="7" t="n">
         <v>0</v>
@@ -4438,7 +4438,7 @@
         <v>6</v>
       </c>
       <c r="Q58" s="7" t="n">
-        <v>17277</v>
+        <v>15379</v>
       </c>
       <c r="R58" s="7" t="n">
         <v>0</v>
@@ -4450,32 +4450,32 @@
         <v>9</v>
       </c>
       <c r="U58" s="5" t="n">
-        <v>28560</v>
+        <v>25711</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>insulin_blood</t>
+          <t>il10</t>
         </is>
       </c>
       <c r="B59" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>56942</v>
+        <v>0</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>9647</v>
+        <v>0</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>25071</v>
+        <v>0</v>
       </c>
       <c r="H59" s="7" t="n">
         <v>0</v>
@@ -4484,46 +4484,46 @@
         <v>0</v>
       </c>
       <c r="J59" s="7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>74472</v>
+        <v>0</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M59" s="7" t="n">
-        <v>23618</v>
+        <v>0</v>
       </c>
       <c r="N59" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O59" s="7" t="n">
-        <v>6587</v>
+        <v>0</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q59" s="7" t="n">
-        <v>25329</v>
+        <v>943</v>
       </c>
       <c r="R59" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S59" s="7" t="n">
-        <v>43342</v>
+        <v>0</v>
       </c>
       <c r="T59" s="5" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="U59" s="5" t="n">
-        <v>265008</v>
+        <v>943</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>isoprostane_8_epi_pgf2a</t>
+          <t>il18</t>
         </is>
       </c>
       <c r="B60" s="7" t="n">
@@ -4533,10 +4533,10 @@
         <v>0</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>2720</v>
+        <v>0</v>
       </c>
       <c r="F60" s="7" t="n">
         <v>0</v>
@@ -4551,10 +4551,10 @@
         <v>0</v>
       </c>
       <c r="J60" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>0</v>
+        <v>38307</v>
       </c>
       <c r="L60" s="7" t="n">
         <v>0</v>
@@ -4569,10 +4569,10 @@
         <v>0</v>
       </c>
       <c r="P60" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q60" s="7" t="n">
-        <v>6805</v>
+        <v>0</v>
       </c>
       <c r="R60" s="7" t="n">
         <v>0</v>
@@ -4581,16 +4581,16 @@
         <v>0</v>
       </c>
       <c r="T60" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U60" s="5" t="n">
-        <v>9525</v>
+        <v>38307</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>lactate</t>
+          <t>il6</t>
         </is>
       </c>
       <c r="B61" s="7" t="n">
@@ -4600,16 +4600,16 @@
         <v>0</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>0</v>
+        <v>689</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>0</v>
+        <v>10594</v>
       </c>
       <c r="H61" s="7" t="n">
         <v>0</v>
@@ -4618,10 +4618,10 @@
         <v>0</v>
       </c>
       <c r="J61" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>26148</v>
+        <v>0</v>
       </c>
       <c r="L61" s="7" t="n">
         <v>0</v>
@@ -4636,10 +4636,10 @@
         <v>0</v>
       </c>
       <c r="P61" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q61" s="7" t="n">
-        <v>0</v>
+        <v>17277</v>
       </c>
       <c r="R61" s="7" t="n">
         <v>0</v>
@@ -4648,35 +4648,35 @@
         <v>0</v>
       </c>
       <c r="T61" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U61" s="5" t="n">
-        <v>26148</v>
+        <v>28560</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>lactate_dehyd</t>
+          <t>insulin_blood</t>
         </is>
       </c>
       <c r="B62" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>0</v>
+        <v>56942</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>0</v>
+        <v>9647</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>0</v>
+        <v>25071</v>
       </c>
       <c r="H62" s="7" t="n">
         <v>0</v>
@@ -4685,65 +4685,65 @@
         <v>0</v>
       </c>
       <c r="J62" s="7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K62" s="7" t="n">
-        <v>3530</v>
+        <v>74472</v>
       </c>
       <c r="L62" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M62" s="7" t="n">
-        <v>0</v>
+        <v>23618</v>
       </c>
       <c r="N62" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O62" s="7" t="n">
-        <v>0</v>
+        <v>6587</v>
       </c>
       <c r="P62" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q62" s="7" t="n">
-        <v>0</v>
+        <v>25329</v>
       </c>
       <c r="R62" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S62" s="7" t="n">
-        <v>0</v>
+        <v>43342</v>
       </c>
       <c r="T62" s="5" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="U62" s="5" t="n">
-        <v>3530</v>
+        <v>265008</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>ldl</t>
+          <t>isoprostane_8_epi_pgf2a</t>
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>173272</v>
+        <v>0</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>16477</v>
+        <v>2720</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>25015</v>
+        <v>0</v>
       </c>
       <c r="H63" s="7" t="n">
         <v>0</v>
@@ -4752,46 +4752,46 @@
         <v>0</v>
       </c>
       <c r="J63" s="7" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>123639</v>
+        <v>0</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M63" s="7" t="n">
-        <v>23409</v>
+        <v>0</v>
       </c>
       <c r="N63" s="7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O63" s="7" t="n">
-        <v>43886</v>
+        <v>0</v>
       </c>
       <c r="P63" s="7" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="Q63" s="7" t="n">
-        <v>68027</v>
+        <v>6805</v>
       </c>
       <c r="R63" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S63" s="7" t="n">
-        <v>46331</v>
+        <v>0</v>
       </c>
       <c r="T63" s="5" t="n">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c r="U63" s="5" t="n">
-        <v>520056</v>
+        <v>9525</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>lppla2_act</t>
+          <t>lactate</t>
         </is>
       </c>
       <c r="B64" s="7" t="n">
@@ -4807,10 +4807,10 @@
         <v>0</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>10910</v>
+        <v>0</v>
       </c>
       <c r="H64" s="7" t="n">
         <v>0</v>
@@ -4819,10 +4819,10 @@
         <v>0</v>
       </c>
       <c r="J64" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K64" s="7" t="n">
-        <v>0</v>
+        <v>26148</v>
       </c>
       <c r="L64" s="7" t="n">
         <v>0</v>
@@ -4837,10 +4837,10 @@
         <v>0</v>
       </c>
       <c r="P64" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q64" s="7" t="n">
-        <v>5122</v>
+        <v>0</v>
       </c>
       <c r="R64" s="7" t="n">
         <v>0</v>
@@ -4849,16 +4849,16 @@
         <v>0</v>
       </c>
       <c r="T64" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U64" s="5" t="n">
-        <v>16032</v>
+        <v>26148</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>lppla2_mass</t>
+          <t>lactate_dehyd</t>
         </is>
       </c>
       <c r="B65" s="7" t="n">
@@ -4874,10 +4874,10 @@
         <v>0</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>10923</v>
+        <v>0</v>
       </c>
       <c r="H65" s="7" t="n">
         <v>0</v>
@@ -4886,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="J65" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>0</v>
+        <v>3530</v>
       </c>
       <c r="L65" s="7" t="n">
         <v>0</v>
@@ -4904,10 +4904,10 @@
         <v>0</v>
       </c>
       <c r="P65" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q65" s="7" t="n">
-        <v>5042</v>
+        <v>0</v>
       </c>
       <c r="R65" s="7" t="n">
         <v>0</v>
@@ -4919,87 +4919,87 @@
         <v>3</v>
       </c>
       <c r="U65" s="5" t="n">
-        <v>15965</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>lympho_ct</t>
+          <t>ldl</t>
         </is>
       </c>
       <c r="B66" s="7" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>5706</v>
+        <v>173272</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>3968</v>
+        <v>16477</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>0</v>
+        <v>25015</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I66" s="7" t="n">
-        <v>53590</v>
+        <v>0</v>
       </c>
       <c r="J66" s="7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K66" s="7" t="n">
-        <v>0</v>
+        <v>123639</v>
       </c>
       <c r="L66" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M66" s="7" t="n">
-        <v>22908</v>
+        <v>23409</v>
       </c>
       <c r="N66" s="7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O66" s="7" t="n">
-        <v>0</v>
+        <v>43886</v>
       </c>
       <c r="P66" s="7" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="Q66" s="7" t="n">
-        <v>2338</v>
+        <v>68027</v>
       </c>
       <c r="R66" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S66" s="7" t="n">
-        <v>0</v>
+        <v>46331</v>
       </c>
       <c r="T66" s="5" t="n">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="U66" s="5" t="n">
-        <v>88510</v>
+        <v>520056</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>lympho_pct</t>
+          <t>lppla2_act</t>
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>24362</v>
+        <v>0</v>
       </c>
       <c r="D67" s="7" t="n">
         <v>0</v>
@@ -5008,10 +5008,10 @@
         <v>0</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>0</v>
+        <v>10910</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0</v>
@@ -5020,28 +5020,28 @@
         <v>0</v>
       </c>
       <c r="J67" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>12638</v>
+        <v>0</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M67" s="7" t="n">
-        <v>22908</v>
+        <v>0</v>
       </c>
       <c r="N67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="O67" s="7" t="n">
-        <v>3362</v>
-      </c>
-      <c r="P67" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="Q67" s="7" t="n">
-        <v>0</v>
+        <v>5122</v>
       </c>
       <c r="R67" s="7" t="n">
         <v>0</v>
@@ -5050,65 +5050,65 @@
         <v>0</v>
       </c>
       <c r="T67" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U67" s="5" t="n">
-        <v>63270</v>
+        <v>16032</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>mch</t>
+          <t>lppla2_mass</t>
         </is>
       </c>
       <c r="B68" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>12069</v>
+        <v>0</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>7165</v>
+        <v>0</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>0</v>
+        <v>10923</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I68" s="7" t="n">
-        <v>53674</v>
+        <v>0</v>
       </c>
       <c r="J68" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>54003</v>
+        <v>0</v>
       </c>
       <c r="L68" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M68" s="7" t="n">
-        <v>23567</v>
+        <v>0</v>
       </c>
       <c r="N68" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" s="7" t="n">
-        <v>3376</v>
+        <v>0</v>
       </c>
       <c r="P68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="Q68" s="7" t="n">
-        <v>2756</v>
+        <v>5042</v>
       </c>
       <c r="R68" s="7" t="n">
         <v>0</v>
@@ -5117,29 +5117,29 @@
         <v>0</v>
       </c>
       <c r="T68" s="5" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="U68" s="5" t="n">
-        <v>156610</v>
+        <v>15965</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>mchc</t>
+          <t>lympho_ct</t>
         </is>
       </c>
       <c r="B69" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>8408</v>
+        <v>5706</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>0</v>
+        <v>3968</v>
       </c>
       <c r="F69" s="7" t="n">
         <v>0</v>
@@ -5151,31 +5151,31 @@
         <v>3</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>53674</v>
+        <v>53590</v>
       </c>
       <c r="J69" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>39615</v>
+        <v>0</v>
       </c>
       <c r="L69" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M69" s="7" t="n">
-        <v>23567</v>
+        <v>22908</v>
       </c>
       <c r="N69" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" s="7" t="n">
-        <v>3377</v>
+        <v>0</v>
       </c>
       <c r="P69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="Q69" s="7" t="n">
-        <v>2756</v>
+        <v>2338</v>
       </c>
       <c r="R69" s="7" t="n">
         <v>0</v>
@@ -5184,23 +5184,23 @@
         <v>0</v>
       </c>
       <c r="T69" s="5" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="U69" s="5" t="n">
-        <v>131397</v>
+        <v>88510</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>mcv</t>
+          <t>lympho_pct</t>
         </is>
       </c>
       <c r="B70" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>28238</v>
+        <v>24362</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>0</v>
@@ -5215,34 +5215,34 @@
         <v>0</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I70" s="7" t="n">
-        <v>53674</v>
+        <v>0</v>
       </c>
       <c r="J70" s="7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>39615</v>
+        <v>12638</v>
       </c>
       <c r="L70" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M70" s="7" t="n">
-        <v>23567</v>
+        <v>22908</v>
       </c>
       <c r="N70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="O70" s="7" t="n">
-        <v>3377</v>
+        <v>3362</v>
       </c>
       <c r="P70" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="7" t="n">
-        <v>2756</v>
+        <v>0</v>
       </c>
       <c r="R70" s="7" t="n">
         <v>0</v>
@@ -5251,29 +5251,29 @@
         <v>0</v>
       </c>
       <c r="T70" s="5" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="U70" s="5" t="n">
-        <v>151227</v>
+        <v>63270</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>mean_art_press</t>
+          <t>mch</t>
         </is>
       </c>
       <c r="B71" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>0</v>
+        <v>12069</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>0</v>
+        <v>7165</v>
       </c>
       <c r="F71" s="7" t="n">
         <v>0</v>
@@ -5282,34 +5282,34 @@
         <v>0</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>0</v>
+        <v>53674</v>
       </c>
       <c r="J71" s="7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>50002</v>
+        <v>54003</v>
       </c>
       <c r="L71" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M71" s="7" t="n">
-        <v>0</v>
+        <v>23567</v>
       </c>
       <c r="N71" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" s="7" t="n">
-        <v>0</v>
+        <v>3376</v>
       </c>
       <c r="P71" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q71" s="7" t="n">
-        <v>0</v>
+        <v>2756</v>
       </c>
       <c r="R71" s="7" t="n">
         <v>0</v>
@@ -5318,23 +5318,23 @@
         <v>0</v>
       </c>
       <c r="T71" s="5" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="U71" s="5" t="n">
-        <v>50002</v>
+        <v>156610</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>mmp9</t>
+          <t>mchc</t>
         </is>
       </c>
       <c r="B72" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>0</v>
+        <v>8408</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>0</v>
@@ -5349,34 +5349,34 @@
         <v>0</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I72" s="7" t="n">
-        <v>0</v>
+        <v>53674</v>
       </c>
       <c r="J72" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K72" s="7" t="n">
-        <v>0</v>
+        <v>39615</v>
       </c>
       <c r="L72" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M72" s="7" t="n">
-        <v>0</v>
+        <v>23567</v>
       </c>
       <c r="N72" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" s="7" t="n">
-        <v>0</v>
+        <v>3377</v>
       </c>
       <c r="P72" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q72" s="7" t="n">
-        <v>7393</v>
+        <v>2756</v>
       </c>
       <c r="R72" s="7" t="n">
         <v>0</v>
@@ -5385,65 +5385,65 @@
         <v>0</v>
       </c>
       <c r="T72" s="5" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="U72" s="5" t="n">
-        <v>7393</v>
+        <v>131397</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>mn_art_pres</t>
+          <t>mcv</t>
         </is>
       </c>
       <c r="B73" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>28238</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>53674</v>
+      </c>
+      <c r="J73" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K73" s="7" t="n">
+        <v>39615</v>
+      </c>
+      <c r="L73" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M73" s="7" t="n">
+        <v>23567</v>
+      </c>
+      <c r="N73" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C73" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="D73" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E73" s="7" t="n">
-        <v>24769</v>
-      </c>
-      <c r="F73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="O73" s="7" t="n">
-        <v>0</v>
+        <v>3377</v>
       </c>
       <c r="P73" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q73" s="7" t="n">
-        <v>18383</v>
+        <v>2756</v>
       </c>
       <c r="R73" s="7" t="n">
         <v>0</v>
@@ -5452,29 +5452,29 @@
         <v>0</v>
       </c>
       <c r="T73" s="5" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="U73" s="5" t="n">
-        <v>43170</v>
+        <v>151227</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>monocyte_ncnc_bld</t>
+          <t>mean_art_press</t>
         </is>
       </c>
       <c r="B74" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C74" s="7" t="n">
-        <v>5706</v>
+        <v>0</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="F74" s="7" t="n">
         <v>0</v>
@@ -5483,22 +5483,22 @@
         <v>0</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I74" s="7" t="n">
-        <v>53588</v>
+        <v>0</v>
       </c>
       <c r="J74" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K74" s="7" t="n">
-        <v>32540</v>
+        <v>50002</v>
       </c>
       <c r="L74" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M74" s="7" t="n">
-        <v>22913</v>
+        <v>0</v>
       </c>
       <c r="N74" s="7" t="n">
         <v>0</v>
@@ -5507,10 +5507,10 @@
         <v>0</v>
       </c>
       <c r="P74" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q74" s="7" t="n">
-        <v>3231</v>
+        <v>0</v>
       </c>
       <c r="R74" s="7" t="n">
         <v>0</v>
@@ -5519,29 +5519,29 @@
         <v>0</v>
       </c>
       <c r="T74" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="U74" s="5" t="n">
-        <v>118362</v>
+        <v>50002</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>neutro_pct</t>
+          <t>mmp9</t>
         </is>
       </c>
       <c r="B75" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>18618</v>
+        <v>0</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>2407</v>
+        <v>0</v>
       </c>
       <c r="F75" s="7" t="n">
         <v>0</v>
@@ -5562,10 +5562,10 @@
         <v>0</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M75" s="7" t="n">
-        <v>22908</v>
+        <v>0</v>
       </c>
       <c r="N75" s="7" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="P75" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q75" s="7" t="n">
-        <v>0</v>
+        <v>7393</v>
       </c>
       <c r="R75" s="7" t="n">
         <v>0</v>
@@ -5586,29 +5586,29 @@
         <v>0</v>
       </c>
       <c r="T75" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U75" s="5" t="n">
-        <v>43933</v>
+        <v>7393</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>neutrophil_ct</t>
+          <t>mn_art_pres</t>
         </is>
       </c>
       <c r="B76" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>324</v>
+        <v>24769</v>
       </c>
       <c r="F76" s="7" t="n">
         <v>0</v>
@@ -5617,10 +5617,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I76" s="7" t="n">
-        <v>53590</v>
+        <v>0</v>
       </c>
       <c r="J76" s="7" t="n">
         <v>0</v>
@@ -5629,10 +5629,10 @@
         <v>0</v>
       </c>
       <c r="L76" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M76" s="7" t="n">
-        <v>22909</v>
+        <v>0</v>
       </c>
       <c r="N76" s="7" t="n">
         <v>0</v>
@@ -5641,10 +5641,10 @@
         <v>0</v>
       </c>
       <c r="P76" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q76" s="7" t="n">
-        <v>2338</v>
+        <v>18383</v>
       </c>
       <c r="R76" s="7" t="n">
         <v>0</v>
@@ -5653,29 +5653,29 @@
         <v>0</v>
       </c>
       <c r="T76" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U76" s="5" t="n">
-        <v>79161</v>
+        <v>43170</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>nt_bnp</t>
+          <t>monocyte_ncnc_bld</t>
         </is>
       </c>
       <c r="B77" s="7" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>47302</v>
+        <v>5706</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="F77" s="7" t="n">
         <v>0</v>
@@ -5684,22 +5684,22 @@
         <v>0</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>0</v>
+        <v>53588</v>
       </c>
       <c r="J77" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>19114</v>
+        <v>32540</v>
       </c>
       <c r="L77" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M77" s="7" t="n">
-        <v>0</v>
+        <v>22913</v>
       </c>
       <c r="N77" s="7" t="n">
         <v>0</v>
@@ -5711,38 +5711,38 @@
         <v>2</v>
       </c>
       <c r="Q77" s="7" t="n">
-        <v>10090</v>
+        <v>3231</v>
       </c>
       <c r="R77" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S77" s="7" t="n">
-        <v>1802</v>
+        <v>0</v>
       </c>
       <c r="T77" s="5" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="U77" s="5" t="n">
-        <v>78308</v>
+        <v>118362</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>pacem_stat</t>
+          <t>neutro_pct</t>
         </is>
       </c>
       <c r="B78" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>13110</v>
+        <v>18618</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>0</v>
+        <v>2407</v>
       </c>
       <c r="F78" s="7" t="n">
         <v>0</v>
@@ -5766,7 +5766,7 @@
         <v>2</v>
       </c>
       <c r="M78" s="7" t="n">
-        <v>11848</v>
+        <v>22908</v>
       </c>
       <c r="N78" s="7" t="n">
         <v>0</v>
@@ -5775,10 +5775,10 @@
         <v>0</v>
       </c>
       <c r="P78" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q78" s="7" t="n">
-        <v>12922</v>
+        <v>0</v>
       </c>
       <c r="R78" s="7" t="n">
         <v>0</v>
@@ -5787,90 +5787,90 @@
         <v>0</v>
       </c>
       <c r="T78" s="5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="U78" s="5" t="n">
-        <v>37880</v>
+        <v>43933</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>platelet_ct</t>
+          <t>neutrophil_ct</t>
         </is>
       </c>
       <c r="B79" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>37442</v>
+        <v>0</v>
       </c>
       <c r="D79" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>324</v>
+      </c>
+      <c r="F79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I79" s="7" t="n">
+        <v>53590</v>
+      </c>
+      <c r="J79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M79" s="7" t="n">
+        <v>22909</v>
+      </c>
+      <c r="N79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E79" s="7" t="n">
-        <v>3581</v>
-      </c>
-      <c r="F79" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G79" s="7" t="n">
-        <v>25046</v>
-      </c>
-      <c r="H79" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I79" s="7" t="n">
-        <v>53654</v>
-      </c>
-      <c r="J79" s="7" t="n">
+      <c r="Q79" s="7" t="n">
+        <v>2338</v>
+      </c>
+      <c r="R79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="K79" s="7" t="n">
-        <v>35931</v>
-      </c>
-      <c r="L79" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M79" s="7" t="n">
-        <v>23560</v>
-      </c>
-      <c r="N79" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O79" s="7" t="n">
-        <v>3749</v>
-      </c>
-      <c r="P79" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q79" s="7" t="n">
-        <v>3644</v>
-      </c>
-      <c r="R79" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="S79" s="7" t="n">
-        <v>623065</v>
-      </c>
-      <c r="T79" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="U79" s="5" t="n">
-        <v>809672</v>
+        <v>79161</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>pmv</t>
+          <t>nt_bnp</t>
         </is>
       </c>
       <c r="B80" s="7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>5707</v>
+        <v>47302</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>0</v>
@@ -5891,10 +5891,10 @@
         <v>0</v>
       </c>
       <c r="J80" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>32540</v>
+        <v>19114</v>
       </c>
       <c r="L80" s="7" t="n">
         <v>0</v>
@@ -5903,53 +5903,53 @@
         <v>0</v>
       </c>
       <c r="N80" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" s="7" t="n">
-        <v>3376</v>
+        <v>0</v>
       </c>
       <c r="P80" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q80" s="7" t="n">
-        <v>0</v>
+        <v>10090</v>
       </c>
       <c r="R80" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S80" s="7" t="n">
-        <v>0</v>
+        <v>1802</v>
       </c>
       <c r="T80" s="5" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="U80" s="5" t="n">
-        <v>41623</v>
+        <v>78308</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>potassium</t>
+          <t>pacem_stat</t>
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>37384</v>
+        <v>13110</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>6310</v>
+        <v>0</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>25155</v>
+        <v>0</v>
       </c>
       <c r="H81" s="7" t="n">
         <v>0</v>
@@ -5964,22 +5964,22 @@
         <v>0</v>
       </c>
       <c r="L81" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>0</v>
+        <v>11848</v>
       </c>
       <c r="N81" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>3839</v>
+        <v>0</v>
       </c>
       <c r="P81" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q81" s="7" t="n">
-        <v>18964</v>
+        <v>12922</v>
       </c>
       <c r="R81" s="7" t="n">
         <v>0</v>
@@ -5988,90 +5988,90 @@
         <v>0</v>
       </c>
       <c r="T81" s="5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="U81" s="5" t="n">
-        <v>91652</v>
+        <v>37880</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>pr_ekg</t>
+          <t>platelet_ct</t>
         </is>
       </c>
       <c r="B82" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>59015</v>
+        <v>37442</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>0</v>
+        <v>3581</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>0</v>
+        <v>25046</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I82" s="7" t="n">
-        <v>0</v>
+        <v>53654</v>
       </c>
       <c r="J82" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K82" s="7" t="n">
-        <v>0</v>
+        <v>35931</v>
       </c>
       <c r="L82" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M82" s="7" t="n">
-        <v>23526</v>
+        <v>23560</v>
       </c>
       <c r="N82" s="7" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="O82" s="7" t="n">
-        <v>78673</v>
+        <v>3749</v>
       </c>
       <c r="P82" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q82" s="7" t="n">
-        <v>22435</v>
+        <v>3644</v>
       </c>
       <c r="R82" s="7" t="n">
         <v>3</v>
       </c>
       <c r="S82" s="7" t="n">
-        <v>500439</v>
+        <v>623065</v>
       </c>
       <c r="T82" s="5" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="U82" s="5" t="n">
-        <v>684088</v>
+        <v>809672</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>pr_qrs_qt</t>
+          <t>pmv</t>
         </is>
       </c>
       <c r="B83" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>0</v>
+        <v>5707</v>
       </c>
       <c r="D83" s="7" t="n">
         <v>0</v>
@@ -6092,10 +6092,10 @@
         <v>0</v>
       </c>
       <c r="J83" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>66296</v>
+        <v>32540</v>
       </c>
       <c r="L83" s="7" t="n">
         <v>0</v>
@@ -6104,10 +6104,10 @@
         <v>0</v>
       </c>
       <c r="N83" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" s="7" t="n">
-        <v>0</v>
+        <v>3376</v>
       </c>
       <c r="P83" s="7" t="n">
         <v>0</v>
@@ -6122,35 +6122,35 @@
         <v>0</v>
       </c>
       <c r="T83" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U83" s="5" t="n">
-        <v>66296</v>
+        <v>41623</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>pselectin</t>
+          <t>potassium</t>
         </is>
       </c>
       <c r="B84" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>0</v>
+        <v>37384</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>326</v>
+        <v>6310</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>0</v>
+        <v>25155</v>
       </c>
       <c r="H84" s="7" t="n">
         <v>0</v>
@@ -6171,16 +6171,16 @@
         <v>0</v>
       </c>
       <c r="N84" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O84" s="7" t="n">
-        <v>8299</v>
+        <v>3839</v>
       </c>
       <c r="P84" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q84" s="7" t="n">
-        <v>0</v>
+        <v>18964</v>
       </c>
       <c r="R84" s="7" t="n">
         <v>0</v>
@@ -6189,23 +6189,23 @@
         <v>0</v>
       </c>
       <c r="T84" s="5" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="U84" s="5" t="n">
-        <v>8625</v>
+        <v>91652</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>qrs_ekg</t>
+          <t>pr_ekg</t>
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>274284</v>
+        <v>59015</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>0</v>
@@ -6214,10 +6214,10 @@
         <v>0</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>43430</v>
+        <v>0</v>
       </c>
       <c r="H85" s="7" t="n">
         <v>0</v>
@@ -6226,28 +6226,28 @@
         <v>0</v>
       </c>
       <c r="J85" s="7" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>202581</v>
+        <v>0</v>
       </c>
       <c r="L85" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>23558</v>
+        <v>23526</v>
       </c>
       <c r="N85" s="7" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O85" s="7" t="n">
-        <v>65524</v>
+        <v>78673</v>
       </c>
       <c r="P85" s="7" t="n">
         <v>8</v>
       </c>
       <c r="Q85" s="7" t="n">
-        <v>22514</v>
+        <v>22435</v>
       </c>
       <c r="R85" s="7" t="n">
         <v>3</v>
@@ -6256,23 +6256,23 @@
         <v>500439</v>
       </c>
       <c r="T85" s="5" t="n">
-        <v>139</v>
+        <v>42</v>
       </c>
       <c r="U85" s="5" t="n">
-        <v>1132330</v>
+        <v>684088</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>qt_ekg</t>
+          <t>pr_qrs_qt</t>
         </is>
       </c>
       <c r="B86" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>61199</v>
+        <v>0</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>0</v>
@@ -6293,59 +6293,59 @@
         <v>0</v>
       </c>
       <c r="J86" s="7" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>90128</v>
+        <v>66296</v>
       </c>
       <c r="L86" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M86" s="7" t="n">
-        <v>35283</v>
+        <v>0</v>
       </c>
       <c r="N86" s="7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O86" s="7" t="n">
-        <v>46378</v>
+        <v>0</v>
       </c>
       <c r="P86" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q86" s="7" t="n">
-        <v>22514</v>
+        <v>0</v>
       </c>
       <c r="R86" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S86" s="7" t="n">
-        <v>500439</v>
+        <v>0</v>
       </c>
       <c r="T86" s="5" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="U86" s="5" t="n">
-        <v>755941</v>
+        <v>66296</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>rdbld_ct</t>
+          <t>pselectin</t>
         </is>
       </c>
       <c r="B87" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>14728</v>
+        <v>0</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>3583</v>
+        <v>326</v>
       </c>
       <c r="F87" s="7" t="n">
         <v>0</v>
@@ -6354,34 +6354,34 @@
         <v>0</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I87" s="7" t="n">
-        <v>53674</v>
+        <v>0</v>
       </c>
       <c r="J87" s="7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>59154</v>
+        <v>0</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>23567</v>
+        <v>0</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>3377</v>
+        <v>8299</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q87" s="7" t="n">
-        <v>3656</v>
+        <v>0</v>
       </c>
       <c r="R87" s="7" t="n">
         <v>0</v>
@@ -6390,23 +6390,23 @@
         <v>0</v>
       </c>
       <c r="T87" s="5" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="U87" s="5" t="n">
-        <v>161739</v>
+        <v>8625</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>rdw</t>
+          <t>qrs_ekg</t>
         </is>
       </c>
       <c r="B88" s="7" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>12016</v>
+        <v>274284</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>0</v>
@@ -6415,10 +6415,10 @@
         <v>0</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>0</v>
+        <v>43430</v>
       </c>
       <c r="H88" s="7" t="n">
         <v>0</v>
@@ -6427,65 +6427,65 @@
         <v>0</v>
       </c>
       <c r="J88" s="7" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="K88" s="7" t="n">
-        <v>32543</v>
+        <v>202581</v>
       </c>
       <c r="L88" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M88" s="7" t="n">
-        <v>23566</v>
+        <v>23558</v>
       </c>
       <c r="N88" s="7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O88" s="7" t="n">
-        <v>0</v>
+        <v>65524</v>
       </c>
       <c r="P88" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q88" s="7" t="n">
-        <v>0</v>
+        <v>22514</v>
       </c>
       <c r="R88" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S88" s="7" t="n">
-        <v>0</v>
+        <v>500439</v>
       </c>
       <c r="T88" s="5" t="n">
-        <v>11</v>
+        <v>139</v>
       </c>
       <c r="U88" s="5" t="n">
-        <v>68125</v>
+        <v>1132330</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>sleep_duration_daily</t>
+          <t>qt_ekg</t>
         </is>
       </c>
       <c r="B89" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>5925</v>
+        <v>61199</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>3529</v>
+        <v>0</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>13853</v>
+        <v>0</v>
       </c>
       <c r="H89" s="7" t="n">
         <v>0</v>
@@ -6494,59 +6494,59 @@
         <v>0</v>
       </c>
       <c r="J89" s="7" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>129670</v>
+        <v>90128</v>
       </c>
       <c r="L89" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M89" s="7" t="n">
-        <v>23080</v>
+        <v>35283</v>
       </c>
       <c r="N89" s="7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O89" s="7" t="n">
-        <v>6955</v>
+        <v>46378</v>
       </c>
       <c r="P89" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q89" s="7" t="n">
-        <v>10941</v>
+        <v>22514</v>
       </c>
       <c r="R89" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S89" s="7" t="n">
-        <v>626832</v>
+        <v>500439</v>
       </c>
       <c r="T89" s="5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U89" s="5" t="n">
-        <v>820785</v>
+        <v>755941</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>sodium_blood</t>
+          <t>rdbld_ct</t>
         </is>
       </c>
       <c r="B90" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>52984</v>
+        <v>14728</v>
       </c>
       <c r="D90" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>0</v>
+        <v>3583</v>
       </c>
       <c r="F90" s="7" t="n">
         <v>0</v>
@@ -6555,89 +6555,89 @@
         <v>0</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I90" s="7" t="n">
-        <v>0</v>
+        <v>53674</v>
       </c>
       <c r="J90" s="7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K90" s="7" t="n">
-        <v>17171</v>
+        <v>59154</v>
       </c>
       <c r="L90" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M90" s="7" t="n">
-        <v>0</v>
+        <v>23567</v>
       </c>
       <c r="N90" s="7" t="n">
         <v>1</v>
       </c>
       <c r="O90" s="7" t="n">
-        <v>3839</v>
+        <v>3377</v>
       </c>
       <c r="P90" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q90" s="7" t="n">
-        <v>6129</v>
+        <v>3656</v>
       </c>
       <c r="R90" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S90" s="7" t="n">
-        <v>5721</v>
+        <v>0</v>
       </c>
       <c r="T90" s="5" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="U90" s="5" t="n">
-        <v>85844</v>
+        <v>161739</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>sodium_intak</t>
+          <t>rdw</t>
         </is>
       </c>
       <c r="B91" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>28614</v>
+        <v>12016</v>
       </c>
       <c r="D91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E91" s="7" t="n">
-        <v>16962</v>
-      </c>
-      <c r="F91" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G91" s="7" t="n">
-        <v>12180</v>
-      </c>
-      <c r="H91" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="7" t="n">
-        <v>18</v>
-      </c>
       <c r="K91" s="7" t="n">
-        <v>82860</v>
+        <v>32543</v>
       </c>
       <c r="L91" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M91" s="7" t="n">
-        <v>0</v>
+        <v>23566</v>
       </c>
       <c r="N91" s="7" t="n">
         <v>0</v>
@@ -6646,102 +6646,102 @@
         <v>0</v>
       </c>
       <c r="P91" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="7" t="n">
-        <v>4252</v>
+        <v>0</v>
       </c>
       <c r="R91" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S91" s="7" t="n">
-        <v>338044</v>
+        <v>0</v>
       </c>
       <c r="T91" s="5" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="U91" s="5" t="n">
-        <v>482912</v>
+        <v>68125</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>spirometry</t>
+          <t>sleep_duration_daily</t>
         </is>
       </c>
       <c r="B92" s="7" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C92" s="7" t="n">
-        <v>226242</v>
+        <v>5925</v>
       </c>
       <c r="D92" s="7" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>118442</v>
+        <v>3529</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>77987</v>
+        <v>13853</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I92" s="7" t="n">
-        <v>264146</v>
+        <v>0</v>
       </c>
       <c r="J92" s="7" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="K92" s="7" t="n">
-        <v>186708</v>
+        <v>129670</v>
       </c>
       <c r="L92" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M92" s="7" t="n">
-        <v>79778</v>
+        <v>23080</v>
       </c>
       <c r="N92" s="7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O92" s="7" t="n">
-        <v>44329</v>
+        <v>6955</v>
       </c>
       <c r="P92" s="7" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="Q92" s="7" t="n">
-        <v>28584</v>
+        <v>10941</v>
       </c>
       <c r="R92" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S92" s="7" t="n">
-        <v>0</v>
+        <v>626832</v>
       </c>
       <c r="T92" s="5" t="n">
-        <v>211</v>
+        <v>55</v>
       </c>
       <c r="U92" s="5" t="n">
-        <v>1026216</v>
+        <v>820785</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>spo2</t>
+          <t>sodium_blood</t>
         </is>
       </c>
       <c r="B93" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>0</v>
+        <v>52984</v>
       </c>
       <c r="D93" s="7" t="n">
         <v>0</v>
@@ -6750,77 +6750,77 @@
         <v>0</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>10480</v>
+        <v>0</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>64224</v>
+        <v>0</v>
       </c>
       <c r="J93" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K93" s="7" t="n">
+        <v>17171</v>
+      </c>
+      <c r="L93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="K93" s="7" t="n">
-        <v>715</v>
-      </c>
-      <c r="L93" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M93" s="7" t="n">
-        <v>22347</v>
-      </c>
-      <c r="N93" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="O93" s="7" t="n">
-        <v>0</v>
+        <v>3839</v>
       </c>
       <c r="P93" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" s="7" t="n">
-        <v>0</v>
+        <v>6129</v>
       </c>
       <c r="R93" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S93" s="7" t="n">
-        <v>0</v>
+        <v>5721</v>
       </c>
       <c r="T93" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U93" s="5" t="n">
-        <v>97766</v>
+        <v>85844</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>tnfa</t>
+          <t>sodium_intak</t>
         </is>
       </c>
       <c r="B94" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>0</v>
+        <v>28614</v>
       </c>
       <c r="D94" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>0</v>
+        <v>16962</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>0</v>
+        <v>12180</v>
       </c>
       <c r="H94" s="7" t="n">
         <v>0</v>
@@ -6829,10 +6829,10 @@
         <v>0</v>
       </c>
       <c r="J94" s="7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K94" s="7" t="n">
-        <v>0</v>
+        <v>82860</v>
       </c>
       <c r="L94" s="7" t="n">
         <v>0</v>
@@ -6847,28 +6847,28 @@
         <v>0</v>
       </c>
       <c r="P94" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q94" s="7" t="n">
-        <v>6524</v>
+        <v>4252</v>
       </c>
       <c r="R94" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S94" s="7" t="n">
-        <v>0</v>
+        <v>338044</v>
       </c>
       <c r="T94" s="5" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="U94" s="5" t="n">
-        <v>6524</v>
+        <v>482912</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>tnfa_r1</t>
+          <t>spo2</t>
         </is>
       </c>
       <c r="B95" s="7" t="n">
@@ -6884,28 +6884,28 @@
         <v>0</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>0</v>
+        <v>10480</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>0</v>
+        <v>64224</v>
       </c>
       <c r="J95" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" s="7" t="n">
-        <v>0</v>
+        <v>715</v>
       </c>
       <c r="L95" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M95" s="7" t="n">
-        <v>0</v>
+        <v>22347</v>
       </c>
       <c r="N95" s="7" t="n">
         <v>0</v>
@@ -6914,10 +6914,10 @@
         <v>0</v>
       </c>
       <c r="P95" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q95" s="7" t="n">
-        <v>9242</v>
+        <v>0</v>
       </c>
       <c r="R95" s="7" t="n">
         <v>0</v>
@@ -6926,35 +6926,35 @@
         <v>0</v>
       </c>
       <c r="T95" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="U95" s="5" t="n">
-        <v>9242</v>
+        <v>97766</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>tot_chol_bld</t>
+          <t>tnfa</t>
         </is>
       </c>
       <c r="B96" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C96" s="7" t="n">
-        <v>245458</v>
+        <v>0</v>
       </c>
       <c r="D96" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E96" s="7" t="n">
-        <v>6897</v>
+        <v>0</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G96" s="7" t="n">
-        <v>11010</v>
+        <v>0</v>
       </c>
       <c r="H96" s="7" t="n">
         <v>0</v>
@@ -6963,65 +6963,65 @@
         <v>0</v>
       </c>
       <c r="J96" s="7" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="K96" s="7" t="n">
-        <v>218271</v>
+        <v>0</v>
       </c>
       <c r="L96" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M96" s="7" t="n">
-        <v>23653</v>
+        <v>0</v>
       </c>
       <c r="N96" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O96" s="7" t="n">
-        <v>31460</v>
+        <v>0</v>
       </c>
       <c r="P96" s="7" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="Q96" s="7" t="n">
-        <v>68149</v>
+        <v>6524</v>
       </c>
       <c r="R96" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S96" s="7" t="n">
-        <v>46610</v>
+        <v>0</v>
       </c>
       <c r="T96" s="5" t="n">
-        <v>131</v>
+        <v>6</v>
       </c>
       <c r="U96" s="5" t="n">
-        <v>651508</v>
+        <v>6524</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>triglyc_bld</t>
+          <t>tnfa_r1</t>
         </is>
       </c>
       <c r="B97" s="7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C97" s="7" t="n">
-        <v>167017</v>
+        <v>0</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>16569</v>
+        <v>0</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>29264</v>
+        <v>0</v>
       </c>
       <c r="H97" s="7" t="n">
         <v>0</v>
@@ -7030,65 +7030,65 @@
         <v>0</v>
       </c>
       <c r="J97" s="7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K97" s="7" t="n">
-        <v>168009</v>
+        <v>0</v>
       </c>
       <c r="L97" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M97" s="7" t="n">
-        <v>23653</v>
+        <v>0</v>
       </c>
       <c r="N97" s="7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O97" s="7" t="n">
-        <v>32777</v>
+        <v>0</v>
       </c>
       <c r="P97" s="7" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Q97" s="7" t="n">
-        <v>67803</v>
+        <v>9242</v>
       </c>
       <c r="R97" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S97" s="7" t="n">
-        <v>46610</v>
+        <v>0</v>
       </c>
       <c r="T97" s="5" t="n">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="U97" s="5" t="n">
-        <v>551702</v>
+        <v>9242</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>troponin</t>
+          <t>tot_chol_bld</t>
         </is>
       </c>
       <c r="B98" s="7" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C98" s="7" t="n">
-        <v>59241</v>
+        <v>245458</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>77</v>
+        <v>6897</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>0</v>
+        <v>11010</v>
       </c>
       <c r="H98" s="7" t="n">
         <v>0</v>
@@ -7097,65 +7097,65 @@
         <v>0</v>
       </c>
       <c r="J98" s="7" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="K98" s="7" t="n">
-        <v>14391</v>
+        <v>218271</v>
       </c>
       <c r="L98" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M98" s="7" t="n">
-        <v>0</v>
+        <v>23653</v>
       </c>
       <c r="N98" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O98" s="7" t="n">
-        <v>0</v>
+        <v>31460</v>
       </c>
       <c r="P98" s="7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q98" s="7" t="n">
-        <v>0</v>
+        <v>68149</v>
       </c>
       <c r="R98" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S98" s="7" t="n">
-        <v>4604</v>
+        <v>46610</v>
       </c>
       <c r="T98" s="5" t="n">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="U98" s="5" t="n">
-        <v>78313</v>
+        <v>651508</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>vege_serving</t>
+          <t>triglyc_bld</t>
         </is>
       </c>
       <c r="B99" s="7" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C99" s="7" t="n">
-        <v>322380</v>
+        <v>167017</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>74514</v>
+        <v>16569</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>771</v>
+        <v>29264</v>
       </c>
       <c r="H99" s="7" t="n">
         <v>0</v>
@@ -7164,132 +7164,132 @@
         <v>0</v>
       </c>
       <c r="J99" s="7" t="n">
-        <v>232</v>
+        <v>50</v>
       </c>
       <c r="K99" s="7" t="n">
-        <v>638568</v>
+        <v>168009</v>
       </c>
       <c r="L99" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M99" s="7" t="n">
-        <v>0</v>
+        <v>23653</v>
       </c>
       <c r="N99" s="7" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O99" s="7" t="n">
-        <v>7594</v>
+        <v>32777</v>
       </c>
       <c r="P99" s="7" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="Q99" s="7" t="n">
-        <v>29869</v>
+        <v>67803</v>
       </c>
       <c r="R99" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S99" s="7" t="n">
-        <v>680137</v>
+        <v>46610</v>
       </c>
       <c r="T99" s="5" t="n">
-        <v>300</v>
+        <v>117</v>
       </c>
       <c r="U99" s="5" t="n">
-        <v>1753833</v>
+        <v>551702</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>waist_circ</t>
+          <t>troponin</t>
         </is>
       </c>
       <c r="B100" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C100" s="7" t="n">
-        <v>54019</v>
+        <v>59241</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>30185</v>
+        <v>77</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>43939</v>
+        <v>0</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I100" s="7" t="n">
-        <v>53850</v>
+        <v>0</v>
       </c>
       <c r="J100" s="7" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="K100" s="7" t="n">
-        <v>175209</v>
+        <v>14391</v>
       </c>
       <c r="L100" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M100" s="7" t="n">
-        <v>23633</v>
+        <v>0</v>
       </c>
       <c r="N100" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O100" s="7" t="n">
-        <v>25409</v>
+        <v>0</v>
       </c>
       <c r="P100" s="7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="7" t="n">
-        <v>56543</v>
+        <v>0</v>
       </c>
       <c r="R100" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S100" s="7" t="n">
-        <v>1619039</v>
+        <v>4604</v>
       </c>
       <c r="T100" s="5" t="n">
-        <v>112</v>
+        <v>18</v>
       </c>
       <c r="U100" s="5" t="n">
-        <v>2081826</v>
+        <v>78313</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>waist_hip</t>
+          <t>vege_serving</t>
         </is>
       </c>
       <c r="B101" s="7" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C101" s="7" t="n">
-        <v>106654</v>
+        <v>322380</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>388</v>
+        <v>74514</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>0</v>
+        <v>771</v>
       </c>
       <c r="H101" s="7" t="n">
         <v>0</v>
@@ -7298,241 +7298,375 @@
         <v>0</v>
       </c>
       <c r="J101" s="7" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="K101" s="7" t="n">
-        <v>0</v>
+        <v>638568</v>
       </c>
       <c r="L101" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M101" s="7" t="n">
-        <v>23626</v>
+        <v>0</v>
       </c>
       <c r="N101" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>23478</v>
+        <v>7594</v>
       </c>
       <c r="P101" s="7" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="Q101" s="7" t="n">
-        <v>89497</v>
+        <v>29869</v>
       </c>
       <c r="R101" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S101" s="7" t="n">
-        <v>1610605</v>
+        <v>680137</v>
       </c>
       <c r="T101" s="5" t="n">
-        <v>51</v>
+        <v>300</v>
       </c>
       <c r="U101" s="5" t="n">
-        <v>1854248</v>
+        <v>1753833</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>whtbld_ct</t>
+          <t>waist_circ</t>
         </is>
       </c>
       <c r="B102" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C102" s="7" t="n">
-        <v>43076</v>
+        <v>54019</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>3583</v>
+        <v>30185</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>10978</v>
+        <v>43939</v>
       </c>
       <c r="H102" s="7" t="n">
         <v>3</v>
       </c>
       <c r="I102" s="7" t="n">
-        <v>53674</v>
+        <v>53850</v>
       </c>
       <c r="J102" s="7" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="K102" s="7" t="n">
-        <v>60160</v>
+        <v>175209</v>
       </c>
       <c r="L102" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M102" s="7" t="n">
-        <v>22911</v>
+        <v>23633</v>
       </c>
       <c r="N102" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O102" s="7" t="n">
-        <v>3377</v>
+        <v>25409</v>
       </c>
       <c r="P102" s="7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Q102" s="7" t="n">
-        <v>3656</v>
+        <v>56543</v>
       </c>
       <c r="R102" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S102" s="7" t="n">
-        <v>623680</v>
+        <v>1619039</v>
       </c>
       <c r="T102" s="5" t="n">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="U102" s="5" t="n">
-        <v>825095</v>
+        <v>2081826</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
+          <t>waist_hip</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C103" s="7" t="n">
+        <v>106654</v>
+      </c>
+      <c r="D103" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E103" s="7" t="n">
+        <v>388</v>
+      </c>
+      <c r="F103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M103" s="7" t="n">
+        <v>23626</v>
+      </c>
+      <c r="N103" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="O103" s="7" t="n">
+        <v>23478</v>
+      </c>
+      <c r="P103" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q103" s="7" t="n">
+        <v>89497</v>
+      </c>
+      <c r="R103" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S103" s="7" t="n">
+        <v>1610605</v>
+      </c>
+      <c r="T103" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="U103" s="5" t="n">
+        <v>1854248</v>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>whtbld_ct</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C104" s="7" t="n">
+        <v>43076</v>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="7" t="n">
+        <v>3583</v>
+      </c>
+      <c r="F104" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G104" s="7" t="n">
+        <v>10978</v>
+      </c>
+      <c r="H104" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I104" s="7" t="n">
+        <v>53674</v>
+      </c>
+      <c r="J104" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K104" s="7" t="n">
+        <v>60160</v>
+      </c>
+      <c r="L104" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M104" s="7" t="n">
+        <v>22911</v>
+      </c>
+      <c r="N104" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O104" s="7" t="n">
+        <v>3377</v>
+      </c>
+      <c r="P104" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q104" s="7" t="n">
+        <v>3656</v>
+      </c>
+      <c r="R104" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S104" s="7" t="n">
+        <v>623680</v>
+      </c>
+      <c r="T104" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="U104" s="5" t="n">
+        <v>825095</v>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
           <t>willeb_fac</t>
         </is>
       </c>
-      <c r="B103" s="7" t="n">
+      <c r="B105" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C103" s="7" t="n">
+      <c r="C105" s="7" t="n">
         <v>14801</v>
       </c>
-      <c r="D103" s="7" t="n">
+      <c r="D105" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E103" s="7" t="n">
+      <c r="E105" s="7" t="n">
         <v>6928</v>
       </c>
-      <c r="F103" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K103" s="7" t="n">
+      <c r="F105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K105" s="7" t="n">
         <v>12072</v>
       </c>
-      <c r="L103" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q103" s="7" t="n">
+      <c r="L105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q105" s="7" t="n">
         <v>7391</v>
       </c>
-      <c r="R103" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" s="5" t="n">
+      <c r="R105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="U103" s="5" t="n">
+      <c r="U105" s="5" t="n">
         <v>41192</v>
       </c>
     </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="8" t="inlineStr">
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B104" s="9" t="n">
-        <v>1178</v>
-      </c>
-      <c r="C104" s="9" t="n">
-        <v>11553653</v>
-      </c>
-      <c r="D104" s="9" t="n">
-        <v>565</v>
-      </c>
-      <c r="E104" s="9" t="n">
-        <v>1035671</v>
-      </c>
-      <c r="F104" s="9" t="n">
-        <v>1349</v>
-      </c>
-      <c r="G104" s="9" t="n">
-        <v>4161858</v>
-      </c>
-      <c r="H104" s="9" t="n">
-        <v>112</v>
-      </c>
-      <c r="I104" s="9" t="n">
-        <v>2122662</v>
-      </c>
-      <c r="J104" s="9" t="n">
-        <v>3087</v>
-      </c>
-      <c r="K104" s="9" t="n">
-        <v>9071383</v>
-      </c>
-      <c r="L104" s="9" t="n">
-        <v>165</v>
-      </c>
-      <c r="M104" s="9" t="n">
-        <v>1772032</v>
-      </c>
-      <c r="N104" s="9" t="n">
-        <v>477</v>
-      </c>
-      <c r="O104" s="9" t="n">
-        <v>1643015</v>
-      </c>
-      <c r="P104" s="9" t="n">
-        <v>1196</v>
-      </c>
-      <c r="Q104" s="9" t="n">
-        <v>3908574</v>
-      </c>
-      <c r="R104" s="9" t="n">
+      <c r="B106" s="9" t="n">
+        <v>1180</v>
+      </c>
+      <c r="C106" s="9" t="n">
+        <v>11570834</v>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>566</v>
+      </c>
+      <c r="E106" s="9" t="n">
+        <v>1038752</v>
+      </c>
+      <c r="F106" s="9" t="n">
+        <v>1346</v>
+      </c>
+      <c r="G106" s="9" t="n">
+        <v>4149685</v>
+      </c>
+      <c r="H106" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="I106" s="9" t="n">
+        <v>2104709</v>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>3109</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>9247109</v>
+      </c>
+      <c r="L106" s="9" t="n">
+        <v>167</v>
+      </c>
+      <c r="M106" s="9" t="n">
+        <v>1795694</v>
+      </c>
+      <c r="N106" s="9" t="n">
+        <v>476</v>
+      </c>
+      <c r="O106" s="9" t="n">
+        <v>1639132</v>
+      </c>
+      <c r="P106" s="9" t="n">
+        <v>1201</v>
+      </c>
+      <c r="Q106" s="9" t="n">
+        <v>3916957</v>
+      </c>
+      <c r="R106" s="9" t="n">
         <v>360</v>
       </c>
-      <c r="S104" s="9" t="n">
+      <c r="S106" s="9" t="n">
         <v>34121402</v>
       </c>
-      <c r="T104" s="9" t="n">
-        <v>8489</v>
-      </c>
-      <c r="U104" s="9" t="n">
-        <v>69390250</v>
+      <c r="T106" s="9" t="n">
+        <v>8516</v>
+      </c>
+      <c r="U106" s="9" t="n">
+        <v>69584274</v>
       </c>
     </row>
   </sheetData>

--- a/tables/before_table.xlsx
+++ b/tables/before_table.xlsx
@@ -3589,52 +3589,52 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>87503</v>
+        <v>52873</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>64098</v>
+        <v>57425</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>31282</v>
+        <v>20005</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>82063</v>
+        <v>61881</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>124086</v>
+        <v>127166</v>
       </c>
       <c r="L46" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>34509</v>
+        <v>23178</v>
       </c>
       <c r="N46" s="7" t="n">
         <v>4</v>
       </c>
       <c r="O46" s="7" t="n">
-        <v>14702</v>
+        <v>14700</v>
       </c>
       <c r="P46" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q46" s="7" t="n">
-        <v>12201</v>
+        <v>8427</v>
       </c>
       <c r="R46" s="7" t="n">
         <v>0</v>
@@ -3643,10 +3643,10 @@
         <v>0</v>
       </c>
       <c r="T46" s="5" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="U46" s="5" t="n">
-        <v>450444</v>
+        <v>365655</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>82611</v>
+        <v>43161</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>0</v>
@@ -3668,16 +3668,16 @@
         <v>0</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>9673</v>
+        <v>4819</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>82063</v>
+        <v>61877</v>
       </c>
       <c r="J47" s="7" t="n">
         <v>24</v>
@@ -3686,10 +3686,10 @@
         <v>111182</v>
       </c>
       <c r="L47" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M47" s="7" t="n">
-        <v>34422</v>
+        <v>23077</v>
       </c>
       <c r="N47" s="7" t="n">
         <v>3</v>
@@ -3698,10 +3698,10 @@
         <v>11044</v>
       </c>
       <c r="P47" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q47" s="7" t="n">
-        <v>12550</v>
+        <v>8410</v>
       </c>
       <c r="R47" s="7" t="n">
         <v>0</v>
@@ -3710,10 +3710,10 @@
         <v>0</v>
       </c>
       <c r="T47" s="5" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="U47" s="5" t="n">
-        <v>343545</v>
+        <v>263570</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3857,52 +3857,52 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>73309</v>
+        <v>52873</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>57425</v>
+        <v>64098</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>24859</v>
+        <v>20004</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>82067</v>
+        <v>61877</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>127166</v>
+        <v>124086</v>
       </c>
       <c r="L50" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>34509</v>
+        <v>23178</v>
       </c>
       <c r="N50" s="7" t="n">
         <v>4</v>
       </c>
       <c r="O50" s="7" t="n">
-        <v>14700</v>
+        <v>14702</v>
       </c>
       <c r="P50" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q50" s="7" t="n">
-        <v>12216</v>
+        <v>8412</v>
       </c>
       <c r="R50" s="7" t="n">
         <v>0</v>
@@ -3911,10 +3911,10 @@
         <v>0</v>
       </c>
       <c r="T50" s="5" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="U50" s="5" t="n">
-        <v>426251</v>
+        <v>369230</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -7609,10 +7609,10 @@
         </is>
       </c>
       <c r="B106" s="9" t="n">
-        <v>1180</v>
+        <v>1167</v>
       </c>
       <c r="C106" s="9" t="n">
-        <v>11570834</v>
+        <v>11476318</v>
       </c>
       <c r="D106" s="9" t="n">
         <v>566</v>
@@ -7621,16 +7621,16 @@
         <v>1038752</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>1346</v>
+        <v>1341</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>4149685</v>
+        <v>4128699</v>
       </c>
       <c r="H106" s="9" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>2104709</v>
+        <v>2044151</v>
       </c>
       <c r="J106" s="9" t="n">
         <v>3109</v>
@@ -7639,10 +7639,10 @@
         <v>9247109</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="M106" s="9" t="n">
-        <v>1795694</v>
+        <v>1761687</v>
       </c>
       <c r="N106" s="9" t="n">
         <v>476</v>
@@ -7651,10 +7651,10 @@
         <v>1639132</v>
       </c>
       <c r="P106" s="9" t="n">
-        <v>1201</v>
+        <v>1192</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>3916957</v>
+        <v>3905239</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>360</v>
@@ -7663,10 +7663,10 @@
         <v>34121402</v>
       </c>
       <c r="T106" s="9" t="n">
-        <v>8516</v>
+        <v>8483</v>
       </c>
       <c r="U106" s="9" t="n">
-        <v>69584274</v>
+        <v>69362489</v>
       </c>
     </row>
   </sheetData>

--- a/tables/before_table.xlsx
+++ b/tables/before_table.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U106"/>
+  <dimension ref="A1:U105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -836,95 +836,95 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>SdohObservations</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>31245</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>13125</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>76998</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>23307</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>34488</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>14099</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>51894</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>413856</v>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>albumin_bld</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>17974</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>3583</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>32360</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>61223</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>659012</v>
+        <v>115140</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>albumin_bld</t>
+          <t>albumin_creatinine</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>17974</v>
+        <v>0</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>3583</v>
+        <v>5927</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>32360</v>
+        <v>0</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
@@ -933,28 +933,28 @@
         <v>0</v>
       </c>
       <c r="J6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>23162</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <v>4810</v>
+      </c>
+      <c r="P6" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="K6" s="7" t="n">
-        <v>61223</v>
-      </c>
-      <c r="L6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="Q6" s="7" t="n">
-        <v>0</v>
+        <v>45400</v>
       </c>
       <c r="R6" s="7" t="n">
         <v>0</v>
@@ -963,29 +963,29 @@
         <v>0</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="U6" s="5" t="n">
-        <v>115140</v>
+        <v>79299</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>albumin_creatinine</t>
+          <t>albumin_urine</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>0</v>
+        <v>19036</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>5927</v>
+        <v>5930</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>0</v>
@@ -1000,28 +1000,28 @@
         <v>0</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0</v>
+        <v>96443</v>
       </c>
       <c r="L7" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>23162</v>
+        <v>23161</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>4810</v>
+        <v>15128</v>
       </c>
       <c r="P7" s="7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>45400</v>
+        <v>48594</v>
       </c>
       <c r="R7" s="7" t="n">
         <v>0</v>
@@ -1030,83 +1030,83 @@
         <v>0</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>79299</v>
+        <v>208292</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>albumin_urine</t>
+          <t>alcohol_servings</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>70762</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>77508</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>48863</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="7" t="n">
-        <v>19036</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>5930</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="K8" s="7" t="n">
-        <v>96443</v>
-      </c>
-      <c r="L8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>23161</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>9</v>
-      </c>
       <c r="O8" s="7" t="n">
-        <v>15128</v>
+        <v>13255</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>48594</v>
+        <v>77728</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>0</v>
+        <v>480675</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="U8" s="5" t="n">
-        <v>208292</v>
+        <v>768791</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>alcohol_servings</t>
+          <t>alt_sgpt</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
@@ -1116,28 +1116,28 @@
         <v>0</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>70762</v>
+        <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>77508</v>
+        <v>0</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>48863</v>
+        <v>0</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0</v>
+        <v>61921</v>
       </c>
       <c r="L9" s="7" t="n">
         <v>0</v>
@@ -1146,34 +1146,34 @@
         <v>0</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>13255</v>
+        <v>0</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>77728</v>
+        <v>0</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>480675</v>
+        <v>0</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v>768791</v>
+        <v>61921</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>alt_sgpt</t>
+          <t>apnea_hypop_index</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
@@ -1189,10 +1189,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0</v>
+        <v>204354</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>0</v>
@@ -1201,16 +1201,16 @@
         <v>0</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>61921</v>
+        <v>6355</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0</v>
+        <v>22317</v>
       </c>
       <c r="N10" s="7" t="n">
         <v>0</v>
@@ -1231,16 +1231,16 @@
         <v>0</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>12</v>
+        <v>203</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>61921</v>
+        <v>233026</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>apnea_hypop_index</t>
+          <t>ast_sgot</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
@@ -1250,16 +1250,16 @@
         <v>0</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0</v>
+        <v>3581</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>204354</v>
+        <v>0</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>0</v>
@@ -1268,16 +1268,16 @@
         <v>0</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>6355</v>
+        <v>60437</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>22317</v>
+        <v>0</v>
       </c>
       <c r="N11" s="7" t="n">
         <v>0</v>
@@ -1298,16 +1298,16 @@
         <v>0</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>203</v>
+        <v>12</v>
       </c>
       <c r="U11" s="5" t="n">
-        <v>233026</v>
+        <v>64018</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>ast_sgot</t>
+          <t>basophil_ncnc_bld</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
@@ -1317,10 +1317,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3581</v>
+        <v>340</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>0</v>
@@ -1329,22 +1329,22 @@
         <v>0</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0</v>
+        <v>53587</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>60437</v>
+        <v>32540</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0</v>
+        <v>22894</v>
       </c>
       <c r="N12" s="7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>0</v>
+        <v>3126</v>
       </c>
       <c r="R12" s="7" t="n">
         <v>0</v>
@@ -1365,284 +1365,284 @@
         <v>0</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U12" s="5" t="n">
-        <v>64018</v>
+        <v>112487</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>basophil_ncnc_bld</t>
+          <t>bdy_hgt</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>0</v>
+        <v>95859</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>340</v>
+        <v>40007</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0</v>
+        <v>34019</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>3</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>53587</v>
+        <v>64251</v>
       </c>
       <c r="J13" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>282446</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>33201</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>40969</v>
+      </c>
+      <c r="P13" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q13" s="7" t="n">
+        <v>68674</v>
+      </c>
+      <c r="R13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K13" s="7" t="n">
-        <v>32540</v>
-      </c>
-      <c r="L13" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>22894</v>
-      </c>
-      <c r="N13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="7" t="n">
-        <v>3126</v>
-      </c>
-      <c r="R13" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="S13" s="7" t="n">
-        <v>0</v>
+        <v>1852916</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="U13" s="5" t="n">
-        <v>112487</v>
+        <v>2512342</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>bdy_hgt</t>
+          <t>bdy_temp</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>95859</v>
+        <v>0</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>40007</v>
+        <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>34019</v>
+        <v>0</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>64251</v>
+        <v>0</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>282446</v>
+        <v>0</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>33201</v>
+        <v>0</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>40969</v>
+        <v>0</v>
       </c>
       <c r="P14" s="7" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>68674</v>
+        <v>7647</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>1852916</v>
+        <v>0</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>2512342</v>
+        <v>7647</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>bdy_temp</t>
+          <t>bdy_wgt</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0</v>
+        <v>63657</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0</v>
+        <v>36242</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0</v>
+        <v>57898</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0</v>
+        <v>64250</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0</v>
+        <v>239196</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0</v>
+        <v>42107</v>
       </c>
       <c r="N15" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>0</v>
+        <v>23318</v>
       </c>
       <c r="P15" s="7" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>7647</v>
+        <v>41958</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>0</v>
+        <v>2297360</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>2</v>
+        <v>158</v>
       </c>
       <c r="U15" s="5" t="n">
-        <v>7647</v>
+        <v>2865986</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>bdy_wgt</t>
+          <t>bilirubin_con</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>63657</v>
+        <v>0</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>36242</v>
+        <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>57898</v>
+        <v>0</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>64250</v>
+        <v>0</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>239196</v>
+        <v>16127</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>42107</v>
+        <v>0</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>23318</v>
+        <v>0</v>
       </c>
       <c r="P16" s="7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>41958</v>
+        <v>0</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>2297360</v>
+        <v>0</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>158</v>
+        <v>2</v>
       </c>
       <c r="U16" s="5" t="n">
-        <v>2865986</v>
+        <v>16127</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>bilirubin_con</t>
+          <t>bilirubin_tot</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0</v>
+        <v>3583</v>
       </c>
       <c r="F17" s="7" t="n">
         <v>0</v>
@@ -1670,10 +1670,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>16127</v>
+        <v>61431</v>
       </c>
       <c r="L17" s="7" t="n">
         <v>0</v>
@@ -1700,230 +1700,230 @@
         <v>0</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="U17" s="5" t="n">
-        <v>16127</v>
+        <v>65014</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>bilirubin_tot</t>
+          <t>blood_pressure</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>0</v>
+        <v>1003408</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>3583</v>
+        <v>7596</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0</v>
+        <v>130363</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>0</v>
+        <v>84438</v>
       </c>
       <c r="J18" s="7" t="n">
+        <v>156</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>408522</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>35476</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <v>97134</v>
+      </c>
+      <c r="P18" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q18" s="7" t="n">
+        <v>89867</v>
+      </c>
+      <c r="R18" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="K18" s="7" t="n">
-        <v>61431</v>
-      </c>
-      <c r="L18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" s="7" t="n">
-        <v>0</v>
+        <v>3726863</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>13</v>
+        <v>391</v>
       </c>
       <c r="U18" s="5" t="n">
-        <v>65014</v>
+        <v>5583667</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>blood_pressure</t>
+          <t>bmi</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>1003408</v>
+        <v>15611</v>
       </c>
       <c r="D19" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>20435</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>33989</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>64250</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>214420</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>23629</v>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="O19" s="7" t="n">
+        <v>19440</v>
+      </c>
+      <c r="P19" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q19" s="7" t="n">
+        <v>59750</v>
+      </c>
+      <c r="R19" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="7" t="n">
-        <v>7596</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>130363</v>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>84438</v>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>156</v>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>408522</v>
-      </c>
-      <c r="L19" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M19" s="7" t="n">
-        <v>35476</v>
-      </c>
-      <c r="N19" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="O19" s="7" t="n">
-        <v>97134</v>
-      </c>
-      <c r="P19" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q19" s="7" t="n">
-        <v>89867</v>
-      </c>
-      <c r="R19" s="7" t="n">
-        <v>12</v>
-      </c>
       <c r="S19" s="7" t="n">
-        <v>3726863</v>
+        <v>1849280</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>391</v>
+        <v>127</v>
       </c>
       <c r="U19" s="5" t="n">
-        <v>5583667</v>
+        <v>2300804</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>bmi</t>
+          <t>bnp</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>15611</v>
+        <v>39457</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>20435</v>
+        <v>1177</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>33989</v>
+        <v>0</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>64250</v>
+        <v>0</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>214420</v>
+        <v>11965</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>23629</v>
+        <v>0</v>
       </c>
       <c r="N20" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>19440</v>
+        <v>3544</v>
       </c>
       <c r="P20" s="7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>59750</v>
+        <v>0</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>1849280</v>
+        <v>7028</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="U20" s="5" t="n">
-        <v>2300804</v>
+        <v>63171</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>bnp</t>
+          <t>bun</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>39457</v>
+        <v>14918</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>1177</v>
+        <v>0</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0</v>
@@ -1938,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>11965</v>
+        <v>40549</v>
       </c>
       <c r="L21" s="7" t="n">
         <v>0</v>
@@ -1953,7 +1953,7 @@
         <v>1</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>3544</v>
+        <v>2773</v>
       </c>
       <c r="P21" s="7" t="n">
         <v>0</v>
@@ -1962,41 +1962,41 @@
         <v>0</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>7028</v>
+        <v>5928</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="U21" s="5" t="n">
-        <v>63171</v>
+        <v>64168</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>bun</t>
+          <t>cac_score</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>14918</v>
+        <v>0</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0</v>
+        <v>17133</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0</v>
+        <v>12170</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>0</v>
@@ -2005,10 +2005,10 @@
         <v>0</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>40549</v>
+        <v>36330</v>
       </c>
       <c r="L22" s="7" t="n">
         <v>0</v>
@@ -2020,31 +2020,31 @@
         <v>1</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>2773</v>
+        <v>2144</v>
       </c>
       <c r="P22" s="7" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>0</v>
+        <v>185186</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>5928</v>
+        <v>0</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="U22" s="5" t="n">
-        <v>64168</v>
+        <v>252963</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>cac_score</t>
+          <t>cac_volume</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
@@ -2054,16 +2054,16 @@
         <v>0</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>17133</v>
+        <v>0</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>12170</v>
+        <v>0</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>0</v>
@@ -2072,10 +2072,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>36330</v>
+        <v>2851</v>
       </c>
       <c r="L23" s="7" t="n">
         <v>0</v>
@@ -2084,16 +2084,16 @@
         <v>0</v>
       </c>
       <c r="N23" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>2144</v>
+        <v>0</v>
       </c>
       <c r="P23" s="7" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>185186</v>
+        <v>145982</v>
       </c>
       <c r="R23" s="7" t="n">
         <v>0</v>
@@ -2102,23 +2102,23 @@
         <v>0</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="U23" s="5" t="n">
-        <v>252963</v>
+        <v>148833</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>cac_volume</t>
+          <t>carotid_imt</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>0</v>
+        <v>340092</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>0</v>
+        <v>59398</v>
       </c>
       <c r="H24" s="7" t="n">
         <v>0</v>
@@ -2139,10 +2139,10 @@
         <v>0</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>2851</v>
+        <v>20515</v>
       </c>
       <c r="L24" s="7" t="n">
         <v>0</v>
@@ -2151,16 +2151,16 @@
         <v>0</v>
       </c>
       <c r="N24" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>0</v>
+        <v>19862</v>
       </c>
       <c r="P24" s="7" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>145982</v>
+        <v>13345</v>
       </c>
       <c r="R24" s="7" t="n">
         <v>0</v>
@@ -2169,23 +2169,23 @@
         <v>0</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="U24" s="5" t="n">
-        <v>148833</v>
+        <v>453212</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>carotid_imt</t>
+          <t>carotid_sten_left</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>340092</v>
+        <v>165</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>0</v>
@@ -2194,10 +2194,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>59398</v>
+        <v>15520</v>
       </c>
       <c r="H25" s="7" t="n">
         <v>0</v>
@@ -2206,10 +2206,10 @@
         <v>0</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>20515</v>
+        <v>10779</v>
       </c>
       <c r="L25" s="7" t="n">
         <v>0</v>
@@ -2218,16 +2218,16 @@
         <v>0</v>
       </c>
       <c r="N25" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>19862</v>
+        <v>0</v>
       </c>
       <c r="P25" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>13345</v>
+        <v>12791</v>
       </c>
       <c r="R25" s="7" t="n">
         <v>0</v>
@@ -2236,23 +2236,23 @@
         <v>0</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="U25" s="5" t="n">
-        <v>453212</v>
+        <v>39255</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>carotid_sten_left</t>
+          <t>carotid_sten_right</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>0</v>
@@ -2264,7 +2264,7 @@
         <v>3</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>15520</v>
+        <v>15537</v>
       </c>
       <c r="H26" s="7" t="n">
         <v>0</v>
@@ -2276,7 +2276,7 @@
         <v>2</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>10779</v>
+        <v>10786</v>
       </c>
       <c r="L26" s="7" t="n">
         <v>0</v>
@@ -2306,20 +2306,20 @@
         <v>8</v>
       </c>
       <c r="U26" s="5" t="n">
-        <v>39255</v>
+        <v>39276</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>carotid_sten_right</t>
+          <t>cd40</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
         <v>0</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>15537</v>
+        <v>0</v>
       </c>
       <c r="H27" s="7" t="n">
         <v>0</v>
@@ -2340,10 +2340,10 @@
         <v>0</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>10786</v>
+        <v>0</v>
       </c>
       <c r="L27" s="7" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>2</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>12791</v>
+        <v>7393</v>
       </c>
       <c r="R27" s="7" t="n">
         <v>0</v>
@@ -2370,29 +2370,29 @@
         <v>0</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="U27" s="5" t="n">
-        <v>39276</v>
+        <v>7393</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>cd40</t>
+          <t>cesd_score</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>0</v>
+        <v>27247</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0</v>
+        <v>8987</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>0</v>
@@ -2407,28 +2407,28 @@
         <v>0</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0</v>
+        <v>23495</v>
       </c>
       <c r="N28" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>0</v>
+        <v>6423</v>
       </c>
       <c r="P28" s="7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>7393</v>
+        <v>47837</v>
       </c>
       <c r="R28" s="7" t="n">
         <v>0</v>
@@ -2437,29 +2437,29 @@
         <v>0</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="U28" s="5" t="n">
-        <v>7393</v>
+        <v>114133</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>cesd_score</t>
+          <t>chloride_bld</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>27247</v>
+        <v>5827</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>8987</v>
+        <v>0</v>
       </c>
       <c r="F29" s="7" t="n">
         <v>0</v>
@@ -2474,28 +2474,28 @@
         <v>0</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>144</v>
+        <v>19616</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>23495</v>
+        <v>0</v>
       </c>
       <c r="N29" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>6423</v>
+        <v>3839</v>
       </c>
       <c r="P29" s="7" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>47837</v>
+        <v>6129</v>
       </c>
       <c r="R29" s="7" t="n">
         <v>0</v>
@@ -2504,163 +2504,163 @@
         <v>0</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="U29" s="5" t="n">
-        <v>114133</v>
+        <v>35411</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>chloride_bld</t>
+          <t>cig_smok</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>173641</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>5084</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>84173</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>66043</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>225600</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>28449</v>
+      </c>
+      <c r="N30" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O30" s="7" t="n">
+        <v>12859</v>
+      </c>
+      <c r="P30" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>87578</v>
+      </c>
+      <c r="R30" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="7" t="n">
-        <v>5827</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>19616</v>
-      </c>
-      <c r="L30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" s="7" t="n">
-        <v>3839</v>
-      </c>
-      <c r="P30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q30" s="7" t="n">
-        <v>6129</v>
-      </c>
-      <c r="R30" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" s="7" t="n">
-        <v>0</v>
+        <v>141363</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="U30" s="5" t="n">
-        <v>35411</v>
+        <v>824790</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>cig_smok</t>
+          <t>creat_bld</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>173641</v>
+        <v>220393</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>5084</v>
+        <v>6451</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>84173</v>
+        <v>0</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>66043</v>
+        <v>0</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>225600</v>
+        <v>159845</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>28449</v>
+        <v>23654</v>
       </c>
       <c r="N31" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="O31" s="7" t="n">
+        <v>23763</v>
+      </c>
+      <c r="P31" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="O31" s="7" t="n">
-        <v>12859</v>
-      </c>
-      <c r="P31" s="7" t="n">
-        <v>31</v>
-      </c>
       <c r="Q31" s="7" t="n">
-        <v>87578</v>
+        <v>9186</v>
       </c>
       <c r="R31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="S31" s="7" t="n">
-        <v>141363</v>
+        <v>5987</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>160</v>
+        <v>103</v>
       </c>
       <c r="U31" s="5" t="n">
-        <v>824790</v>
+        <v>449279</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>creat_bld</t>
+          <t>creat_urin</t>
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>220393</v>
+        <v>8779</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>6451</v>
+        <v>6591</v>
       </c>
       <c r="F32" s="7" t="n">
         <v>0</v>
@@ -2675,65 +2675,65 @@
         <v>0</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>159845</v>
+        <v>87104</v>
       </c>
       <c r="L32" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>23654</v>
+        <v>23618</v>
       </c>
       <c r="N32" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O32" s="7" t="n">
-        <v>23763</v>
+        <v>23244</v>
       </c>
       <c r="P32" s="7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q32" s="7" t="n">
-        <v>9186</v>
+        <v>48092</v>
       </c>
       <c r="R32" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" s="7" t="n">
-        <v>5987</v>
+        <v>0</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="U32" s="5" t="n">
-        <v>449279</v>
+        <v>197428</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>creat_urin</t>
+          <t>crp</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>8779</v>
+        <v>20542</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>3</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>6591</v>
+        <v>9585</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>0</v>
+        <v>20288</v>
       </c>
       <c r="H33" s="7" t="n">
         <v>0</v>
@@ -2742,28 +2742,28 @@
         <v>0</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>87104</v>
+        <v>109598</v>
       </c>
       <c r="L33" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>23618</v>
+        <v>23651</v>
       </c>
       <c r="N33" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>23244</v>
+        <v>27442</v>
       </c>
       <c r="P33" s="7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q33" s="7" t="n">
-        <v>48092</v>
+        <v>23290</v>
       </c>
       <c r="R33" s="7" t="n">
         <v>0</v>
@@ -2772,90 +2772,90 @@
         <v>0</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="U33" s="5" t="n">
-        <v>197428</v>
+        <v>234396</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>crp</t>
+          <t>cysc_bld</t>
         </is>
       </c>
       <c r="B34" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>69181</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>4417</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" s="7" t="n">
+        <v>10725</v>
+      </c>
+      <c r="L34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>23569</v>
+      </c>
+      <c r="N34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="7" t="n">
+        <v>3783</v>
+      </c>
+      <c r="P34" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C34" s="7" t="n">
-        <v>20542</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>9585</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>20288</v>
-      </c>
-      <c r="H34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="7" t="n">
+      <c r="Q34" s="7" t="n">
+        <v>21600</v>
+      </c>
+      <c r="R34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="K34" s="7" t="n">
-        <v>109598</v>
-      </c>
-      <c r="L34" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M34" s="7" t="n">
-        <v>23651</v>
-      </c>
-      <c r="N34" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="O34" s="7" t="n">
-        <v>27442</v>
-      </c>
-      <c r="P34" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q34" s="7" t="n">
-        <v>23290</v>
-      </c>
-      <c r="R34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="5" t="n">
-        <v>51</v>
-      </c>
       <c r="U34" s="5" t="n">
-        <v>234396</v>
+        <v>133275</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>cysc_bld</t>
+          <t>d_dimer</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>69181</v>
+        <v>12422</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>0</v>
@@ -2864,10 +2864,10 @@
         <v>0</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>4417</v>
+        <v>10710</v>
       </c>
       <c r="H35" s="7" t="n">
         <v>0</v>
@@ -2879,25 +2879,25 @@
         <v>2</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>10725</v>
+        <v>10868</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>23569</v>
+        <v>0</v>
       </c>
       <c r="N35" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>3783</v>
+        <v>0</v>
       </c>
       <c r="P35" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q35" s="7" t="n">
-        <v>21600</v>
+        <v>22453</v>
       </c>
       <c r="R35" s="7" t="n">
         <v>0</v>
@@ -2906,90 +2906,90 @@
         <v>0</v>
       </c>
       <c r="T35" s="5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U35" s="5" t="n">
-        <v>133275</v>
+        <v>56453</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>d_dimer</t>
+          <t>edu_lvl</t>
         </is>
       </c>
       <c r="B36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>31245</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>5515</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>66007</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>23307</v>
+      </c>
+      <c r="L36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>23644</v>
+      </c>
+      <c r="N36" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="7" t="n">
-        <v>12422</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>10710</v>
-      </c>
-      <c r="H36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>10868</v>
-      </c>
-      <c r="L36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="O36" s="7" t="n">
-        <v>0</v>
+        <v>3871</v>
       </c>
       <c r="P36" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q36" s="7" t="n">
-        <v>22453</v>
+        <v>8905</v>
       </c>
       <c r="R36" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" s="7" t="n">
-        <v>0</v>
+        <v>142131</v>
       </c>
       <c r="T36" s="5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="U36" s="5" t="n">
-        <v>56453</v>
+        <v>304625</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>edu_lvl</t>
+          <t>egfr</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>0</v>
+        <v>209569</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
@@ -2998,10 +2998,10 @@
         <v>0</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>5515</v>
+        <v>0</v>
       </c>
       <c r="H37" s="7" t="n">
         <v>0</v>
@@ -3016,22 +3016,22 @@
         <v>0</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M37" s="7" t="n">
-        <v>0</v>
+        <v>34095</v>
       </c>
       <c r="N37" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>0</v>
+        <v>11561</v>
       </c>
       <c r="P37" s="7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q37" s="7" t="n">
-        <v>0</v>
+        <v>69891</v>
       </c>
       <c r="R37" s="7" t="n">
         <v>0</v>
@@ -3040,29 +3040,29 @@
         <v>0</v>
       </c>
       <c r="T37" s="5" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="U37" s="5" t="n">
-        <v>5515</v>
+        <v>325116</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>egfr</t>
+          <t>eosinophil_ncnc_bld</t>
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>209569</v>
+        <v>0</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="F38" s="7" t="n">
         <v>0</v>
@@ -3071,34 +3071,34 @@
         <v>0</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>0</v>
+        <v>53588</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0</v>
+        <v>32540</v>
       </c>
       <c r="L38" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M38" s="7" t="n">
-        <v>34095</v>
+        <v>22910</v>
       </c>
       <c r="N38" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O38" s="7" t="n">
-        <v>11561</v>
+        <v>0</v>
       </c>
       <c r="P38" s="7" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Q38" s="7" t="n">
-        <v>69891</v>
+        <v>3196</v>
       </c>
       <c r="R38" s="7" t="n">
         <v>0</v>
@@ -3107,16 +3107,16 @@
         <v>0</v>
       </c>
       <c r="T38" s="5" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="U38" s="5" t="n">
-        <v>325116</v>
+        <v>112606</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>eosinophil_ncnc_bld</t>
+          <t>eselectin</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
@@ -3126,10 +3126,10 @@
         <v>0</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>372</v>
+        <v>0</v>
       </c>
       <c r="F39" s="7" t="n">
         <v>0</v>
@@ -3138,34 +3138,34 @@
         <v>0</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>53588</v>
+        <v>0</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>32540</v>
+        <v>7783</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M39" s="7" t="n">
-        <v>22910</v>
+        <v>0</v>
       </c>
       <c r="N39" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>0</v>
+        <v>5581</v>
       </c>
       <c r="P39" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q39" s="7" t="n">
-        <v>3196</v>
+        <v>13840</v>
       </c>
       <c r="R39" s="7" t="n">
         <v>0</v>
@@ -3174,35 +3174,35 @@
         <v>0</v>
       </c>
       <c r="T39" s="5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="U39" s="5" t="n">
-        <v>112606</v>
+        <v>27204</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>eselectin</t>
+          <t>factor_7</t>
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>0</v>
+        <v>15472</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>0</v>
+        <v>4636</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>0</v>
+        <v>25635</v>
       </c>
       <c r="H40" s="7" t="n">
         <v>0</v>
@@ -3211,10 +3211,10 @@
         <v>0</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>7783</v>
+        <v>27175</v>
       </c>
       <c r="L40" s="7" t="n">
         <v>0</v>
@@ -3223,187 +3223,187 @@
         <v>0</v>
       </c>
       <c r="N40" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O40" s="7" t="n">
-        <v>5581</v>
+        <v>0</v>
       </c>
       <c r="P40" s="7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="7" t="n">
-        <v>13840</v>
+        <v>0</v>
       </c>
       <c r="R40" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S40" s="7" t="n">
-        <v>0</v>
+        <v>61040</v>
       </c>
       <c r="T40" s="5" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="U40" s="5" t="n">
-        <v>27204</v>
+        <v>133958</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>factor_7</t>
+          <t>factor_8</t>
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>15472</v>
+        <v>14793</v>
       </c>
       <c r="D41" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>2989</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>4817</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E41" s="7" t="n">
-        <v>4636</v>
-      </c>
-      <c r="F41" s="7" t="n">
+      <c r="Q41" s="7" t="n">
+        <v>20145</v>
+      </c>
+      <c r="R41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="G41" s="7" t="n">
-        <v>25635</v>
-      </c>
-      <c r="H41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>27175</v>
-      </c>
-      <c r="L41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="S41" s="7" t="n">
-        <v>61040</v>
-      </c>
-      <c r="T41" s="5" t="n">
-        <v>22</v>
-      </c>
       <c r="U41" s="5" t="n">
-        <v>133958</v>
+        <v>42744</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>factor_8</t>
+          <t>fam_income</t>
         </is>
       </c>
       <c r="B42" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>27593</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>13125</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>9471</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>55035</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K42" s="7" t="n">
+        <v>49939</v>
+      </c>
+      <c r="L42" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C42" s="7" t="n">
-        <v>14793</v>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>2989</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>4817</v>
-      </c>
-      <c r="H42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" s="7" t="n">
-        <v>0</v>
+        <v>10844</v>
       </c>
       <c r="N42" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O42" s="7" t="n">
-        <v>0</v>
+        <v>10228</v>
       </c>
       <c r="P42" s="7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Q42" s="7" t="n">
-        <v>20145</v>
+        <v>42989</v>
       </c>
       <c r="R42" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S42" s="7" t="n">
-        <v>0</v>
+        <v>271725</v>
       </c>
       <c r="T42" s="5" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="U42" s="5" t="n">
-        <v>42744</v>
+        <v>490949</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>fam_income</t>
+          <t>fast_gluc_bld</t>
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>27593</v>
+        <v>65854</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0</v>
+        <v>6434</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>9471</v>
+        <v>7205</v>
       </c>
       <c r="H43" s="7" t="n">
         <v>0</v>
@@ -3412,28 +3412,28 @@
         <v>0</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>49939</v>
+        <v>83472</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43" s="7" t="n">
-        <v>0</v>
+        <v>23653</v>
       </c>
       <c r="N43" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O43" s="7" t="n">
-        <v>0</v>
+        <v>17868</v>
       </c>
       <c r="P43" s="7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q43" s="7" t="n">
-        <v>0</v>
+        <v>68476</v>
       </c>
       <c r="R43" s="7" t="n">
         <v>0</v>
@@ -3442,35 +3442,35 @@
         <v>0</v>
       </c>
       <c r="T43" s="5" t="n">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="U43" s="5" t="n">
-        <v>87003</v>
+        <v>272962</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>fast_gluc_bld</t>
+          <t>ferritin</t>
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>65854</v>
+        <v>0</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>6434</v>
+        <v>0</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>7205</v>
+        <v>0</v>
       </c>
       <c r="H44" s="7" t="n">
         <v>0</v>
@@ -3479,28 +3479,28 @@
         <v>0</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>83472</v>
+        <v>0</v>
       </c>
       <c r="L44" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>23653</v>
+        <v>23448</v>
       </c>
       <c r="N44" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O44" s="7" t="n">
-        <v>17868</v>
+        <v>3811</v>
       </c>
       <c r="P44" s="7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="7" t="n">
-        <v>68476</v>
+        <v>0</v>
       </c>
       <c r="R44" s="7" t="n">
         <v>0</v>
@@ -3509,65 +3509,65 @@
         <v>0</v>
       </c>
       <c r="T44" s="5" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="U44" s="5" t="n">
-        <v>272962</v>
+        <v>27259</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>ferritin</t>
+          <t>fev1</t>
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>0</v>
+        <v>52873</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>0</v>
+        <v>57425</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>0</v>
+        <v>20005</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>0</v>
+        <v>61881</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0</v>
+        <v>127166</v>
       </c>
       <c r="L45" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M45" s="7" t="n">
-        <v>23448</v>
+        <v>23178</v>
       </c>
       <c r="N45" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O45" s="7" t="n">
-        <v>3811</v>
+        <v>14700</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q45" s="7" t="n">
-        <v>0</v>
+        <v>8427</v>
       </c>
       <c r="R45" s="7" t="n">
         <v>0</v>
@@ -3576,65 +3576,65 @@
         <v>0</v>
       </c>
       <c r="T45" s="5" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="U45" s="5" t="n">
-        <v>27259</v>
+        <v>365655</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>fev1</t>
+          <t>fev1_fvc</t>
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>52873</v>
+        <v>43161</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>57425</v>
+        <v>0</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>20005</v>
+        <v>4819</v>
       </c>
       <c r="H46" s="7" t="n">
         <v>3</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>61881</v>
+        <v>61877</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>127166</v>
+        <v>111182</v>
       </c>
       <c r="L46" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>23178</v>
+        <v>23077</v>
       </c>
       <c r="N46" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O46" s="7" t="n">
-        <v>14700</v>
+        <v>11044</v>
       </c>
       <c r="P46" s="7" t="n">
         <v>6</v>
       </c>
       <c r="Q46" s="7" t="n">
-        <v>8427</v>
+        <v>8410</v>
       </c>
       <c r="R46" s="7" t="n">
         <v>0</v>
@@ -3643,102 +3643,102 @@
         <v>0</v>
       </c>
       <c r="T46" s="5" t="n">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="U46" s="5" t="n">
-        <v>365655</v>
+        <v>263570</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>fev1_fvc</t>
+          <t>fibrin</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>43161</v>
+        <v>15767</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0</v>
+        <v>10916</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>4819</v>
+        <v>25124</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>61877</v>
+        <v>0</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>111182</v>
+        <v>53858</v>
       </c>
       <c r="L47" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M47" s="7" t="n">
-        <v>23077</v>
+        <v>0</v>
       </c>
       <c r="N47" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O47" s="7" t="n">
-        <v>11044</v>
+        <v>0</v>
       </c>
       <c r="P47" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q47" s="7" t="n">
-        <v>8410</v>
+        <v>21121</v>
       </c>
       <c r="R47" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S47" s="7" t="n">
-        <v>0</v>
+        <v>46006</v>
       </c>
       <c r="T47" s="5" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="U47" s="5" t="n">
-        <v>263570</v>
+        <v>172792</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>fibrin</t>
+          <t>fruit_serving</t>
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>15767</v>
+        <v>175886</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>10916</v>
+        <v>40644</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>25124</v>
+        <v>5690</v>
       </c>
       <c r="H48" s="7" t="n">
         <v>0</v>
@@ -3747,10 +3747,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>53858</v>
+        <v>375548</v>
       </c>
       <c r="L48" s="7" t="n">
         <v>0</v>
@@ -3765,181 +3765,181 @@
         <v>0</v>
       </c>
       <c r="P48" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="7" t="n">
-        <v>21121</v>
+        <v>8534</v>
       </c>
       <c r="R48" s="7" t="n">
         <v>3</v>
       </c>
       <c r="S48" s="7" t="n">
-        <v>46006</v>
+        <v>1018181</v>
       </c>
       <c r="T48" s="5" t="n">
-        <v>39</v>
+        <v>168</v>
       </c>
       <c r="U48" s="5" t="n">
-        <v>172792</v>
+        <v>1624483</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>fruit_serving</t>
+          <t>fvc</t>
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>175886</v>
+        <v>52873</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>40644</v>
+        <v>64098</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>5690</v>
+        <v>20004</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>0</v>
+        <v>61877</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>375548</v>
+        <v>124086</v>
       </c>
       <c r="L49" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0</v>
+        <v>23178</v>
       </c>
       <c r="N49" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O49" s="7" t="n">
-        <v>0</v>
+        <v>14702</v>
       </c>
       <c r="P49" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q49" s="7" t="n">
-        <v>8534</v>
+        <v>8412</v>
       </c>
       <c r="R49" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S49" s="7" t="n">
-        <v>1018181</v>
+        <v>0</v>
       </c>
       <c r="T49" s="5" t="n">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="U49" s="5" t="n">
-        <v>1624483</v>
+        <v>369230</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>fvc</t>
+          <t>glucose_bld</t>
         </is>
       </c>
       <c r="B50" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>211779</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>6763</v>
+      </c>
+      <c r="F50" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="C50" s="7" t="n">
-        <v>52873</v>
-      </c>
-      <c r="D50" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="E50" s="7" t="n">
-        <v>64098</v>
-      </c>
-      <c r="F50" s="7" t="n">
-        <v>5</v>
-      </c>
       <c r="G50" s="7" t="n">
-        <v>20004</v>
+        <v>25155</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>61877</v>
+        <v>0</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>124086</v>
+        <v>292594</v>
       </c>
       <c r="L50" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>23178</v>
+        <v>0</v>
       </c>
       <c r="N50" s="7" t="n">
         <v>4</v>
       </c>
       <c r="O50" s="7" t="n">
-        <v>14702</v>
+        <v>10187</v>
       </c>
       <c r="P50" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q50" s="7" t="n">
-        <v>8412</v>
+        <v>358</v>
       </c>
       <c r="R50" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S50" s="7" t="n">
-        <v>0</v>
+        <v>46598</v>
       </c>
       <c r="T50" s="5" t="n">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="U50" s="5" t="n">
-        <v>369230</v>
+        <v>593434</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>glucose_bld</t>
+          <t>hdl</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>211779</v>
+        <v>282573</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>6763</v>
+        <v>16570</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>25155</v>
+        <v>29869</v>
       </c>
       <c r="H51" s="7" t="n">
         <v>0</v>
@@ -3948,120 +3948,120 @@
         <v>0</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>292594</v>
+        <v>148153</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>0</v>
+        <v>23652</v>
       </c>
       <c r="N51" s="7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O51" s="7" t="n">
-        <v>10187</v>
+        <v>32797</v>
       </c>
       <c r="P51" s="7" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Q51" s="7" t="n">
-        <v>358</v>
+        <v>74205</v>
       </c>
       <c r="R51" s="7" t="n">
         <v>3</v>
       </c>
       <c r="S51" s="7" t="n">
-        <v>46598</v>
+        <v>46573</v>
       </c>
       <c r="T51" s="5" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="U51" s="5" t="n">
-        <v>593434</v>
+        <v>654392</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>hdl</t>
+          <t>hemat</t>
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C52" s="7" t="n">
-        <v>282573</v>
+        <v>61658</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>16570</v>
+        <v>3582</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>29869</v>
+        <v>25115</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>0</v>
+        <v>53674</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>148153</v>
+        <v>154499</v>
       </c>
       <c r="L52" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M52" s="7" t="n">
-        <v>23652</v>
+        <v>23567</v>
       </c>
       <c r="N52" s="7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="O52" s="7" t="n">
-        <v>32797</v>
+        <v>3746</v>
       </c>
       <c r="P52" s="7" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Q52" s="7" t="n">
-        <v>74205</v>
+        <v>3656</v>
       </c>
       <c r="R52" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S52" s="7" t="n">
-        <v>46573</v>
+        <v>629273</v>
       </c>
       <c r="T52" s="5" t="n">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="U52" s="5" t="n">
-        <v>654392</v>
+        <v>958770</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>hemat</t>
+          <t>hemo</t>
         </is>
       </c>
       <c r="B53" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>61658</v>
+        <v>64879</v>
       </c>
       <c r="D53" s="7" t="n">
         <v>1</v>
@@ -4082,10 +4082,10 @@
         <v>53674</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>154499</v>
+        <v>102103</v>
       </c>
       <c r="L53" s="7" t="n">
         <v>2</v>
@@ -4103,111 +4103,111 @@
         <v>2</v>
       </c>
       <c r="Q53" s="7" t="n">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="R53" s="7" t="n">
         <v>4</v>
       </c>
       <c r="S53" s="7" t="n">
-        <v>629273</v>
+        <v>629314</v>
       </c>
       <c r="T53" s="5" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="U53" s="5" t="n">
-        <v>958770</v>
+        <v>909635</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>hemo</t>
+          <t>hemo_a1c</t>
         </is>
       </c>
       <c r="B54" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>64879</v>
+        <v>8841</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>3582</v>
+        <v>0</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>25115</v>
+        <v>0</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I54" s="7" t="n">
-        <v>53674</v>
+        <v>0</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>102103</v>
+        <v>55340</v>
       </c>
       <c r="L54" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M54" s="7" t="n">
-        <v>23567</v>
+        <v>23612</v>
       </c>
       <c r="N54" s="7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O54" s="7" t="n">
-        <v>3746</v>
+        <v>28547</v>
       </c>
       <c r="P54" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q54" s="7" t="n">
-        <v>3655</v>
+        <v>20878</v>
       </c>
       <c r="R54" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S54" s="7" t="n">
-        <v>629314</v>
+        <v>0</v>
       </c>
       <c r="T54" s="5" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="U54" s="5" t="n">
-        <v>909635</v>
+        <v>137218</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>hemo_a1c</t>
+          <t>hip_circ</t>
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>8841</v>
+        <v>54020</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>0</v>
+        <v>33281</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>0</v>
+        <v>30339</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>0</v>
@@ -4216,180 +4216,180 @@
         <v>0</v>
       </c>
       <c r="J55" s="7" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>55340</v>
+        <v>126492</v>
       </c>
       <c r="L55" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>23612</v>
+        <v>23627</v>
       </c>
       <c r="N55" s="7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O55" s="7" t="n">
-        <v>28547</v>
+        <v>17671</v>
       </c>
       <c r="P55" s="7" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Q55" s="7" t="n">
-        <v>20878</v>
+        <v>56541</v>
       </c>
       <c r="R55" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S55" s="7" t="n">
-        <v>0</v>
+        <v>1610762</v>
       </c>
       <c r="T55" s="5" t="n">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="U55" s="5" t="n">
-        <v>137218</v>
+        <v>1952733</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>hip_circ</t>
+          <t>hrtrt</t>
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>54020</v>
+        <v>439669</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>33281</v>
+        <v>60109</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>30339</v>
+        <v>252223</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I56" s="7" t="n">
-        <v>0</v>
+        <v>64245</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>126492</v>
+        <v>185296</v>
       </c>
       <c r="L56" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M56" s="7" t="n">
-        <v>23627</v>
+        <v>35266</v>
       </c>
       <c r="N56" s="7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O56" s="7" t="n">
-        <v>17671</v>
+        <v>35238</v>
       </c>
       <c r="P56" s="7" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="Q56" s="7" t="n">
-        <v>56541</v>
+        <v>154242</v>
       </c>
       <c r="R56" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S56" s="7" t="n">
-        <v>1610762</v>
+        <v>506519</v>
       </c>
       <c r="T56" s="5" t="n">
-        <v>84</v>
+        <v>291</v>
       </c>
       <c r="U56" s="5" t="n">
-        <v>1952733</v>
+        <v>1732807</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>hrtrt</t>
+          <t>icam</t>
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>439669</v>
+        <v>0</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>60109</v>
+        <v>2669</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>87</v>
+        <v>2</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>252223</v>
+        <v>7663</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I57" s="7" t="n">
-        <v>64245</v>
+        <v>0</v>
       </c>
       <c r="J57" s="7" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>185296</v>
+        <v>0</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M57" s="7" t="n">
-        <v>35266</v>
+        <v>0</v>
       </c>
       <c r="N57" s="7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O57" s="7" t="n">
-        <v>35238</v>
+        <v>0</v>
       </c>
       <c r="P57" s="7" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="Q57" s="7" t="n">
-        <v>154242</v>
+        <v>15379</v>
       </c>
       <c r="R57" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S57" s="7" t="n">
-        <v>506519</v>
+        <v>0</v>
       </c>
       <c r="T57" s="5" t="n">
-        <v>291</v>
+        <v>9</v>
       </c>
       <c r="U57" s="5" t="n">
-        <v>1732807</v>
+        <v>25711</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>icam</t>
+          <t>il10</t>
         </is>
       </c>
       <c r="B58" s="7" t="n">
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>2669</v>
+        <v>0</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>7663</v>
+        <v>0</v>
       </c>
       <c r="H58" s="7" t="n">
         <v>0</v>
@@ -4435,10 +4435,10 @@
         <v>0</v>
       </c>
       <c r="P58" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q58" s="7" t="n">
-        <v>15379</v>
+        <v>943</v>
       </c>
       <c r="R58" s="7" t="n">
         <v>0</v>
@@ -4447,16 +4447,16 @@
         <v>0</v>
       </c>
       <c r="T58" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U58" s="5" t="n">
-        <v>25711</v>
+        <v>943</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>il10</t>
+          <t>il18</t>
         </is>
       </c>
       <c r="B59" s="7" t="n">
@@ -4484,10 +4484,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>0</v>
+        <v>38307</v>
       </c>
       <c r="L59" s="7" t="n">
         <v>0</v>
@@ -4502,10 +4502,10 @@
         <v>0</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="7" t="n">
-        <v>943</v>
+        <v>0</v>
       </c>
       <c r="R59" s="7" t="n">
         <v>0</v>
@@ -4514,16 +4514,16 @@
         <v>0</v>
       </c>
       <c r="T59" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U59" s="5" t="n">
-        <v>943</v>
+        <v>38307</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>il18</t>
+          <t>il6</t>
         </is>
       </c>
       <c r="B60" s="7" t="n">
@@ -4533,16 +4533,16 @@
         <v>0</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>0</v>
+        <v>689</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0</v>
+        <v>10594</v>
       </c>
       <c r="H60" s="7" t="n">
         <v>0</v>
@@ -4551,10 +4551,10 @@
         <v>0</v>
       </c>
       <c r="J60" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>38307</v>
+        <v>0</v>
       </c>
       <c r="L60" s="7" t="n">
         <v>0</v>
@@ -4569,10 +4569,10 @@
         <v>0</v>
       </c>
       <c r="P60" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q60" s="7" t="n">
-        <v>0</v>
+        <v>17277</v>
       </c>
       <c r="R60" s="7" t="n">
         <v>0</v>
@@ -4581,35 +4581,35 @@
         <v>0</v>
       </c>
       <c r="T60" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U60" s="5" t="n">
-        <v>38307</v>
+        <v>28560</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>il6</t>
+          <t>insulin_blood</t>
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>0</v>
+        <v>56942</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>689</v>
+        <v>9647</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>10594</v>
+        <v>25071</v>
       </c>
       <c r="H61" s="7" t="n">
         <v>0</v>
@@ -4618,65 +4618,65 @@
         <v>0</v>
       </c>
       <c r="J61" s="7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>0</v>
+        <v>74472</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M61" s="7" t="n">
-        <v>0</v>
+        <v>23618</v>
       </c>
       <c r="N61" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O61" s="7" t="n">
-        <v>0</v>
+        <v>6587</v>
       </c>
       <c r="P61" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q61" s="7" t="n">
-        <v>17277</v>
+        <v>25329</v>
       </c>
       <c r="R61" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S61" s="7" t="n">
-        <v>0</v>
+        <v>43342</v>
       </c>
       <c r="T61" s="5" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="U61" s="5" t="n">
-        <v>28560</v>
+        <v>265008</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>insulin_blood</t>
+          <t>isoprostane_8_epi_pgf2a</t>
         </is>
       </c>
       <c r="B62" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>56942</v>
+        <v>0</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>9647</v>
+        <v>2720</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>25071</v>
+        <v>0</v>
       </c>
       <c r="H62" s="7" t="n">
         <v>0</v>
@@ -4685,46 +4685,46 @@
         <v>0</v>
       </c>
       <c r="J62" s="7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K62" s="7" t="n">
-        <v>74472</v>
+        <v>0</v>
       </c>
       <c r="L62" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" s="7" t="n">
-        <v>23618</v>
+        <v>0</v>
       </c>
       <c r="N62" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O62" s="7" t="n">
-        <v>6587</v>
+        <v>0</v>
       </c>
       <c r="P62" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q62" s="7" t="n">
-        <v>25329</v>
+        <v>6805</v>
       </c>
       <c r="R62" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S62" s="7" t="n">
-        <v>43342</v>
+        <v>0</v>
       </c>
       <c r="T62" s="5" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="U62" s="5" t="n">
-        <v>265008</v>
+        <v>9525</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>isoprostane_8_epi_pgf2a</t>
+          <t>lactate</t>
         </is>
       </c>
       <c r="B63" s="7" t="n">
@@ -4734,10 +4734,10 @@
         <v>0</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>2720</v>
+        <v>0</v>
       </c>
       <c r="F63" s="7" t="n">
         <v>0</v>
@@ -4752,10 +4752,10 @@
         <v>0</v>
       </c>
       <c r="J63" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>0</v>
+        <v>26148</v>
       </c>
       <c r="L63" s="7" t="n">
         <v>0</v>
@@ -4770,10 +4770,10 @@
         <v>0</v>
       </c>
       <c r="P63" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q63" s="7" t="n">
-        <v>6805</v>
+        <v>0</v>
       </c>
       <c r="R63" s="7" t="n">
         <v>0</v>
@@ -4782,16 +4782,16 @@
         <v>0</v>
       </c>
       <c r="T63" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U63" s="5" t="n">
-        <v>9525</v>
+        <v>26148</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>lactate</t>
+          <t>lactate_dehyd</t>
         </is>
       </c>
       <c r="B64" s="7" t="n">
@@ -4819,10 +4819,10 @@
         <v>0</v>
       </c>
       <c r="J64" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K64" s="7" t="n">
-        <v>26148</v>
+        <v>3530</v>
       </c>
       <c r="L64" s="7" t="n">
         <v>0</v>
@@ -4849,35 +4849,35 @@
         <v>0</v>
       </c>
       <c r="T64" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U64" s="5" t="n">
-        <v>26148</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>lactate_dehyd</t>
+          <t>ldl</t>
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>0</v>
+        <v>173272</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>0</v>
+        <v>16477</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>0</v>
+        <v>25015</v>
       </c>
       <c r="H65" s="7" t="n">
         <v>0</v>
@@ -4886,65 +4886,65 @@
         <v>0</v>
       </c>
       <c r="J65" s="7" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>3530</v>
+        <v>123639</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M65" s="7" t="n">
-        <v>0</v>
+        <v>23409</v>
       </c>
       <c r="N65" s="7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O65" s="7" t="n">
-        <v>0</v>
+        <v>43886</v>
       </c>
       <c r="P65" s="7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q65" s="7" t="n">
-        <v>0</v>
+        <v>68027</v>
       </c>
       <c r="R65" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S65" s="7" t="n">
-        <v>0</v>
+        <v>46331</v>
       </c>
       <c r="T65" s="5" t="n">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="U65" s="5" t="n">
-        <v>3530</v>
+        <v>520056</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>ldl</t>
+          <t>lppla2_act</t>
         </is>
       </c>
       <c r="B66" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>173272</v>
+        <v>0</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>16477</v>
+        <v>0</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>25015</v>
+        <v>10910</v>
       </c>
       <c r="H66" s="7" t="n">
         <v>0</v>
@@ -4953,46 +4953,46 @@
         <v>0</v>
       </c>
       <c r="J66" s="7" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K66" s="7" t="n">
-        <v>123639</v>
+        <v>0</v>
       </c>
       <c r="L66" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M66" s="7" t="n">
-        <v>23409</v>
+        <v>0</v>
       </c>
       <c r="N66" s="7" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O66" s="7" t="n">
-        <v>43886</v>
+        <v>0</v>
       </c>
       <c r="P66" s="7" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="Q66" s="7" t="n">
-        <v>68027</v>
+        <v>5122</v>
       </c>
       <c r="R66" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S66" s="7" t="n">
-        <v>46331</v>
+        <v>0</v>
       </c>
       <c r="T66" s="5" t="n">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c r="U66" s="5" t="n">
-        <v>520056</v>
+        <v>16032</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>lppla2_act</t>
+          <t>lppla2_mass</t>
         </is>
       </c>
       <c r="B67" s="7" t="n">
@@ -5011,7 +5011,7 @@
         <v>2</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>10910</v>
+        <v>10923</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0</v>
@@ -5041,7 +5041,7 @@
         <v>1</v>
       </c>
       <c r="Q67" s="7" t="n">
-        <v>5122</v>
+        <v>5042</v>
       </c>
       <c r="R67" s="7" t="n">
         <v>0</v>
@@ -5053,38 +5053,38 @@
         <v>3</v>
       </c>
       <c r="U67" s="5" t="n">
-        <v>16032</v>
+        <v>15965</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>lppla2_mass</t>
+          <t>lympho_ct</t>
         </is>
       </c>
       <c r="B68" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68" s="7" t="n">
-        <v>0</v>
+        <v>5706</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>0</v>
+        <v>3968</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>10923</v>
+        <v>0</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I68" s="7" t="n">
-        <v>0</v>
+        <v>53590</v>
       </c>
       <c r="J68" s="7" t="n">
         <v>0</v>
@@ -5093,10 +5093,10 @@
         <v>0</v>
       </c>
       <c r="L68" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M68" s="7" t="n">
-        <v>0</v>
+        <v>22908</v>
       </c>
       <c r="N68" s="7" t="n">
         <v>0</v>
@@ -5108,7 +5108,7 @@
         <v>1</v>
       </c>
       <c r="Q68" s="7" t="n">
-        <v>5042</v>
+        <v>2338</v>
       </c>
       <c r="R68" s="7" t="n">
         <v>0</v>
@@ -5117,29 +5117,29 @@
         <v>0</v>
       </c>
       <c r="T68" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U68" s="5" t="n">
-        <v>15965</v>
+        <v>88510</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>lympho_ct</t>
+          <t>lympho_pct</t>
         </is>
       </c>
       <c r="B69" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>5706</v>
+        <v>24362</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>3968</v>
+        <v>0</v>
       </c>
       <c r="F69" s="7" t="n">
         <v>0</v>
@@ -5148,16 +5148,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>53590</v>
+        <v>0</v>
       </c>
       <c r="J69" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>0</v>
+        <v>12638</v>
       </c>
       <c r="L69" s="7" t="n">
         <v>2</v>
@@ -5166,16 +5166,16 @@
         <v>22908</v>
       </c>
       <c r="N69" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" s="7" t="n">
-        <v>0</v>
+        <v>3362</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q69" s="7" t="n">
-        <v>2338</v>
+        <v>0</v>
       </c>
       <c r="R69" s="7" t="n">
         <v>0</v>
@@ -5184,29 +5184,29 @@
         <v>0</v>
       </c>
       <c r="T69" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U69" s="5" t="n">
-        <v>88510</v>
+        <v>63270</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>lympho_pct</t>
+          <t>mch</t>
         </is>
       </c>
       <c r="B70" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C70" s="7" t="n">
-        <v>24362</v>
+        <v>12069</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>0</v>
+        <v>7165</v>
       </c>
       <c r="F70" s="7" t="n">
         <v>0</v>
@@ -5215,34 +5215,34 @@
         <v>0</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I70" s="7" t="n">
-        <v>0</v>
+        <v>53674</v>
       </c>
       <c r="J70" s="7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>12638</v>
+        <v>54003</v>
       </c>
       <c r="L70" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M70" s="7" t="n">
-        <v>22908</v>
+        <v>23567</v>
       </c>
       <c r="N70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="O70" s="7" t="n">
-        <v>3362</v>
+        <v>3376</v>
       </c>
       <c r="P70" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q70" s="7" t="n">
-        <v>0</v>
+        <v>2756</v>
       </c>
       <c r="R70" s="7" t="n">
         <v>0</v>
@@ -5251,29 +5251,29 @@
         <v>0</v>
       </c>
       <c r="T70" s="5" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="U70" s="5" t="n">
-        <v>63270</v>
+        <v>156610</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>mch</t>
+          <t>mchc</t>
         </is>
       </c>
       <c r="B71" s="7" t="n">
         <v>3</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>12069</v>
+        <v>8408</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>7165</v>
+        <v>0</v>
       </c>
       <c r="F71" s="7" t="n">
         <v>0</v>
@@ -5288,10 +5288,10 @@
         <v>53674</v>
       </c>
       <c r="J71" s="7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>54003</v>
+        <v>39615</v>
       </c>
       <c r="L71" s="7" t="n">
         <v>2</v>
@@ -5303,7 +5303,7 @@
         <v>1</v>
       </c>
       <c r="O71" s="7" t="n">
-        <v>3376</v>
+        <v>3377</v>
       </c>
       <c r="P71" s="7" t="n">
         <v>1</v>
@@ -5318,23 +5318,23 @@
         <v>0</v>
       </c>
       <c r="T71" s="5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="U71" s="5" t="n">
-        <v>156610</v>
+        <v>131397</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>mchc</t>
+          <t>mcv</t>
         </is>
       </c>
       <c r="B72" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C72" s="7" t="n">
-        <v>8408</v>
+        <v>28238</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>0</v>
@@ -5385,23 +5385,23 @@
         <v>0</v>
       </c>
       <c r="T72" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="U72" s="5" t="n">
-        <v>131397</v>
+        <v>151227</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>mcv</t>
+          <t>mean_art_press</t>
         </is>
       </c>
       <c r="B73" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>28238</v>
+        <v>0</v>
       </c>
       <c r="D73" s="7" t="n">
         <v>0</v>
@@ -5416,34 +5416,34 @@
         <v>0</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>53674</v>
+        <v>0</v>
       </c>
       <c r="J73" s="7" t="n">
         <v>9</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>39615</v>
+        <v>50002</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M73" s="7" t="n">
-        <v>23567</v>
+        <v>0</v>
       </c>
       <c r="N73" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" s="7" t="n">
-        <v>3377</v>
+        <v>0</v>
       </c>
       <c r="P73" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q73" s="7" t="n">
-        <v>2756</v>
+        <v>0</v>
       </c>
       <c r="R73" s="7" t="n">
         <v>0</v>
@@ -5452,16 +5452,16 @@
         <v>0</v>
       </c>
       <c r="T73" s="5" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="U73" s="5" t="n">
-        <v>151227</v>
+        <v>50002</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>mean_art_press</t>
+          <t>mmp9</t>
         </is>
       </c>
       <c r="B74" s="7" t="n">
@@ -5489,10 +5489,10 @@
         <v>0</v>
       </c>
       <c r="J74" s="7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K74" s="7" t="n">
-        <v>50002</v>
+        <v>0</v>
       </c>
       <c r="L74" s="7" t="n">
         <v>0</v>
@@ -5507,10 +5507,10 @@
         <v>0</v>
       </c>
       <c r="P74" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q74" s="7" t="n">
-        <v>0</v>
+        <v>7393</v>
       </c>
       <c r="R74" s="7" t="n">
         <v>0</v>
@@ -5519,29 +5519,29 @@
         <v>0</v>
       </c>
       <c r="T74" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U74" s="5" t="n">
-        <v>50002</v>
+        <v>7393</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>mmp9</t>
+          <t>mn_art_pres</t>
         </is>
       </c>
       <c r="B75" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>0</v>
+        <v>24769</v>
       </c>
       <c r="F75" s="7" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="P75" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q75" s="7" t="n">
-        <v>7393</v>
+        <v>18383</v>
       </c>
       <c r="R75" s="7" t="n">
         <v>0</v>
@@ -5586,29 +5586,29 @@
         <v>0</v>
       </c>
       <c r="T75" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U75" s="5" t="n">
-        <v>7393</v>
+        <v>43170</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>mn_art_pres</t>
+          <t>monocyte_ncnc_bld</t>
         </is>
       </c>
       <c r="B76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>18</v>
+        <v>5706</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>24769</v>
+        <v>384</v>
       </c>
       <c r="F76" s="7" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
         <v>0</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I76" s="7" t="n">
-        <v>0</v>
+        <v>53588</v>
       </c>
       <c r="J76" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>0</v>
+        <v>32540</v>
       </c>
       <c r="L76" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M76" s="7" t="n">
-        <v>0</v>
+        <v>22913</v>
       </c>
       <c r="N76" s="7" t="n">
         <v>0</v>
@@ -5641,10 +5641,10 @@
         <v>0</v>
       </c>
       <c r="P76" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q76" s="7" t="n">
-        <v>18383</v>
+        <v>3231</v>
       </c>
       <c r="R76" s="7" t="n">
         <v>0</v>
@@ -5653,29 +5653,29 @@
         <v>0</v>
       </c>
       <c r="T76" s="5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="U76" s="5" t="n">
-        <v>43170</v>
+        <v>118362</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>monocyte_ncnc_bld</t>
+          <t>neutro_pct</t>
         </is>
       </c>
       <c r="B77" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>18618</v>
+      </c>
+      <c r="D77" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C77" s="7" t="n">
-        <v>5706</v>
-      </c>
-      <c r="D77" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="E77" s="7" t="n">
-        <v>384</v>
+        <v>2407</v>
       </c>
       <c r="F77" s="7" t="n">
         <v>0</v>
@@ -5684,101 +5684,101 @@
         <v>0</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I77" s="7" t="n">
-        <v>53588</v>
+        <v>0</v>
       </c>
       <c r="J77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M77" s="7" t="n">
+        <v>22908</v>
+      </c>
+      <c r="N77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K77" s="7" t="n">
-        <v>32540</v>
-      </c>
-      <c r="L77" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M77" s="7" t="n">
-        <v>22913</v>
-      </c>
-      <c r="N77" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q77" s="7" t="n">
-        <v>3231</v>
-      </c>
-      <c r="R77" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" s="5" t="n">
-        <v>15</v>
-      </c>
       <c r="U77" s="5" t="n">
-        <v>118362</v>
+        <v>43933</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>neutro_pct</t>
+          <t>neutrophil_ct</t>
         </is>
       </c>
       <c r="B78" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C78" s="7" t="n">
-        <v>18618</v>
+        <v>0</v>
       </c>
       <c r="D78" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>324</v>
+      </c>
+      <c r="F78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I78" s="7" t="n">
+        <v>53590</v>
+      </c>
+      <c r="J78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M78" s="7" t="n">
+        <v>22909</v>
+      </c>
+      <c r="N78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E78" s="7" t="n">
-        <v>2407</v>
-      </c>
-      <c r="F78" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M78" s="7" t="n">
-        <v>22908</v>
-      </c>
-      <c r="N78" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="Q78" s="7" t="n">
-        <v>0</v>
+        <v>2338</v>
       </c>
       <c r="R78" s="7" t="n">
         <v>0</v>
@@ -5787,29 +5787,29 @@
         <v>0</v>
       </c>
       <c r="T78" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U78" s="5" t="n">
-        <v>43933</v>
+        <v>79161</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>neutrophil_ct</t>
+          <t>nt_bnp</t>
         </is>
       </c>
       <c r="B79" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>0</v>
+        <v>47302</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="F79" s="7" t="n">
         <v>0</v>
@@ -5818,22 +5818,22 @@
         <v>0</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I79" s="7" t="n">
-        <v>53590</v>
+        <v>0</v>
       </c>
       <c r="J79" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>0</v>
+        <v>19114</v>
       </c>
       <c r="L79" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M79" s="7" t="n">
-        <v>22909</v>
+        <v>0</v>
       </c>
       <c r="N79" s="7" t="n">
         <v>0</v>
@@ -5842,35 +5842,35 @@
         <v>0</v>
       </c>
       <c r="P79" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q79" s="7" t="n">
-        <v>2338</v>
+        <v>10090</v>
       </c>
       <c r="R79" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S79" s="7" t="n">
-        <v>0</v>
+        <v>1802</v>
       </c>
       <c r="T79" s="5" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="U79" s="5" t="n">
-        <v>79161</v>
+        <v>78308</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>nt_bnp</t>
+          <t>pacem_stat</t>
         </is>
       </c>
       <c r="B80" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>47302</v>
+        <v>13110</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>0</v>
@@ -5891,16 +5891,16 @@
         <v>0</v>
       </c>
       <c r="J80" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>19114</v>
+        <v>0</v>
       </c>
       <c r="L80" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M80" s="7" t="n">
-        <v>0</v>
+        <v>11848</v>
       </c>
       <c r="N80" s="7" t="n">
         <v>0</v>
@@ -5909,181 +5909,181 @@
         <v>0</v>
       </c>
       <c r="P80" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q80" s="7" t="n">
-        <v>10090</v>
+        <v>12922</v>
       </c>
       <c r="R80" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S80" s="7" t="n">
-        <v>1802</v>
+        <v>0</v>
       </c>
       <c r="T80" s="5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="U80" s="5" t="n">
-        <v>78308</v>
+        <v>37880</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>pacem_stat</t>
+          <t>platelet_ct</t>
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>13110</v>
+        <v>37442</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>0</v>
+        <v>3581</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>0</v>
+        <v>25046</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>0</v>
+        <v>53654</v>
       </c>
       <c r="J81" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>0</v>
+        <v>35931</v>
       </c>
       <c r="L81" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>11848</v>
+        <v>23560</v>
       </c>
       <c r="N81" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>0</v>
+        <v>3749</v>
       </c>
       <c r="P81" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q81" s="7" t="n">
-        <v>12922</v>
+        <v>3644</v>
       </c>
       <c r="R81" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S81" s="7" t="n">
-        <v>0</v>
+        <v>623065</v>
       </c>
       <c r="T81" s="5" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="U81" s="5" t="n">
-        <v>37880</v>
+        <v>809672</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>platelet_ct</t>
+          <t>pmv</t>
         </is>
       </c>
       <c r="B82" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>37442</v>
+        <v>5707</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>3581</v>
+        <v>0</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>25046</v>
+        <v>0</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I82" s="7" t="n">
-        <v>53654</v>
+        <v>0</v>
       </c>
       <c r="J82" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K82" s="7" t="n">
-        <v>35931</v>
+        <v>32540</v>
       </c>
       <c r="L82" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M82" s="7" t="n">
-        <v>23560</v>
+        <v>0</v>
       </c>
       <c r="N82" s="7" t="n">
         <v>1</v>
       </c>
       <c r="O82" s="7" t="n">
-        <v>3749</v>
+        <v>3376</v>
       </c>
       <c r="P82" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q82" s="7" t="n">
-        <v>3644</v>
+        <v>0</v>
       </c>
       <c r="R82" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S82" s="7" t="n">
-        <v>623065</v>
+        <v>0</v>
       </c>
       <c r="T82" s="5" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="U82" s="5" t="n">
-        <v>809672</v>
+        <v>41623</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>pmv</t>
+          <t>potassium</t>
         </is>
       </c>
       <c r="B83" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>5707</v>
+        <v>37384</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>0</v>
+        <v>6310</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>0</v>
+        <v>25155</v>
       </c>
       <c r="H83" s="7" t="n">
         <v>0</v>
@@ -6092,10 +6092,10 @@
         <v>0</v>
       </c>
       <c r="J83" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>32540</v>
+        <v>0</v>
       </c>
       <c r="L83" s="7" t="n">
         <v>0</v>
@@ -6107,13 +6107,13 @@
         <v>1</v>
       </c>
       <c r="O83" s="7" t="n">
-        <v>3376</v>
+        <v>3839</v>
       </c>
       <c r="P83" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q83" s="7" t="n">
-        <v>0</v>
+        <v>18964</v>
       </c>
       <c r="R83" s="7" t="n">
         <v>0</v>
@@ -6122,35 +6122,35 @@
         <v>0</v>
       </c>
       <c r="T83" s="5" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="U83" s="5" t="n">
-        <v>41623</v>
+        <v>91652</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>potassium</t>
+          <t>pr_ekg</t>
         </is>
       </c>
       <c r="B84" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>37384</v>
+        <v>59015</v>
       </c>
       <c r="D84" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>6310</v>
+        <v>0</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>25155</v>
+        <v>0</v>
       </c>
       <c r="H84" s="7" t="n">
         <v>0</v>
@@ -6165,47 +6165,47 @@
         <v>0</v>
       </c>
       <c r="L84" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M84" s="7" t="n">
-        <v>0</v>
+        <v>23526</v>
       </c>
       <c r="N84" s="7" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O84" s="7" t="n">
-        <v>3839</v>
+        <v>78673</v>
       </c>
       <c r="P84" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q84" s="7" t="n">
-        <v>18964</v>
+        <v>22435</v>
       </c>
       <c r="R84" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S84" s="7" t="n">
-        <v>0</v>
+        <v>500439</v>
       </c>
       <c r="T84" s="5" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="U84" s="5" t="n">
-        <v>91652</v>
+        <v>684088</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>pr_ekg</t>
+          <t>pr_qrs_qt</t>
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>59015</v>
+        <v>0</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>0</v>
@@ -6226,46 +6226,46 @@
         <v>0</v>
       </c>
       <c r="J85" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>0</v>
+        <v>66296</v>
       </c>
       <c r="L85" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>23526</v>
+        <v>0</v>
       </c>
       <c r="N85" s="7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O85" s="7" t="n">
-        <v>78673</v>
+        <v>0</v>
       </c>
       <c r="P85" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q85" s="7" t="n">
-        <v>22435</v>
+        <v>0</v>
       </c>
       <c r="R85" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S85" s="7" t="n">
-        <v>500439</v>
+        <v>0</v>
       </c>
       <c r="T85" s="5" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="U85" s="5" t="n">
-        <v>684088</v>
+        <v>66296</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>pr_qrs_qt</t>
+          <t>pselectin</t>
         </is>
       </c>
       <c r="B86" s="7" t="n">
@@ -6275,10 +6275,10 @@
         <v>0</v>
       </c>
       <c r="D86" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
       <c r="F86" s="7" t="n">
         <v>0</v>
@@ -6293,10 +6293,10 @@
         <v>0</v>
       </c>
       <c r="J86" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>66296</v>
+        <v>0</v>
       </c>
       <c r="L86" s="7" t="n">
         <v>0</v>
@@ -6305,10 +6305,10 @@
         <v>0</v>
       </c>
       <c r="N86" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O86" s="7" t="n">
-        <v>0</v>
+        <v>8299</v>
       </c>
       <c r="P86" s="7" t="n">
         <v>0</v>
@@ -6323,35 +6323,35 @@
         <v>0</v>
       </c>
       <c r="T86" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U86" s="5" t="n">
-        <v>66296</v>
+        <v>8625</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>pselectin</t>
+          <t>qrs_ekg</t>
         </is>
       </c>
       <c r="B87" s="7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>0</v>
+        <v>274284</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>0</v>
+        <v>43430</v>
       </c>
       <c r="H87" s="7" t="n">
         <v>0</v>
@@ -6360,53 +6360,53 @@
         <v>0</v>
       </c>
       <c r="J87" s="7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>0</v>
+        <v>202581</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>0</v>
+        <v>23558</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>8299</v>
+        <v>65524</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q87" s="7" t="n">
-        <v>0</v>
+        <v>22514</v>
       </c>
       <c r="R87" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S87" s="7" t="n">
-        <v>0</v>
+        <v>500439</v>
       </c>
       <c r="T87" s="5" t="n">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="U87" s="5" t="n">
-        <v>8625</v>
+        <v>1132330</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>qrs_ekg</t>
+          <t>qt_ekg</t>
         </is>
       </c>
       <c r="B88" s="7" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>274284</v>
+        <v>61199</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>0</v>
@@ -6415,10 +6415,10 @@
         <v>0</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>43430</v>
+        <v>0</v>
       </c>
       <c r="H88" s="7" t="n">
         <v>0</v>
@@ -6427,22 +6427,22 @@
         <v>0</v>
       </c>
       <c r="J88" s="7" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="K88" s="7" t="n">
-        <v>202581</v>
+        <v>90128</v>
       </c>
       <c r="L88" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M88" s="7" t="n">
-        <v>23558</v>
+        <v>35283</v>
       </c>
       <c r="N88" s="7" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="O88" s="7" t="n">
-        <v>65524</v>
+        <v>46378</v>
       </c>
       <c r="P88" s="7" t="n">
         <v>8</v>
@@ -6457,29 +6457,29 @@
         <v>500439</v>
       </c>
       <c r="T88" s="5" t="n">
-        <v>139</v>
+        <v>54</v>
       </c>
       <c r="U88" s="5" t="n">
-        <v>1132330</v>
+        <v>755941</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>qt_ekg</t>
+          <t>rdbld_ct</t>
         </is>
       </c>
       <c r="B89" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>61199</v>
+        <v>14728</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>0</v>
+        <v>3583</v>
       </c>
       <c r="F89" s="7" t="n">
         <v>0</v>
@@ -6488,65 +6488,65 @@
         <v>0</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>0</v>
+        <v>53674</v>
       </c>
       <c r="J89" s="7" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>90128</v>
+        <v>59154</v>
       </c>
       <c r="L89" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M89" s="7" t="n">
-        <v>35283</v>
+        <v>23567</v>
       </c>
       <c r="N89" s="7" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O89" s="7" t="n">
-        <v>46378</v>
+        <v>3377</v>
       </c>
       <c r="P89" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q89" s="7" t="n">
-        <v>22514</v>
+        <v>3656</v>
       </c>
       <c r="R89" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S89" s="7" t="n">
-        <v>500439</v>
+        <v>0</v>
       </c>
       <c r="T89" s="5" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="U89" s="5" t="n">
-        <v>755941</v>
+        <v>161739</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>rdbld_ct</t>
+          <t>rdw</t>
         </is>
       </c>
       <c r="B90" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>14728</v>
+        <v>12016</v>
       </c>
       <c r="D90" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>3583</v>
+        <v>0</v>
       </c>
       <c r="F90" s="7" t="n">
         <v>0</v>
@@ -6555,71 +6555,71 @@
         <v>0</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I90" s="7" t="n">
-        <v>53674</v>
+        <v>0</v>
       </c>
       <c r="J90" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" s="7" t="n">
+        <v>32543</v>
+      </c>
+      <c r="L90" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M90" s="7" t="n">
+        <v>23566</v>
+      </c>
+      <c r="N90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="K90" s="7" t="n">
-        <v>59154</v>
-      </c>
-      <c r="L90" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M90" s="7" t="n">
-        <v>23567</v>
-      </c>
-      <c r="N90" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O90" s="7" t="n">
-        <v>3377</v>
-      </c>
-      <c r="P90" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q90" s="7" t="n">
-        <v>3656</v>
-      </c>
-      <c r="R90" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="U90" s="5" t="n">
-        <v>161739</v>
+        <v>68125</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>rdw</t>
+          <t>sleep_duration_daily</t>
         </is>
       </c>
       <c r="B91" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>12016</v>
+        <v>5925</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>0</v>
+        <v>3529</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>0</v>
+        <v>13853</v>
       </c>
       <c r="H91" s="7" t="n">
         <v>0</v>
@@ -6628,132 +6628,132 @@
         <v>0</v>
       </c>
       <c r="J91" s="7" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="K91" s="7" t="n">
-        <v>32543</v>
+        <v>129670</v>
       </c>
       <c r="L91" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M91" s="7" t="n">
-        <v>23566</v>
+        <v>23080</v>
       </c>
       <c r="N91" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O91" s="7" t="n">
-        <v>0</v>
+        <v>6955</v>
       </c>
       <c r="P91" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q91" s="7" t="n">
-        <v>0</v>
+        <v>10941</v>
       </c>
       <c r="R91" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S91" s="7" t="n">
-        <v>0</v>
+        <v>626832</v>
       </c>
       <c r="T91" s="5" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="U91" s="5" t="n">
-        <v>68125</v>
+        <v>820785</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>sleep_duration_daily</t>
+          <t>sodium_blood</t>
         </is>
       </c>
       <c r="B92" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C92" s="7" t="n">
+        <v>52984</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K92" s="7" t="n">
+        <v>17171</v>
+      </c>
+      <c r="L92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C92" s="7" t="n">
-        <v>5925</v>
-      </c>
-      <c r="D92" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E92" s="7" t="n">
-        <v>3529</v>
-      </c>
-      <c r="F92" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G92" s="7" t="n">
-        <v>13853</v>
-      </c>
-      <c r="H92" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="K92" s="7" t="n">
-        <v>129670</v>
-      </c>
-      <c r="L92" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M92" s="7" t="n">
-        <v>23080</v>
-      </c>
-      <c r="N92" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="O92" s="7" t="n">
-        <v>6955</v>
+        <v>3839</v>
       </c>
       <c r="P92" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q92" s="7" t="n">
-        <v>10941</v>
+        <v>6129</v>
       </c>
       <c r="R92" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S92" s="7" t="n">
-        <v>626832</v>
+        <v>5721</v>
       </c>
       <c r="T92" s="5" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="U92" s="5" t="n">
-        <v>820785</v>
+        <v>85844</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>sodium_blood</t>
+          <t>sodium_intak</t>
         </is>
       </c>
       <c r="B93" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C93" s="7" t="n">
+        <v>28614</v>
+      </c>
+      <c r="D93" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C93" s="7" t="n">
-        <v>52984</v>
-      </c>
-      <c r="D93" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="E93" s="7" t="n">
-        <v>0</v>
+        <v>16962</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>0</v>
+        <v>12180</v>
       </c>
       <c r="H93" s="7" t="n">
         <v>0</v>
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="J93" s="7" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K93" s="7" t="n">
-        <v>17171</v>
+        <v>82860</v>
       </c>
       <c r="L93" s="7" t="n">
         <v>0</v>
@@ -6774,71 +6774,71 @@
         <v>0</v>
       </c>
       <c r="N93" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93" s="7" t="n">
-        <v>3839</v>
+        <v>0</v>
       </c>
       <c r="P93" s="7" t="n">
         <v>1</v>
       </c>
       <c r="Q93" s="7" t="n">
-        <v>6129</v>
+        <v>4252</v>
       </c>
       <c r="R93" s="7" t="n">
         <v>1</v>
       </c>
       <c r="S93" s="7" t="n">
-        <v>5721</v>
+        <v>338044</v>
       </c>
       <c r="T93" s="5" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="U93" s="5" t="n">
-        <v>85844</v>
+        <v>482912</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>sodium_intak</t>
+          <t>spo2</t>
         </is>
       </c>
       <c r="B94" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C94" s="7" t="n">
-        <v>28614</v>
+        <v>0</v>
       </c>
       <c r="D94" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>16962</v>
+        <v>0</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>12180</v>
+        <v>10480</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I94" s="7" t="n">
-        <v>0</v>
+        <v>64224</v>
       </c>
       <c r="J94" s="7" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K94" s="7" t="n">
-        <v>82860</v>
+        <v>715</v>
       </c>
       <c r="L94" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M94" s="7" t="n">
-        <v>0</v>
+        <v>22347</v>
       </c>
       <c r="N94" s="7" t="n">
         <v>0</v>
@@ -6847,28 +6847,28 @@
         <v>0</v>
       </c>
       <c r="P94" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q94" s="7" t="n">
-        <v>4252</v>
+        <v>0</v>
       </c>
       <c r="R94" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S94" s="7" t="n">
-        <v>338044</v>
+        <v>0</v>
       </c>
       <c r="T94" s="5" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="U94" s="5" t="n">
-        <v>482912</v>
+        <v>97766</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>spo2</t>
+          <t>tnfa</t>
         </is>
       </c>
       <c r="B95" s="7" t="n">
@@ -6884,28 +6884,28 @@
         <v>0</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>10480</v>
+        <v>0</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I95" s="7" t="n">
-        <v>64224</v>
+        <v>0</v>
       </c>
       <c r="J95" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" s="7" t="n">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="L95" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M95" s="7" t="n">
-        <v>22347</v>
+        <v>0</v>
       </c>
       <c r="N95" s="7" t="n">
         <v>0</v>
@@ -6914,10 +6914,10 @@
         <v>0</v>
       </c>
       <c r="P95" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q95" s="7" t="n">
-        <v>0</v>
+        <v>6524</v>
       </c>
       <c r="R95" s="7" t="n">
         <v>0</v>
@@ -6926,16 +6926,16 @@
         <v>0</v>
       </c>
       <c r="T95" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U95" s="5" t="n">
-        <v>97766</v>
+        <v>6524</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>tnfa</t>
+          <t>tnfa_r1</t>
         </is>
       </c>
       <c r="B96" s="7" t="n">
@@ -6981,10 +6981,10 @@
         <v>0</v>
       </c>
       <c r="P96" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q96" s="7" t="n">
-        <v>6524</v>
+        <v>9242</v>
       </c>
       <c r="R96" s="7" t="n">
         <v>0</v>
@@ -6993,35 +6993,35 @@
         <v>0</v>
       </c>
       <c r="T96" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U96" s="5" t="n">
-        <v>6524</v>
+        <v>9242</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>tnfa_r1</t>
+          <t>tot_chol_bld</t>
         </is>
       </c>
       <c r="B97" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C97" s="7" t="n">
-        <v>0</v>
+        <v>245458</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>0</v>
+        <v>6897</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>0</v>
+        <v>11010</v>
       </c>
       <c r="H97" s="7" t="n">
         <v>0</v>
@@ -7030,65 +7030,65 @@
         <v>0</v>
       </c>
       <c r="J97" s="7" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="K97" s="7" t="n">
-        <v>0</v>
+        <v>218271</v>
       </c>
       <c r="L97" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M97" s="7" t="n">
-        <v>0</v>
+        <v>23653</v>
       </c>
       <c r="N97" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O97" s="7" t="n">
-        <v>0</v>
+        <v>31460</v>
       </c>
       <c r="P97" s="7" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Q97" s="7" t="n">
-        <v>9242</v>
+        <v>68149</v>
       </c>
       <c r="R97" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S97" s="7" t="n">
-        <v>0</v>
+        <v>46610</v>
       </c>
       <c r="T97" s="5" t="n">
-        <v>2</v>
+        <v>131</v>
       </c>
       <c r="U97" s="5" t="n">
-        <v>9242</v>
+        <v>651508</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>tot_chol_bld</t>
+          <t>triglyc_bld</t>
         </is>
       </c>
       <c r="B98" s="7" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C98" s="7" t="n">
-        <v>245458</v>
+        <v>167017</v>
       </c>
       <c r="D98" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>6897</v>
+        <v>16569</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>11010</v>
+        <v>29264</v>
       </c>
       <c r="H98" s="7" t="n">
         <v>0</v>
@@ -7097,10 +7097,10 @@
         <v>0</v>
       </c>
       <c r="J98" s="7" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="K98" s="7" t="n">
-        <v>218271</v>
+        <v>168009</v>
       </c>
       <c r="L98" s="7" t="n">
         <v>2</v>
@@ -7109,16 +7109,16 @@
         <v>23653</v>
       </c>
       <c r="N98" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O98" s="7" t="n">
-        <v>31460</v>
+        <v>32777</v>
       </c>
       <c r="P98" s="7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q98" s="7" t="n">
-        <v>68149</v>
+        <v>67803</v>
       </c>
       <c r="R98" s="7" t="n">
         <v>3</v>
@@ -7127,102 +7127,102 @@
         <v>46610</v>
       </c>
       <c r="T98" s="5" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="U98" s="5" t="n">
-        <v>651508</v>
+        <v>551702</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>triglyc_bld</t>
+          <t>troponin</t>
         </is>
       </c>
       <c r="B99" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C99" s="7" t="n">
+        <v>59241</v>
+      </c>
+      <c r="D99" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E99" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="F99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K99" s="7" t="n">
+        <v>14391</v>
+      </c>
+      <c r="L99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S99" s="7" t="n">
+        <v>4604</v>
+      </c>
+      <c r="T99" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="C99" s="7" t="n">
-        <v>167017</v>
-      </c>
-      <c r="D99" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E99" s="7" t="n">
-        <v>16569</v>
-      </c>
-      <c r="F99" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G99" s="7" t="n">
-        <v>29264</v>
-      </c>
-      <c r="H99" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="K99" s="7" t="n">
-        <v>168009</v>
-      </c>
-      <c r="L99" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M99" s="7" t="n">
-        <v>23653</v>
-      </c>
-      <c r="N99" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="O99" s="7" t="n">
-        <v>32777</v>
-      </c>
-      <c r="P99" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q99" s="7" t="n">
-        <v>67803</v>
-      </c>
-      <c r="R99" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="S99" s="7" t="n">
-        <v>46610</v>
-      </c>
-      <c r="T99" s="5" t="n">
-        <v>117</v>
-      </c>
       <c r="U99" s="5" t="n">
-        <v>551702</v>
+        <v>78313</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>troponin</t>
+          <t>vege_serving</t>
         </is>
       </c>
       <c r="B100" s="7" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C100" s="7" t="n">
-        <v>59241</v>
+        <v>322380</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>77</v>
+        <v>74514</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>0</v>
+        <v>771</v>
       </c>
       <c r="H100" s="7" t="n">
         <v>0</v>
@@ -7231,10 +7231,10 @@
         <v>0</v>
       </c>
       <c r="J100" s="7" t="n">
-        <v>4</v>
+        <v>232</v>
       </c>
       <c r="K100" s="7" t="n">
-        <v>14391</v>
+        <v>638568</v>
       </c>
       <c r="L100" s="7" t="n">
         <v>0</v>
@@ -7243,430 +7243,363 @@
         <v>0</v>
       </c>
       <c r="N100" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O100" s="7" t="n">
-        <v>0</v>
+        <v>7594</v>
       </c>
       <c r="P100" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q100" s="7" t="n">
-        <v>0</v>
+        <v>29869</v>
       </c>
       <c r="R100" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S100" s="7" t="n">
-        <v>4604</v>
+        <v>680137</v>
       </c>
       <c r="T100" s="5" t="n">
-        <v>18</v>
+        <v>300</v>
       </c>
       <c r="U100" s="5" t="n">
-        <v>78313</v>
+        <v>1753833</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>vege_serving</t>
+          <t>waist_circ</t>
         </is>
       </c>
       <c r="B101" s="7" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="C101" s="7" t="n">
-        <v>322380</v>
+        <v>54019</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>74514</v>
+        <v>30185</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>771</v>
+        <v>43939</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>0</v>
+        <v>53850</v>
       </c>
       <c r="J101" s="7" t="n">
-        <v>232</v>
+        <v>55</v>
       </c>
       <c r="K101" s="7" t="n">
-        <v>638568</v>
+        <v>175209</v>
       </c>
       <c r="L101" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M101" s="7" t="n">
-        <v>0</v>
+        <v>23633</v>
       </c>
       <c r="N101" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>7594</v>
+        <v>25409</v>
       </c>
       <c r="P101" s="7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Q101" s="7" t="n">
-        <v>29869</v>
+        <v>56543</v>
       </c>
       <c r="R101" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S101" s="7" t="n">
-        <v>680137</v>
+        <v>1619039</v>
       </c>
       <c r="T101" s="5" t="n">
-        <v>300</v>
+        <v>112</v>
       </c>
       <c r="U101" s="5" t="n">
-        <v>1753833</v>
+        <v>2081826</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>waist_circ</t>
+          <t>waist_hip</t>
         </is>
       </c>
       <c r="B102" s="7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C102" s="7" t="n">
-        <v>54019</v>
+        <v>106654</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>30185</v>
+        <v>388</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>43939</v>
+        <v>0</v>
       </c>
       <c r="H102" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I102" s="7" t="n">
-        <v>53850</v>
+        <v>0</v>
       </c>
       <c r="J102" s="7" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K102" s="7" t="n">
-        <v>175209</v>
+        <v>0</v>
       </c>
       <c r="L102" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M102" s="7" t="n">
-        <v>23633</v>
+        <v>23626</v>
       </c>
       <c r="N102" s="7" t="n">
         <v>8</v>
       </c>
       <c r="O102" s="7" t="n">
-        <v>25409</v>
+        <v>23478</v>
       </c>
       <c r="P102" s="7" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="Q102" s="7" t="n">
-        <v>56543</v>
+        <v>89497</v>
       </c>
       <c r="R102" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S102" s="7" t="n">
-        <v>1619039</v>
+        <v>1610605</v>
       </c>
       <c r="T102" s="5" t="n">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="U102" s="5" t="n">
-        <v>2081826</v>
+        <v>1854248</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>waist_hip</t>
+          <t>whtbld_ct</t>
         </is>
       </c>
       <c r="B103" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C103" s="7" t="n">
+        <v>43076</v>
+      </c>
+      <c r="D103" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="7" t="n">
+        <v>3583</v>
+      </c>
+      <c r="F103" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G103" s="7" t="n">
+        <v>10978</v>
+      </c>
+      <c r="H103" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I103" s="7" t="n">
+        <v>53674</v>
+      </c>
+      <c r="J103" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C103" s="7" t="n">
-        <v>106654</v>
-      </c>
-      <c r="D103" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E103" s="7" t="n">
-        <v>388</v>
-      </c>
-      <c r="F103" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="K103" s="7" t="n">
-        <v>0</v>
+        <v>60160</v>
       </c>
       <c r="L103" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M103" s="7" t="n">
-        <v>23626</v>
+        <v>22911</v>
       </c>
       <c r="N103" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O103" s="7" t="n">
-        <v>23478</v>
+        <v>3377</v>
       </c>
       <c r="P103" s="7" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="Q103" s="7" t="n">
-        <v>89497</v>
+        <v>3656</v>
       </c>
       <c r="R103" s="7" t="n">
         <v>3</v>
       </c>
       <c r="S103" s="7" t="n">
-        <v>1610605</v>
+        <v>623680</v>
       </c>
       <c r="T103" s="5" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="U103" s="5" t="n">
-        <v>1854248</v>
+        <v>825095</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>whtbld_ct</t>
+          <t>willeb_fac</t>
         </is>
       </c>
       <c r="B104" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C104" s="7" t="n">
-        <v>43076</v>
+        <v>14801</v>
       </c>
       <c r="D104" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E104" s="7" t="n">
-        <v>3583</v>
+        <v>6928</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>10978</v>
+        <v>0</v>
       </c>
       <c r="H104" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I104" s="7" t="n">
-        <v>53674</v>
+        <v>0</v>
       </c>
       <c r="J104" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K104" s="7" t="n">
-        <v>60160</v>
+        <v>12072</v>
       </c>
       <c r="L104" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M104" s="7" t="n">
-        <v>22911</v>
+        <v>0</v>
       </c>
       <c r="N104" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O104" s="7" t="n">
-        <v>3377</v>
+        <v>0</v>
       </c>
       <c r="P104" s="7" t="n">
         <v>2</v>
       </c>
       <c r="Q104" s="7" t="n">
-        <v>3656</v>
+        <v>7391</v>
       </c>
       <c r="R104" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S104" s="7" t="n">
-        <v>623680</v>
+        <v>0</v>
       </c>
       <c r="T104" s="5" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="U104" s="5" t="n">
-        <v>825095</v>
+        <v>41192</v>
       </c>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>willeb_fac</t>
-        </is>
-      </c>
-      <c r="B105" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C105" s="7" t="n">
-        <v>14801</v>
-      </c>
-      <c r="D105" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E105" s="7" t="n">
-        <v>6928</v>
-      </c>
-      <c r="F105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K105" s="7" t="n">
-        <v>12072</v>
-      </c>
-      <c r="L105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q105" s="7" t="n">
-        <v>7391</v>
-      </c>
-      <c r="R105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S105" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="U105" s="5" t="n">
-        <v>41192</v>
-      </c>
-    </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="A106" s="8" t="inlineStr">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B106" s="9" t="n">
+      <c r="B105" s="9" t="n">
         <v>1167</v>
       </c>
-      <c r="C106" s="9" t="n">
+      <c r="C105" s="9" t="n">
         <v>11476318</v>
       </c>
-      <c r="D106" s="9" t="n">
+      <c r="D105" s="9" t="n">
         <v>566</v>
       </c>
-      <c r="E106" s="9" t="n">
+      <c r="E105" s="9" t="n">
         <v>1038752</v>
       </c>
-      <c r="F106" s="9" t="n">
+      <c r="F105" s="9" t="n">
         <v>1341</v>
       </c>
-      <c r="G106" s="9" t="n">
+      <c r="G105" s="9" t="n">
         <v>4128699</v>
       </c>
-      <c r="H106" s="9" t="n">
-        <v>108</v>
-      </c>
-      <c r="I106" s="9" t="n">
-        <v>2044151</v>
-      </c>
-      <c r="J106" s="9" t="n">
+      <c r="H105" s="9" t="n">
+        <v>110</v>
+      </c>
+      <c r="I105" s="9" t="n">
+        <v>2088195</v>
+      </c>
+      <c r="J105" s="9" t="n">
         <v>3109</v>
       </c>
-      <c r="K106" s="9" t="n">
+      <c r="K105" s="9" t="n">
         <v>9247109</v>
       </c>
-      <c r="L106" s="9" t="n">
+      <c r="L105" s="9" t="n">
         <v>164</v>
       </c>
-      <c r="M106" s="9" t="n">
+      <c r="M105" s="9" t="n">
         <v>1761687</v>
       </c>
-      <c r="N106" s="9" t="n">
+      <c r="N105" s="9" t="n">
         <v>476</v>
       </c>
-      <c r="O106" s="9" t="n">
+      <c r="O105" s="9" t="n">
         <v>1639132</v>
       </c>
-      <c r="P106" s="9" t="n">
+      <c r="P105" s="9" t="n">
         <v>1192</v>
       </c>
-      <c r="Q106" s="9" t="n">
+      <c r="Q105" s="9" t="n">
         <v>3905239</v>
       </c>
-      <c r="R106" s="9" t="n">
+      <c r="R105" s="9" t="n">
         <v>360</v>
       </c>
-      <c r="S106" s="9" t="n">
+      <c r="S105" s="9" t="n">
         <v>34121402</v>
       </c>
-      <c r="T106" s="9" t="n">
-        <v>8483</v>
-      </c>
-      <c r="U106" s="9" t="n">
-        <v>69362489</v>
+      <c r="T105" s="9" t="n">
+        <v>8485</v>
+      </c>
+      <c r="U105" s="9" t="n">
+        <v>69406533</v>
       </c>
     </row>
   </sheetData>

--- a/tables/before_table.xlsx
+++ b/tables/before_table.xlsx
@@ -647,10 +647,10 @@
         <v>4868066</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>191561</v>
+        <v>154410</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>287</v>
@@ -659,22 +659,22 @@
         <v>878051</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>357328</v>
+        <v>331148</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>662</v>
+        <v>611</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1580952</v>
+        <v>1496855</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>278943</v>
+        <v>267228</v>
       </c>
       <c r="N2" s="4" t="n">
         <v>107</v>
@@ -683,22 +683,22 @@
         <v>474003</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>680731</v>
+        <v>648521</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>8579446</v>
+        <v>8068634</v>
       </c>
       <c r="T2" s="5" t="n">
-        <v>2075</v>
+        <v>1990</v>
       </c>
       <c r="U2" s="5" t="n">
-        <v>17889081</v>
+        <v>17186916</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -7548,10 +7548,10 @@
         <v>11476318</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>566</v>
+        <v>551</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>1038752</v>
+        <v>1001601</v>
       </c>
       <c r="F105" s="9" t="n">
         <v>1341</v>
@@ -7560,22 +7560,22 @@
         <v>4128699</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>2088195</v>
+        <v>2062015</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>3109</v>
+        <v>3058</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>9247109</v>
+        <v>9163012</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M105" s="9" t="n">
-        <v>1761687</v>
+        <v>1749972</v>
       </c>
       <c r="N105" s="9" t="n">
         <v>476</v>
@@ -7584,22 +7584,22 @@
         <v>1639132</v>
       </c>
       <c r="P105" s="9" t="n">
-        <v>1192</v>
+        <v>1183</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>3905239</v>
+        <v>3873029</v>
       </c>
       <c r="R105" s="9" t="n">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="S105" s="9" t="n">
-        <v>34121402</v>
+        <v>33610590</v>
       </c>
       <c r="T105" s="9" t="n">
-        <v>8485</v>
+        <v>8400</v>
       </c>
       <c r="U105" s="9" t="n">
-        <v>69406533</v>
+        <v>68704368</v>
       </c>
     </row>
   </sheetData>

--- a/tables/before_table.xlsx
+++ b/tables/before_table.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U105"/>
+  <dimension ref="A1:U104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>113048</v>
+        <v>126158</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>2</v>
@@ -805,10 +805,10 @@
         <v>28154</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0</v>
+        <v>11848</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>14</v>
@@ -817,10 +817,10 @@
         <v>11088</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>0</v>
+        <v>12922</v>
       </c>
       <c r="R4" s="4" t="n">
         <v>13</v>
@@ -829,10 +829,10 @@
         <v>1236045</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="U4" s="5" t="n">
-        <v>1487492</v>
+        <v>1525372</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -5863,160 +5863,160 @@
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>pacem_stat</t>
+          <t>platelet_ct</t>
         </is>
       </c>
       <c r="B80" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C80" s="7" t="n">
-        <v>13110</v>
+        <v>37442</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>0</v>
+        <v>3581</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>0</v>
+        <v>25046</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I80" s="7" t="n">
-        <v>0</v>
+        <v>53654</v>
       </c>
       <c r="J80" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>0</v>
+        <v>35931</v>
       </c>
       <c r="L80" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M80" s="7" t="n">
-        <v>11848</v>
+        <v>23560</v>
       </c>
       <c r="N80" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" s="7" t="n">
-        <v>0</v>
+        <v>3749</v>
       </c>
       <c r="P80" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q80" s="7" t="n">
-        <v>12922</v>
+        <v>3644</v>
       </c>
       <c r="R80" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S80" s="7" t="n">
-        <v>0</v>
+        <v>623065</v>
       </c>
       <c r="T80" s="5" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="U80" s="5" t="n">
-        <v>37880</v>
+        <v>809672</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>platelet_ct</t>
+          <t>pmv</t>
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>37442</v>
+        <v>5707</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>3581</v>
+        <v>0</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>25046</v>
+        <v>0</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I81" s="7" t="n">
-        <v>53654</v>
+        <v>0</v>
       </c>
       <c r="J81" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>35931</v>
+        <v>32540</v>
       </c>
       <c r="L81" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>23560</v>
+        <v>0</v>
       </c>
       <c r="N81" s="7" t="n">
         <v>1</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>3749</v>
+        <v>3376</v>
       </c>
       <c r="P81" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q81" s="7" t="n">
-        <v>3644</v>
+        <v>0</v>
       </c>
       <c r="R81" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S81" s="7" t="n">
-        <v>623065</v>
+        <v>0</v>
       </c>
       <c r="T81" s="5" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="U81" s="5" t="n">
-        <v>809672</v>
+        <v>41623</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>pmv</t>
+          <t>potassium</t>
         </is>
       </c>
       <c r="B82" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>5707</v>
+        <v>37384</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>0</v>
+        <v>6310</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>0</v>
+        <v>25155</v>
       </c>
       <c r="H82" s="7" t="n">
         <v>0</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="J82" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K82" s="7" t="n">
-        <v>32540</v>
+        <v>0</v>
       </c>
       <c r="L82" s="7" t="n">
         <v>0</v>
@@ -6040,13 +6040,13 @@
         <v>1</v>
       </c>
       <c r="O82" s="7" t="n">
-        <v>3376</v>
+        <v>3839</v>
       </c>
       <c r="P82" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q82" s="7" t="n">
-        <v>0</v>
+        <v>18964</v>
       </c>
       <c r="R82" s="7" t="n">
         <v>0</v>
@@ -6055,35 +6055,35 @@
         <v>0</v>
       </c>
       <c r="T82" s="5" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="U82" s="5" t="n">
-        <v>41623</v>
+        <v>91652</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>potassium</t>
+          <t>pr_ekg</t>
         </is>
       </c>
       <c r="B83" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>37384</v>
+        <v>59015</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>6310</v>
+        <v>0</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>25155</v>
+        <v>0</v>
       </c>
       <c r="H83" s="7" t="n">
         <v>0</v>
@@ -6098,47 +6098,47 @@
         <v>0</v>
       </c>
       <c r="L83" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>0</v>
+        <v>23526</v>
       </c>
       <c r="N83" s="7" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O83" s="7" t="n">
-        <v>3839</v>
+        <v>78673</v>
       </c>
       <c r="P83" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q83" s="7" t="n">
-        <v>18964</v>
+        <v>22435</v>
       </c>
       <c r="R83" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S83" s="7" t="n">
-        <v>0</v>
+        <v>500439</v>
       </c>
       <c r="T83" s="5" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="U83" s="5" t="n">
-        <v>91652</v>
+        <v>684088</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>pr_ekg</t>
+          <t>pr_qrs_qt</t>
         </is>
       </c>
       <c r="B84" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C84" s="7" t="n">
-        <v>59015</v>
+        <v>0</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>0</v>
@@ -6159,46 +6159,46 @@
         <v>0</v>
       </c>
       <c r="J84" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K84" s="7" t="n">
-        <v>0</v>
+        <v>66296</v>
       </c>
       <c r="L84" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M84" s="7" t="n">
-        <v>23526</v>
+        <v>0</v>
       </c>
       <c r="N84" s="7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O84" s="7" t="n">
-        <v>78673</v>
+        <v>0</v>
       </c>
       <c r="P84" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q84" s="7" t="n">
-        <v>22435</v>
+        <v>0</v>
       </c>
       <c r="R84" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S84" s="7" t="n">
-        <v>500439</v>
+        <v>0</v>
       </c>
       <c r="T84" s="5" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="U84" s="5" t="n">
-        <v>684088</v>
+        <v>66296</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>pr_qrs_qt</t>
+          <t>pselectin</t>
         </is>
       </c>
       <c r="B85" s="7" t="n">
@@ -6208,10 +6208,10 @@
         <v>0</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
       <c r="F85" s="7" t="n">
         <v>0</v>
@@ -6226,10 +6226,10 @@
         <v>0</v>
       </c>
       <c r="J85" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>66296</v>
+        <v>0</v>
       </c>
       <c r="L85" s="7" t="n">
         <v>0</v>
@@ -6238,10 +6238,10 @@
         <v>0</v>
       </c>
       <c r="N85" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O85" s="7" t="n">
-        <v>0</v>
+        <v>8299</v>
       </c>
       <c r="P85" s="7" t="n">
         <v>0</v>
@@ -6256,35 +6256,35 @@
         <v>0</v>
       </c>
       <c r="T85" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U85" s="5" t="n">
-        <v>66296</v>
+        <v>8625</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>pselectin</t>
+          <t>qrs_ekg</t>
         </is>
       </c>
       <c r="B86" s="7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>0</v>
+        <v>274284</v>
       </c>
       <c r="D86" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>0</v>
+        <v>43430</v>
       </c>
       <c r="H86" s="7" t="n">
         <v>0</v>
@@ -6293,53 +6293,53 @@
         <v>0</v>
       </c>
       <c r="J86" s="7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>0</v>
+        <v>202581</v>
       </c>
       <c r="L86" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M86" s="7" t="n">
-        <v>0</v>
+        <v>23558</v>
       </c>
       <c r="N86" s="7" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="O86" s="7" t="n">
-        <v>8299</v>
+        <v>65524</v>
       </c>
       <c r="P86" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q86" s="7" t="n">
-        <v>0</v>
+        <v>22514</v>
       </c>
       <c r="R86" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S86" s="7" t="n">
-        <v>0</v>
+        <v>500439</v>
       </c>
       <c r="T86" s="5" t="n">
-        <v>5</v>
+        <v>139</v>
       </c>
       <c r="U86" s="5" t="n">
-        <v>8625</v>
+        <v>1132330</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>qrs_ekg</t>
+          <t>qt_ekg</t>
         </is>
       </c>
       <c r="B87" s="7" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>274284</v>
+        <v>61199</v>
       </c>
       <c r="D87" s="7" t="n">
         <v>0</v>
@@ -6348,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>43430</v>
+        <v>0</v>
       </c>
       <c r="H87" s="7" t="n">
         <v>0</v>
@@ -6360,22 +6360,22 @@
         <v>0</v>
       </c>
       <c r="J87" s="7" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>202581</v>
+        <v>90128</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>23558</v>
+        <v>35283</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>65524</v>
+        <v>46378</v>
       </c>
       <c r="P87" s="7" t="n">
         <v>8</v>
@@ -6390,29 +6390,29 @@
         <v>500439</v>
       </c>
       <c r="T87" s="5" t="n">
-        <v>139</v>
+        <v>54</v>
       </c>
       <c r="U87" s="5" t="n">
-        <v>1132330</v>
+        <v>755941</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>qt_ekg</t>
+          <t>rdbld_ct</t>
         </is>
       </c>
       <c r="B88" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C88" s="7" t="n">
-        <v>61199</v>
+        <v>14728</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>0</v>
+        <v>3583</v>
       </c>
       <c r="F88" s="7" t="n">
         <v>0</v>
@@ -6421,65 +6421,65 @@
         <v>0</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I88" s="7" t="n">
-        <v>0</v>
+        <v>53674</v>
       </c>
       <c r="J88" s="7" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K88" s="7" t="n">
-        <v>90128</v>
+        <v>59154</v>
       </c>
       <c r="L88" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M88" s="7" t="n">
-        <v>35283</v>
+        <v>23567</v>
       </c>
       <c r="N88" s="7" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O88" s="7" t="n">
-        <v>46378</v>
+        <v>3377</v>
       </c>
       <c r="P88" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q88" s="7" t="n">
-        <v>22514</v>
+        <v>3656</v>
       </c>
       <c r="R88" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S88" s="7" t="n">
-        <v>500439</v>
+        <v>0</v>
       </c>
       <c r="T88" s="5" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="U88" s="5" t="n">
-        <v>755941</v>
+        <v>161739</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>rdbld_ct</t>
+          <t>rdw</t>
         </is>
       </c>
       <c r="B89" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>14728</v>
+        <v>12016</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>3583</v>
+        <v>0</v>
       </c>
       <c r="F89" s="7" t="n">
         <v>0</v>
@@ -6488,71 +6488,71 @@
         <v>0</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I89" s="7" t="n">
-        <v>53674</v>
+        <v>0</v>
       </c>
       <c r="J89" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K89" s="7" t="n">
+        <v>32543</v>
+      </c>
+      <c r="L89" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M89" s="7" t="n">
+        <v>23566</v>
+      </c>
+      <c r="N89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="K89" s="7" t="n">
-        <v>59154</v>
-      </c>
-      <c r="L89" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M89" s="7" t="n">
-        <v>23567</v>
-      </c>
-      <c r="N89" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O89" s="7" t="n">
-        <v>3377</v>
-      </c>
-      <c r="P89" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q89" s="7" t="n">
-        <v>3656</v>
-      </c>
-      <c r="R89" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" s="5" t="n">
-        <v>23</v>
-      </c>
       <c r="U89" s="5" t="n">
-        <v>161739</v>
+        <v>68125</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>rdw</t>
+          <t>sleep_duration_daily</t>
         </is>
       </c>
       <c r="B90" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C90" s="7" t="n">
-        <v>12016</v>
+        <v>5925</v>
       </c>
       <c r="D90" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>0</v>
+        <v>3529</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>0</v>
+        <v>13853</v>
       </c>
       <c r="H90" s="7" t="n">
         <v>0</v>
@@ -6561,132 +6561,132 @@
         <v>0</v>
       </c>
       <c r="J90" s="7" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="K90" s="7" t="n">
-        <v>32543</v>
+        <v>129670</v>
       </c>
       <c r="L90" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M90" s="7" t="n">
-        <v>23566</v>
+        <v>23080</v>
       </c>
       <c r="N90" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O90" s="7" t="n">
-        <v>0</v>
+        <v>6955</v>
       </c>
       <c r="P90" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q90" s="7" t="n">
-        <v>0</v>
+        <v>10941</v>
       </c>
       <c r="R90" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S90" s="7" t="n">
-        <v>0</v>
+        <v>626832</v>
       </c>
       <c r="T90" s="5" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="U90" s="5" t="n">
-        <v>68125</v>
+        <v>820785</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>sleep_duration_daily</t>
+          <t>sodium_blood</t>
         </is>
       </c>
       <c r="B91" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>52984</v>
+      </c>
+      <c r="D91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K91" s="7" t="n">
+        <v>17171</v>
+      </c>
+      <c r="L91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="C91" s="7" t="n">
-        <v>5925</v>
-      </c>
-      <c r="D91" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E91" s="7" t="n">
-        <v>3529</v>
-      </c>
-      <c r="F91" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G91" s="7" t="n">
-        <v>13853</v>
-      </c>
-      <c r="H91" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="K91" s="7" t="n">
-        <v>129670</v>
-      </c>
-      <c r="L91" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M91" s="7" t="n">
-        <v>23080</v>
-      </c>
-      <c r="N91" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="O91" s="7" t="n">
-        <v>6955</v>
+        <v>3839</v>
       </c>
       <c r="P91" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q91" s="7" t="n">
-        <v>10941</v>
+        <v>6129</v>
       </c>
       <c r="R91" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S91" s="7" t="n">
-        <v>626832</v>
+        <v>5721</v>
       </c>
       <c r="T91" s="5" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="U91" s="5" t="n">
-        <v>820785</v>
+        <v>85844</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>sodium_blood</t>
+          <t>sodium_intak</t>
         </is>
       </c>
       <c r="B92" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C92" s="7" t="n">
+        <v>28614</v>
+      </c>
+      <c r="D92" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C92" s="7" t="n">
-        <v>52984</v>
-      </c>
-      <c r="D92" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="E92" s="7" t="n">
-        <v>0</v>
+        <v>16962</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>0</v>
+        <v>12180</v>
       </c>
       <c r="H92" s="7" t="n">
         <v>0</v>
@@ -6695,10 +6695,10 @@
         <v>0</v>
       </c>
       <c r="J92" s="7" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="K92" s="7" t="n">
-        <v>17171</v>
+        <v>82860</v>
       </c>
       <c r="L92" s="7" t="n">
         <v>0</v>
@@ -6707,71 +6707,71 @@
         <v>0</v>
       </c>
       <c r="N92" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" s="7" t="n">
-        <v>3839</v>
+        <v>0</v>
       </c>
       <c r="P92" s="7" t="n">
         <v>1</v>
       </c>
       <c r="Q92" s="7" t="n">
-        <v>6129</v>
+        <v>4252</v>
       </c>
       <c r="R92" s="7" t="n">
         <v>1</v>
       </c>
       <c r="S92" s="7" t="n">
-        <v>5721</v>
+        <v>338044</v>
       </c>
       <c r="T92" s="5" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="U92" s="5" t="n">
-        <v>85844</v>
+        <v>482912</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>sodium_intak</t>
+          <t>spo2</t>
         </is>
       </c>
       <c r="B93" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>28614</v>
+        <v>0</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>16962</v>
+        <v>0</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>12180</v>
+        <v>10480</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>0</v>
+        <v>64224</v>
       </c>
       <c r="J93" s="7" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K93" s="7" t="n">
-        <v>82860</v>
+        <v>715</v>
       </c>
       <c r="L93" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M93" s="7" t="n">
-        <v>0</v>
+        <v>22347</v>
       </c>
       <c r="N93" s="7" t="n">
         <v>0</v>
@@ -6780,28 +6780,28 @@
         <v>0</v>
       </c>
       <c r="P93" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q93" s="7" t="n">
-        <v>4252</v>
+        <v>0</v>
       </c>
       <c r="R93" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S93" s="7" t="n">
-        <v>338044</v>
+        <v>0</v>
       </c>
       <c r="T93" s="5" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="U93" s="5" t="n">
-        <v>482912</v>
+        <v>97766</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>spo2</t>
+          <t>tnfa</t>
         </is>
       </c>
       <c r="B94" s="7" t="n">
@@ -6817,28 +6817,28 @@
         <v>0</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>10480</v>
+        <v>0</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I94" s="7" t="n">
-        <v>64224</v>
+        <v>0</v>
       </c>
       <c r="J94" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" s="7" t="n">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="L94" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M94" s="7" t="n">
-        <v>22347</v>
+        <v>0</v>
       </c>
       <c r="N94" s="7" t="n">
         <v>0</v>
@@ -6847,10 +6847,10 @@
         <v>0</v>
       </c>
       <c r="P94" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q94" s="7" t="n">
-        <v>0</v>
+        <v>6524</v>
       </c>
       <c r="R94" s="7" t="n">
         <v>0</v>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="T94" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U94" s="5" t="n">
-        <v>97766</v>
+        <v>6524</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>tnfa</t>
+          <t>tnfa_r1</t>
         </is>
       </c>
       <c r="B95" s="7" t="n">
@@ -6914,10 +6914,10 @@
         <v>0</v>
       </c>
       <c r="P95" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q95" s="7" t="n">
-        <v>6524</v>
+        <v>9242</v>
       </c>
       <c r="R95" s="7" t="n">
         <v>0</v>
@@ -6926,35 +6926,35 @@
         <v>0</v>
       </c>
       <c r="T95" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U95" s="5" t="n">
-        <v>6524</v>
+        <v>9242</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>tnfa_r1</t>
+          <t>tot_chol_bld</t>
         </is>
       </c>
       <c r="B96" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C96" s="7" t="n">
-        <v>0</v>
+        <v>245458</v>
       </c>
       <c r="D96" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E96" s="7" t="n">
-        <v>0</v>
+        <v>6897</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G96" s="7" t="n">
-        <v>0</v>
+        <v>11010</v>
       </c>
       <c r="H96" s="7" t="n">
         <v>0</v>
@@ -6963,65 +6963,65 @@
         <v>0</v>
       </c>
       <c r="J96" s="7" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="K96" s="7" t="n">
-        <v>0</v>
+        <v>218271</v>
       </c>
       <c r="L96" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M96" s="7" t="n">
-        <v>0</v>
+        <v>23653</v>
       </c>
       <c r="N96" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O96" s="7" t="n">
-        <v>0</v>
+        <v>31460</v>
       </c>
       <c r="P96" s="7" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Q96" s="7" t="n">
-        <v>9242</v>
+        <v>68149</v>
       </c>
       <c r="R96" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S96" s="7" t="n">
-        <v>0</v>
+        <v>46610</v>
       </c>
       <c r="T96" s="5" t="n">
-        <v>2</v>
+        <v>131</v>
       </c>
       <c r="U96" s="5" t="n">
-        <v>9242</v>
+        <v>651508</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>tot_chol_bld</t>
+          <t>triglyc_bld</t>
         </is>
       </c>
       <c r="B97" s="7" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C97" s="7" t="n">
-        <v>245458</v>
+        <v>167017</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>6897</v>
+        <v>16569</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>11010</v>
+        <v>29264</v>
       </c>
       <c r="H97" s="7" t="n">
         <v>0</v>
@@ -7030,10 +7030,10 @@
         <v>0</v>
       </c>
       <c r="J97" s="7" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="K97" s="7" t="n">
-        <v>218271</v>
+        <v>168009</v>
       </c>
       <c r="L97" s="7" t="n">
         <v>2</v>
@@ -7042,16 +7042,16 @@
         <v>23653</v>
       </c>
       <c r="N97" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O97" s="7" t="n">
-        <v>31460</v>
+        <v>32777</v>
       </c>
       <c r="P97" s="7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Q97" s="7" t="n">
-        <v>68149</v>
+        <v>67803</v>
       </c>
       <c r="R97" s="7" t="n">
         <v>3</v>
@@ -7060,102 +7060,102 @@
         <v>46610</v>
       </c>
       <c r="T97" s="5" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="U97" s="5" t="n">
-        <v>651508</v>
+        <v>551702</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>triglyc_bld</t>
+          <t>troponin</t>
         </is>
       </c>
       <c r="B98" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C98" s="7" t="n">
+        <v>59241</v>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="F98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K98" s="7" t="n">
+        <v>14391</v>
+      </c>
+      <c r="L98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S98" s="7" t="n">
+        <v>4604</v>
+      </c>
+      <c r="T98" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="C98" s="7" t="n">
-        <v>167017</v>
-      </c>
-      <c r="D98" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E98" s="7" t="n">
-        <v>16569</v>
-      </c>
-      <c r="F98" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G98" s="7" t="n">
-        <v>29264</v>
-      </c>
-      <c r="H98" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="K98" s="7" t="n">
-        <v>168009</v>
-      </c>
-      <c r="L98" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M98" s="7" t="n">
-        <v>23653</v>
-      </c>
-      <c r="N98" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="O98" s="7" t="n">
-        <v>32777</v>
-      </c>
-      <c r="P98" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q98" s="7" t="n">
-        <v>67803</v>
-      </c>
-      <c r="R98" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="S98" s="7" t="n">
-        <v>46610</v>
-      </c>
-      <c r="T98" s="5" t="n">
-        <v>117</v>
-      </c>
       <c r="U98" s="5" t="n">
-        <v>551702</v>
+        <v>78313</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>troponin</t>
+          <t>vege_serving</t>
         </is>
       </c>
       <c r="B99" s="7" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C99" s="7" t="n">
-        <v>59241</v>
+        <v>322380</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>77</v>
+        <v>74514</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>0</v>
+        <v>771</v>
       </c>
       <c r="H99" s="7" t="n">
         <v>0</v>
@@ -7164,10 +7164,10 @@
         <v>0</v>
       </c>
       <c r="J99" s="7" t="n">
-        <v>4</v>
+        <v>232</v>
       </c>
       <c r="K99" s="7" t="n">
-        <v>14391</v>
+        <v>638568</v>
       </c>
       <c r="L99" s="7" t="n">
         <v>0</v>
@@ -7176,429 +7176,362 @@
         <v>0</v>
       </c>
       <c r="N99" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O99" s="7" t="n">
-        <v>0</v>
+        <v>7594</v>
       </c>
       <c r="P99" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q99" s="7" t="n">
-        <v>0</v>
+        <v>29869</v>
       </c>
       <c r="R99" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S99" s="7" t="n">
-        <v>4604</v>
+        <v>680137</v>
       </c>
       <c r="T99" s="5" t="n">
-        <v>18</v>
+        <v>300</v>
       </c>
       <c r="U99" s="5" t="n">
-        <v>78313</v>
+        <v>1753833</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>vege_serving</t>
+          <t>waist_circ</t>
         </is>
       </c>
       <c r="B100" s="7" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="C100" s="7" t="n">
-        <v>322380</v>
+        <v>54019</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>74514</v>
+        <v>30185</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>771</v>
+        <v>43939</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I100" s="7" t="n">
-        <v>0</v>
+        <v>53850</v>
       </c>
       <c r="J100" s="7" t="n">
-        <v>232</v>
+        <v>55</v>
       </c>
       <c r="K100" s="7" t="n">
-        <v>638568</v>
+        <v>175209</v>
       </c>
       <c r="L100" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M100" s="7" t="n">
-        <v>0</v>
+        <v>23633</v>
       </c>
       <c r="N100" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O100" s="7" t="n">
-        <v>7594</v>
+        <v>25409</v>
       </c>
       <c r="P100" s="7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Q100" s="7" t="n">
-        <v>29869</v>
+        <v>56543</v>
       </c>
       <c r="R100" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S100" s="7" t="n">
-        <v>680137</v>
+        <v>1619039</v>
       </c>
       <c r="T100" s="5" t="n">
-        <v>300</v>
+        <v>112</v>
       </c>
       <c r="U100" s="5" t="n">
-        <v>1753833</v>
+        <v>2081826</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>waist_circ</t>
+          <t>waist_hip</t>
         </is>
       </c>
       <c r="B101" s="7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C101" s="7" t="n">
-        <v>54019</v>
+        <v>106654</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>30185</v>
+        <v>388</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>43939</v>
+        <v>0</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I101" s="7" t="n">
-        <v>53850</v>
+        <v>0</v>
       </c>
       <c r="J101" s="7" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K101" s="7" t="n">
-        <v>175209</v>
+        <v>0</v>
       </c>
       <c r="L101" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M101" s="7" t="n">
-        <v>23633</v>
+        <v>23626</v>
       </c>
       <c r="N101" s="7" t="n">
         <v>8</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>25409</v>
+        <v>23478</v>
       </c>
       <c r="P101" s="7" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="Q101" s="7" t="n">
-        <v>56543</v>
+        <v>89497</v>
       </c>
       <c r="R101" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S101" s="7" t="n">
-        <v>1619039</v>
+        <v>1610605</v>
       </c>
       <c r="T101" s="5" t="n">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="U101" s="5" t="n">
-        <v>2081826</v>
+        <v>1854248</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>waist_hip</t>
+          <t>whtbld_ct</t>
         </is>
       </c>
       <c r="B102" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C102" s="7" t="n">
+        <v>43076</v>
+      </c>
+      <c r="D102" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="7" t="n">
+        <v>3583</v>
+      </c>
+      <c r="F102" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G102" s="7" t="n">
+        <v>10978</v>
+      </c>
+      <c r="H102" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I102" s="7" t="n">
+        <v>53674</v>
+      </c>
+      <c r="J102" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="C102" s="7" t="n">
-        <v>106654</v>
-      </c>
-      <c r="D102" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E102" s="7" t="n">
-        <v>388</v>
-      </c>
-      <c r="F102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="K102" s="7" t="n">
-        <v>0</v>
+        <v>60160</v>
       </c>
       <c r="L102" s="7" t="n">
         <v>2</v>
       </c>
       <c r="M102" s="7" t="n">
-        <v>23626</v>
+        <v>22911</v>
       </c>
       <c r="N102" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O102" s="7" t="n">
-        <v>23478</v>
+        <v>3377</v>
       </c>
       <c r="P102" s="7" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="Q102" s="7" t="n">
-        <v>89497</v>
+        <v>3656</v>
       </c>
       <c r="R102" s="7" t="n">
         <v>3</v>
       </c>
       <c r="S102" s="7" t="n">
-        <v>1610605</v>
+        <v>623680</v>
       </c>
       <c r="T102" s="5" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="U102" s="5" t="n">
-        <v>1854248</v>
+        <v>825095</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>whtbld_ct</t>
+          <t>willeb_fac</t>
         </is>
       </c>
       <c r="B103" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C103" s="7" t="n">
-        <v>43076</v>
+        <v>14801</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>3583</v>
+        <v>6928</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>10978</v>
+        <v>0</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I103" s="7" t="n">
-        <v>53674</v>
+        <v>0</v>
       </c>
       <c r="J103" s="7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K103" s="7" t="n">
-        <v>60160</v>
+        <v>12072</v>
       </c>
       <c r="L103" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M103" s="7" t="n">
-        <v>22911</v>
+        <v>0</v>
       </c>
       <c r="N103" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O103" s="7" t="n">
-        <v>3377</v>
+        <v>0</v>
       </c>
       <c r="P103" s="7" t="n">
         <v>2</v>
       </c>
       <c r="Q103" s="7" t="n">
-        <v>3656</v>
+        <v>7391</v>
       </c>
       <c r="R103" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S103" s="7" t="n">
-        <v>623680</v>
+        <v>0</v>
       </c>
       <c r="T103" s="5" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="U103" s="5" t="n">
-        <v>825095</v>
+        <v>41192</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
-      <c r="A104" s="6" t="inlineStr">
-        <is>
-          <t>willeb_fac</t>
-        </is>
-      </c>
-      <c r="B104" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C104" s="7" t="n">
-        <v>14801</v>
-      </c>
-      <c r="D104" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E104" s="7" t="n">
-        <v>6928</v>
-      </c>
-      <c r="F104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K104" s="7" t="n">
-        <v>12072</v>
-      </c>
-      <c r="L104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q104" s="7" t="n">
-        <v>7391</v>
-      </c>
-      <c r="R104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="U104" s="5" t="n">
-        <v>41192</v>
-      </c>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="8" t="inlineStr">
+      <c r="A104" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B105" s="9" t="n">
+      <c r="B104" s="9" t="n">
         <v>1167</v>
       </c>
-      <c r="C105" s="9" t="n">
+      <c r="C104" s="9" t="n">
         <v>11476318</v>
       </c>
-      <c r="D105" s="9" t="n">
+      <c r="D104" s="9" t="n">
         <v>551</v>
       </c>
-      <c r="E105" s="9" t="n">
+      <c r="E104" s="9" t="n">
         <v>1001601</v>
       </c>
-      <c r="F105" s="9" t="n">
+      <c r="F104" s="9" t="n">
         <v>1341</v>
       </c>
-      <c r="G105" s="9" t="n">
+      <c r="G104" s="9" t="n">
         <v>4128699</v>
       </c>
-      <c r="H105" s="9" t="n">
+      <c r="H104" s="9" t="n">
         <v>108</v>
       </c>
-      <c r="I105" s="9" t="n">
+      <c r="I104" s="9" t="n">
         <v>2062015</v>
       </c>
-      <c r="J105" s="9" t="n">
+      <c r="J104" s="9" t="n">
         <v>3058</v>
       </c>
-      <c r="K105" s="9" t="n">
+      <c r="K104" s="9" t="n">
         <v>9163012</v>
       </c>
-      <c r="L105" s="9" t="n">
+      <c r="L104" s="9" t="n">
         <v>163</v>
       </c>
-      <c r="M105" s="9" t="n">
+      <c r="M104" s="9" t="n">
         <v>1749972</v>
       </c>
-      <c r="N105" s="9" t="n">
+      <c r="N104" s="9" t="n">
         <v>476</v>
       </c>
-      <c r="O105" s="9" t="n">
+      <c r="O104" s="9" t="n">
         <v>1639132</v>
       </c>
-      <c r="P105" s="9" t="n">
+      <c r="P104" s="9" t="n">
         <v>1183</v>
       </c>
-      <c r="Q105" s="9" t="n">
+      <c r="Q104" s="9" t="n">
         <v>3873029</v>
       </c>
-      <c r="R105" s="9" t="n">
+      <c r="R104" s="9" t="n">
         <v>353</v>
       </c>
-      <c r="S105" s="9" t="n">
+      <c r="S104" s="9" t="n">
         <v>33610590</v>
       </c>
-      <c r="T105" s="9" t="n">
+      <c r="T104" s="9" t="n">
         <v>8400</v>
       </c>
-      <c r="U105" s="9" t="n">
+      <c r="U104" s="9" t="n">
         <v>68704368</v>
       </c>
     </row>

--- a/tables/before_table.xlsx
+++ b/tables/before_table.xlsx
@@ -641,64 +641,64 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4868066</v>
+        <v>4825794</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>154410</v>
+        <v>145591</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>878051</v>
+        <v>858601</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>331148</v>
+        <v>296446</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>611</v>
+        <v>570</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1496855</v>
+        <v>1299302</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>267228</v>
+        <v>249094</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>474003</v>
+        <v>459028</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>648521</v>
+        <v>624842</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>8068634</v>
+        <v>7517225</v>
       </c>
       <c r="T2" s="5" t="n">
-        <v>1990</v>
+        <v>1782</v>
       </c>
       <c r="U2" s="5" t="n">
-        <v>17186916</v>
+        <v>16275923</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
@@ -708,64 +708,64 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>522633</v>
+        <v>0</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>25020</v>
+        <v>9952</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1591435</v>
+        <v>0</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>87430</v>
+        <v>65408</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>709242</v>
+        <v>681549</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>188958</v>
+        <v>0</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>172944</v>
+        <v>0</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>255</v>
+        <v>56</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>879620</v>
+        <v>205177</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>1112650</v>
+        <v>0</v>
       </c>
       <c r="T3" s="5" t="n">
-        <v>1289</v>
+        <v>469</v>
       </c>
       <c r="U3" s="5" t="n">
-        <v>5289932</v>
+        <v>962086</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -781,7 +781,7 @@
         <v>126158</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
@@ -793,46 +793,46 @@
         <v>34126</v>
       </c>
       <c r="H4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>43009</v>
+      </c>
+      <c r="J4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="4" t="n">
-        <v>65031</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>15</v>
-      </c>
       <c r="K4" s="4" t="n">
-        <v>28154</v>
+        <v>8853</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>11848</v>
+        <v>17</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>11088</v>
+        <v>2548</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>12922</v>
+        <v>6403</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>1236045</v>
+        <v>285473</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="U4" s="5" t="n">
-        <v>1525372</v>
+        <v>506587</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -854,10 +854,10 @@
         <v>3583</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>32360</v>
+        <v>17846</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>0</v>
@@ -866,10 +866,10 @@
         <v>0</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>61223</v>
+        <v>16370</v>
       </c>
       <c r="L5" s="7" t="n">
         <v>0</v>
@@ -896,10 +896,10 @@
         <v>0</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>115140</v>
+        <v>55773</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -939,10 +939,10 @@
         <v>0</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>23162</v>
+        <v>11331</v>
       </c>
       <c r="N6" s="7" t="n">
         <v>2</v>
@@ -951,10 +951,10 @@
         <v>4810</v>
       </c>
       <c r="P6" s="7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q6" s="7" t="n">
-        <v>45400</v>
+        <v>22540</v>
       </c>
       <c r="R6" s="7" t="n">
         <v>0</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="U6" s="5" t="n">
-        <v>79299</v>
+        <v>44608</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -1000,16 +1000,16 @@
         <v>0</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>96443</v>
+        <v>28722</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>23161</v>
+        <v>11330</v>
       </c>
       <c r="N7" s="7" t="n">
         <v>9</v>
@@ -1018,10 +1018,10 @@
         <v>15128</v>
       </c>
       <c r="P7" s="7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>48594</v>
+        <v>24118</v>
       </c>
       <c r="R7" s="7" t="n">
         <v>0</v>
@@ -1030,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>208292</v>
+        <v>104264</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -1055,16 +1055,16 @@
         <v>70762</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>77508</v>
+        <v>41781</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>48863</v>
+        <v>4819</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>0</v>
@@ -1079,16 +1079,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>13255</v>
+        <v>6555</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>77728</v>
+        <v>47747</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>2</v>
@@ -1097,10 +1097,10 @@
         <v>480675</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="U8" s="5" t="n">
-        <v>768791</v>
+        <v>652339</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -1134,10 +1134,10 @@
         <v>0</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>61921</v>
+        <v>17068</v>
       </c>
       <c r="L9" s="7" t="n">
         <v>0</v>
@@ -1164,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v>61921</v>
+        <v>17068</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -1201,16 +1201,16 @@
         <v>0</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>6355</v>
+        <v>2505</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>22317</v>
+        <v>10486</v>
       </c>
       <c r="N10" s="7" t="n">
         <v>0</v>
@@ -1231,10 +1231,10 @@
         <v>0</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="U10" s="5" t="n">
-        <v>233026</v>
+        <v>217345</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -1268,10 +1268,10 @@
         <v>0</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>60437</v>
+        <v>15584</v>
       </c>
       <c r="L11" s="7" t="n">
         <v>0</v>
@@ -1298,10 +1298,10 @@
         <v>0</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="U11" s="5" t="n">
-        <v>64018</v>
+        <v>19165</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -1317,10 +1317,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>340</v>
+        <v>151</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>0</v>
@@ -1329,22 +1329,22 @@
         <v>0</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>53587</v>
+        <v>9543</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>32540</v>
+        <v>5287</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>22894</v>
+        <v>11063</v>
       </c>
       <c r="N12" s="7" t="n">
         <v>0</v>
@@ -1365,10 +1365,10 @@
         <v>0</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="U12" s="5" t="n">
-        <v>112487</v>
+        <v>29170</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -1378,64 +1378,64 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>95859</v>
+        <v>77178</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>40007</v>
+        <v>33036</v>
       </c>
       <c r="F13" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>18890</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>20207</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>160050</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>21370</v>
+      </c>
+      <c r="N13" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="G13" s="7" t="n">
-        <v>34019</v>
-      </c>
-      <c r="H13" s="7" t="n">
+      <c r="O13" s="7" t="n">
+        <v>31163</v>
+      </c>
+      <c r="P13" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q13" s="7" t="n">
+        <v>34249</v>
+      </c>
+      <c r="R13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="7" t="n">
-        <v>64251</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>110</v>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>282446</v>
-      </c>
-      <c r="L13" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>33201</v>
-      </c>
-      <c r="N13" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="O13" s="7" t="n">
-        <v>40969</v>
-      </c>
-      <c r="P13" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q13" s="7" t="n">
-        <v>68674</v>
-      </c>
-      <c r="R13" s="7" t="n">
-        <v>5</v>
-      </c>
       <c r="S13" s="7" t="n">
-        <v>1852916</v>
+        <v>621786</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>200</v>
+        <v>135</v>
       </c>
       <c r="U13" s="5" t="n">
-        <v>2512342</v>
+        <v>1017929</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -1487,10 +1487,10 @@
         <v>0</v>
       </c>
       <c r="P14" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>7647</v>
+        <v>3789</v>
       </c>
       <c r="R14" s="7" t="n">
         <v>0</v>
@@ -1499,10 +1499,10 @@
         <v>0</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>7647</v>
+        <v>3789</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1512,64 +1512,64 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>35703</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>34874</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>20206</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>120650</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>30276</v>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" s="7" t="n">
+        <v>13512</v>
+      </c>
+      <c r="P15" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q15" s="7" t="n">
+        <v>29010</v>
+      </c>
+      <c r="R15" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="C15" s="7" t="n">
-        <v>63657</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>36242</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>57898</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>64250</v>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>78</v>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>239196</v>
-      </c>
-      <c r="L15" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M15" s="7" t="n">
-        <v>42107</v>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="O15" s="7" t="n">
-        <v>23318</v>
-      </c>
-      <c r="P15" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q15" s="7" t="n">
-        <v>41958</v>
-      </c>
-      <c r="R15" s="7" t="n">
-        <v>10</v>
-      </c>
       <c r="S15" s="7" t="n">
-        <v>2297360</v>
+        <v>1066230</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>158</v>
+        <v>103</v>
       </c>
       <c r="U15" s="5" t="n">
-        <v>2865986</v>
+        <v>1409298</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -1603,10 +1603,10 @@
         <v>0</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>16127</v>
+        <v>3580</v>
       </c>
       <c r="L16" s="7" t="n">
         <v>0</v>
@@ -1633,10 +1633,10 @@
         <v>0</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" s="5" t="n">
-        <v>16127</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -1670,10 +1670,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>61431</v>
+        <v>16578</v>
       </c>
       <c r="L17" s="7" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="U17" s="5" t="n">
-        <v>65014</v>
+        <v>20161</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>1003408</v>
+        <v>983732</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>4</v>
@@ -1725,52 +1725,52 @@
         <v>7596</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>130363</v>
+        <v>84209</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>84438</v>
+        <v>40394</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>408522</v>
+        <v>289976</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>35476</v>
+        <v>23645</v>
       </c>
       <c r="N18" s="7" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>97134</v>
+        <v>87328</v>
       </c>
       <c r="P18" s="7" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>89867</v>
+        <v>59712</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>3726863</v>
+        <v>2495733</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>391</v>
+        <v>327</v>
       </c>
       <c r="U18" s="5" t="n">
-        <v>5583667</v>
+        <v>4072325</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -1786,58 +1786,58 @@
         <v>15611</v>
       </c>
       <c r="D19" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>20246</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>18860</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>20206</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>92024</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>11798</v>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" s="7" t="n">
+        <v>9634</v>
+      </c>
+      <c r="P19" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="E19" s="7" t="n">
-        <v>20435</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>33989</v>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>64250</v>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>214420</v>
-      </c>
-      <c r="L19" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" s="7" t="n">
-        <v>23629</v>
-      </c>
-      <c r="N19" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="O19" s="7" t="n">
-        <v>19440</v>
-      </c>
-      <c r="P19" s="7" t="n">
-        <v>16</v>
-      </c>
       <c r="Q19" s="7" t="n">
-        <v>59750</v>
+        <v>29769</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>1849280</v>
+        <v>618150</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="U19" s="5" t="n">
-        <v>2300804</v>
+        <v>836298</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>39457</v>
+        <v>29485</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>1</v>
@@ -1871,10 +1871,10 @@
         <v>0</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>11965</v>
+        <v>4424</v>
       </c>
       <c r="L20" s="7" t="n">
         <v>0</v>
@@ -1901,10 +1901,10 @@
         <v>7028</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U20" s="5" t="n">
-        <v>63171</v>
+        <v>45658</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1938,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>40549</v>
+        <v>10402</v>
       </c>
       <c r="L21" s="7" t="n">
         <v>0</v>
@@ -1968,10 +1968,10 @@
         <v>5928</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U21" s="5" t="n">
-        <v>64168</v>
+        <v>34021</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1987,28 +1987,28 @@
         <v>0</v>
       </c>
       <c r="D22" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>16944</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>554</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="E22" s="7" t="n">
-        <v>17133</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>12170</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="7" t="n">
-        <v>11</v>
-      </c>
       <c r="K22" s="7" t="n">
-        <v>36330</v>
+        <v>13705</v>
       </c>
       <c r="L22" s="7" t="n">
         <v>0</v>
@@ -2023,10 +2023,10 @@
         <v>2144</v>
       </c>
       <c r="P22" s="7" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>185186</v>
+        <v>155205</v>
       </c>
       <c r="R22" s="7" t="n">
         <v>0</v>
@@ -2035,10 +2035,10 @@
         <v>0</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="U22" s="5" t="n">
-        <v>252963</v>
+        <v>188552</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2090,10 +2090,10 @@
         <v>0</v>
       </c>
       <c r="P23" s="7" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>145982</v>
+        <v>116001</v>
       </c>
       <c r="R23" s="7" t="n">
         <v>0</v>
@@ -2102,10 +2102,10 @@
         <v>0</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="U23" s="5" t="n">
-        <v>148833</v>
+        <v>118852</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>59398</v>
+        <v>48336</v>
       </c>
       <c r="H24" s="7" t="n">
         <v>0</v>
@@ -2139,10 +2139,10 @@
         <v>0</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>20515</v>
+        <v>12974</v>
       </c>
       <c r="L24" s="7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>19862</v>
       </c>
       <c r="P24" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>13345</v>
+        <v>6719</v>
       </c>
       <c r="R24" s="7" t="n">
         <v>0</v>
@@ -2169,10 +2169,10 @@
         <v>0</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="U24" s="5" t="n">
-        <v>453212</v>
+        <v>427983</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2194,10 +2194,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>15520</v>
+        <v>4458</v>
       </c>
       <c r="H25" s="7" t="n">
         <v>0</v>
@@ -2206,10 +2206,10 @@
         <v>0</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>10779</v>
+        <v>3238</v>
       </c>
       <c r="L25" s="7" t="n">
         <v>0</v>
@@ -2224,10 +2224,10 @@
         <v>0</v>
       </c>
       <c r="P25" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>12791</v>
+        <v>6362</v>
       </c>
       <c r="R25" s="7" t="n">
         <v>0</v>
@@ -2236,10 +2236,10 @@
         <v>0</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U25" s="5" t="n">
-        <v>39255</v>
+        <v>14223</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2261,10 +2261,10 @@
         <v>0</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>15537</v>
+        <v>4475</v>
       </c>
       <c r="H26" s="7" t="n">
         <v>0</v>
@@ -2273,10 +2273,10 @@
         <v>0</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>10786</v>
+        <v>3245</v>
       </c>
       <c r="L26" s="7" t="n">
         <v>0</v>
@@ -2291,10 +2291,10 @@
         <v>0</v>
       </c>
       <c r="P26" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="7" t="n">
-        <v>12791</v>
+        <v>6362</v>
       </c>
       <c r="R26" s="7" t="n">
         <v>0</v>
@@ -2303,10 +2303,10 @@
         <v>0</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U26" s="5" t="n">
-        <v>39276</v>
+        <v>14244</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2358,10 +2358,10 @@
         <v>0</v>
       </c>
       <c r="P27" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>7393</v>
+        <v>964</v>
       </c>
       <c r="R27" s="7" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" s="5" t="n">
-        <v>7393</v>
+        <v>964</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>27247</v>
+        <v>13350</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>3</v>
@@ -2413,22 +2413,22 @@
         <v>144</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>23495</v>
+        <v>11664</v>
       </c>
       <c r="N28" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>6423</v>
+        <v>2540</v>
       </c>
       <c r="P28" s="7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>47837</v>
+        <v>23756</v>
       </c>
       <c r="R28" s="7" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="U28" s="5" t="n">
-        <v>114133</v>
+        <v>60441</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         <v>0</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>19616</v>
+        <v>4558</v>
       </c>
       <c r="L29" s="7" t="n">
         <v>0</v>
@@ -2504,10 +2504,10 @@
         <v>0</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U29" s="5" t="n">
-        <v>35411</v>
+        <v>20353</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>173641</v>
+        <v>158005</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>2</v>
@@ -2529,28 +2529,28 @@
         <v>5084</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>84173</v>
+        <v>44762</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>66043</v>
+        <v>21999</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>225600</v>
+        <v>109290</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>28449</v>
+        <v>16618</v>
       </c>
       <c r="N30" s="7" t="n">
         <v>4</v>
@@ -2559,10 +2559,10 @@
         <v>12859</v>
       </c>
       <c r="P30" s="7" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>87578</v>
+        <v>59582</v>
       </c>
       <c r="R30" s="7" t="n">
         <v>1</v>
@@ -2571,10 +2571,10 @@
         <v>141363</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>160</v>
+        <v>104</v>
       </c>
       <c r="U30" s="5" t="n">
-        <v>824790</v>
+        <v>569562</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>220393</v>
+        <v>174808</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>2</v>
@@ -2608,28 +2608,28 @@
         <v>0</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>159845</v>
+        <v>65161</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>23654</v>
+        <v>11823</v>
       </c>
       <c r="N31" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>23763</v>
+        <v>17063</v>
       </c>
       <c r="P31" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q31" s="7" t="n">
-        <v>9186</v>
+        <v>4534</v>
       </c>
       <c r="R31" s="7" t="n">
         <v>1</v>
@@ -2638,10 +2638,10 @@
         <v>5987</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="U31" s="5" t="n">
-        <v>449279</v>
+        <v>285827</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2675,28 +2675,28 @@
         <v>0</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>87104</v>
+        <v>18541</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>23618</v>
+        <v>11787</v>
       </c>
       <c r="N32" s="7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O32" s="7" t="n">
-        <v>23244</v>
+        <v>13438</v>
       </c>
       <c r="P32" s="7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q32" s="7" t="n">
-        <v>48092</v>
+        <v>23867</v>
       </c>
       <c r="R32" s="7" t="n">
         <v>0</v>
@@ -2705,10 +2705,10 @@
         <v>0</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="U32" s="5" t="n">
-        <v>197428</v>
+        <v>83003</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>20542</v>
+        <v>9547</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>3</v>
@@ -2730,40 +2730,40 @@
         <v>9585</v>
       </c>
       <c r="F33" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>9841</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>33494</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>11820</v>
+      </c>
+      <c r="N33" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="G33" s="7" t="n">
-        <v>20288</v>
-      </c>
-      <c r="H33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>109598</v>
-      </c>
-      <c r="L33" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M33" s="7" t="n">
-        <v>23651</v>
-      </c>
-      <c r="N33" s="7" t="n">
-        <v>9</v>
-      </c>
       <c r="O33" s="7" t="n">
-        <v>27442</v>
+        <v>17636</v>
       </c>
       <c r="P33" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q33" s="7" t="n">
-        <v>23290</v>
+        <v>9489</v>
       </c>
       <c r="R33" s="7" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="U33" s="5" t="n">
-        <v>234396</v>
+        <v>101412</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>69181</v>
+        <v>38650</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>0</v>
@@ -2809,16 +2809,16 @@
         <v>0</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>10725</v>
+        <v>3189</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>23569</v>
+        <v>11738</v>
       </c>
       <c r="N34" s="7" t="n">
         <v>1</v>
@@ -2827,10 +2827,10 @@
         <v>3783</v>
       </c>
       <c r="P34" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="7" t="n">
-        <v>21600</v>
+        <v>10716</v>
       </c>
       <c r="R34" s="7" t="n">
         <v>0</v>
@@ -2839,10 +2839,10 @@
         <v>0</v>
       </c>
       <c r="T34" s="5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="U34" s="5" t="n">
-        <v>133275</v>
+        <v>72493</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2864,10 +2864,10 @@
         <v>0</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>10710</v>
+        <v>5179</v>
       </c>
       <c r="H35" s="7" t="n">
         <v>0</v>
@@ -2876,10 +2876,10 @@
         <v>0</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>10868</v>
+        <v>3327</v>
       </c>
       <c r="L35" s="7" t="n">
         <v>0</v>
@@ -2894,10 +2894,10 @@
         <v>0</v>
       </c>
       <c r="P35" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q35" s="7" t="n">
-        <v>22453</v>
+        <v>8652</v>
       </c>
       <c r="R35" s="7" t="n">
         <v>0</v>
@@ -2906,10 +2906,10 @@
         <v>0</v>
       </c>
       <c r="T35" s="5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="U35" s="5" t="n">
-        <v>56453</v>
+        <v>29580</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>31245</v>
+        <v>15609</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>0</v>
@@ -2937,22 +2937,22 @@
         <v>5515</v>
       </c>
       <c r="H36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>21963</v>
+      </c>
+      <c r="J36" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="7" t="n">
-        <v>66007</v>
-      </c>
-      <c r="J36" s="7" t="n">
-        <v>4</v>
-      </c>
       <c r="K36" s="7" t="n">
-        <v>23307</v>
+        <v>8218</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M36" s="7" t="n">
-        <v>23644</v>
+        <v>11813</v>
       </c>
       <c r="N36" s="7" t="n">
         <v>1</v>
@@ -2961,10 +2961,10 @@
         <v>3871</v>
       </c>
       <c r="P36" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q36" s="7" t="n">
-        <v>8905</v>
+        <v>7781</v>
       </c>
       <c r="R36" s="7" t="n">
         <v>1</v>
@@ -2973,10 +2973,10 @@
         <v>142131</v>
       </c>
       <c r="T36" s="5" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="U36" s="5" t="n">
-        <v>304625</v>
+        <v>216901</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2986,10 +2986,10 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>209569</v>
+        <v>150087</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>0</v>
@@ -3016,22 +3016,22 @@
         <v>0</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M37" s="7" t="n">
-        <v>34095</v>
+        <v>22264</v>
       </c>
       <c r="N37" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>11561</v>
+        <v>7678</v>
       </c>
       <c r="P37" s="7" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="Q37" s="7" t="n">
-        <v>69891</v>
+        <v>45810</v>
       </c>
       <c r="R37" s="7" t="n">
         <v>0</v>
@@ -3040,10 +3040,10 @@
         <v>0</v>
       </c>
       <c r="T37" s="5" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="U37" s="5" t="n">
-        <v>325116</v>
+        <v>225839</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3059,10 +3059,10 @@
         <v>0</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>372</v>
+        <v>183</v>
       </c>
       <c r="F38" s="7" t="n">
         <v>0</v>
@@ -3071,22 +3071,22 @@
         <v>0</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>53588</v>
+        <v>9544</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>32540</v>
+        <v>5287</v>
       </c>
       <c r="L38" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M38" s="7" t="n">
-        <v>22910</v>
+        <v>11079</v>
       </c>
       <c r="N38" s="7" t="n">
         <v>0</v>
@@ -3107,10 +3107,10 @@
         <v>0</v>
       </c>
       <c r="T38" s="5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="U38" s="5" t="n">
-        <v>112606</v>
+        <v>29289</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3144,10 +3144,10 @@
         <v>0</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>7783</v>
+        <v>898</v>
       </c>
       <c r="L39" s="7" t="n">
         <v>0</v>
@@ -3156,16 +3156,16 @@
         <v>0</v>
       </c>
       <c r="N39" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>5581</v>
+        <v>2764</v>
       </c>
       <c r="P39" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q39" s="7" t="n">
-        <v>13840</v>
+        <v>1655</v>
       </c>
       <c r="R39" s="7" t="n">
         <v>0</v>
@@ -3174,10 +3174,10 @@
         <v>0</v>
       </c>
       <c r="T39" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U39" s="5" t="n">
-        <v>27204</v>
+        <v>5317</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3199,10 +3199,10 @@
         <v>4636</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>25635</v>
+        <v>15188</v>
       </c>
       <c r="H40" s="7" t="n">
         <v>0</v>
@@ -3211,10 +3211,10 @@
         <v>0</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>27175</v>
+        <v>3917</v>
       </c>
       <c r="L40" s="7" t="n">
         <v>0</v>
@@ -3235,16 +3235,16 @@
         <v>0</v>
       </c>
       <c r="R40" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S40" s="7" t="n">
-        <v>61040</v>
+        <v>30201</v>
       </c>
       <c r="T40" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="U40" s="5" t="n">
-        <v>133958</v>
+        <v>69414</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3296,10 +3296,10 @@
         <v>0</v>
       </c>
       <c r="P41" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q41" s="7" t="n">
-        <v>20145</v>
+        <v>13716</v>
       </c>
       <c r="R41" s="7" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="T41" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U41" s="5" t="n">
-        <v>42744</v>
+        <v>36315</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3339,16 +3339,16 @@
         <v>9471</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>55035</v>
+        <v>10991</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>49939</v>
+        <v>10503</v>
       </c>
       <c r="L42" s="7" t="n">
         <v>1</v>
@@ -3363,10 +3363,10 @@
         <v>10228</v>
       </c>
       <c r="P42" s="7" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q42" s="7" t="n">
-        <v>42989</v>
+        <v>24413</v>
       </c>
       <c r="R42" s="7" t="n">
         <v>3</v>
@@ -3375,10 +3375,10 @@
         <v>271725</v>
       </c>
       <c r="T42" s="5" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="U42" s="5" t="n">
-        <v>490949</v>
+        <v>388893</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>65854</v>
+        <v>40432</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>2</v>
@@ -3400,10 +3400,10 @@
         <v>6434</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>7205</v>
+        <v>3138</v>
       </c>
       <c r="H43" s="7" t="n">
         <v>0</v>
@@ -3412,28 +3412,28 @@
         <v>0</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>83472</v>
+        <v>35433</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M43" s="7" t="n">
-        <v>23653</v>
+        <v>11822</v>
       </c>
       <c r="N43" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O43" s="7" t="n">
-        <v>17868</v>
+        <v>8062</v>
       </c>
       <c r="P43" s="7" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="Q43" s="7" t="n">
-        <v>68476</v>
+        <v>37371</v>
       </c>
       <c r="R43" s="7" t="n">
         <v>0</v>
@@ -3442,10 +3442,10 @@
         <v>0</v>
       </c>
       <c r="T43" s="5" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="U43" s="5" t="n">
-        <v>272962</v>
+        <v>142692</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3485,10 +3485,10 @@
         <v>0</v>
       </c>
       <c r="L44" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>23448</v>
+        <v>11617</v>
       </c>
       <c r="N44" s="7" t="n">
         <v>1</v>
@@ -3509,10 +3509,10 @@
         <v>0</v>
       </c>
       <c r="T44" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U44" s="5" t="n">
-        <v>27259</v>
+        <v>15428</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3522,40 +3522,40 @@
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>52873</v>
+        <v>34192</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>57425</v>
+        <v>54344</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>20005</v>
+        <v>11228</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I45" s="7" t="n">
-        <v>61881</v>
+        <v>39859</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>127166</v>
+        <v>34161</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M45" s="7" t="n">
-        <v>23178</v>
+        <v>11347</v>
       </c>
       <c r="N45" s="7" t="n">
         <v>4</v>
@@ -3564,10 +3564,10 @@
         <v>14700</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q45" s="7" t="n">
-        <v>8427</v>
+        <v>4157</v>
       </c>
       <c r="R45" s="7" t="n">
         <v>0</v>
@@ -3576,10 +3576,10 @@
         <v>0</v>
       </c>
       <c r="T45" s="5" t="n">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="U45" s="5" t="n">
-        <v>365655</v>
+        <v>203988</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>43161</v>
+        <v>29300</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>0</v>
@@ -3607,22 +3607,22 @@
         <v>4819</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>61877</v>
+        <v>39855</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>111182</v>
+        <v>25469</v>
       </c>
       <c r="L46" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>23077</v>
+        <v>11246</v>
       </c>
       <c r="N46" s="7" t="n">
         <v>3</v>
@@ -3631,10 +3631,10 @@
         <v>11044</v>
       </c>
       <c r="P46" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q46" s="7" t="n">
-        <v>8410</v>
+        <v>4140</v>
       </c>
       <c r="R46" s="7" t="n">
         <v>0</v>
@@ -3643,10 +3643,10 @@
         <v>0</v>
       </c>
       <c r="T46" s="5" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="U46" s="5" t="n">
-        <v>263570</v>
+        <v>125873</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3668,10 +3668,10 @@
         <v>10916</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>25124</v>
+        <v>14677</v>
       </c>
       <c r="H47" s="7" t="n">
         <v>0</v>
@@ -3680,10 +3680,10 @@
         <v>0</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>53858</v>
+        <v>15189</v>
       </c>
       <c r="L47" s="7" t="n">
         <v>0</v>
@@ -3698,22 +3698,22 @@
         <v>0</v>
       </c>
       <c r="P47" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q47" s="7" t="n">
-        <v>21121</v>
+        <v>8936</v>
       </c>
       <c r="R47" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S47" s="7" t="n">
-        <v>46006</v>
+        <v>15167</v>
       </c>
       <c r="T47" s="5" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="U47" s="5" t="n">
-        <v>172792</v>
+        <v>80652</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3735,10 +3735,10 @@
         <v>40644</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>5690</v>
+        <v>5062</v>
       </c>
       <c r="H48" s="7" t="n">
         <v>0</v>
@@ -3747,10 +3747,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>375548</v>
+        <v>315421</v>
       </c>
       <c r="L48" s="7" t="n">
         <v>0</v>
@@ -3777,10 +3777,10 @@
         <v>1018181</v>
       </c>
       <c r="T48" s="5" t="n">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="U48" s="5" t="n">
-        <v>1624483</v>
+        <v>1563728</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3790,40 +3790,40 @@
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>52873</v>
+        <v>34192</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>64098</v>
+        <v>61017</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>20004</v>
+        <v>11227</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I49" s="7" t="n">
-        <v>61877</v>
+        <v>39855</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>124086</v>
+        <v>34073</v>
       </c>
       <c r="L49" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>23178</v>
+        <v>11347</v>
       </c>
       <c r="N49" s="7" t="n">
         <v>4</v>
@@ -3832,10 +3832,10 @@
         <v>14702</v>
       </c>
       <c r="P49" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q49" s="7" t="n">
-        <v>8412</v>
+        <v>4142</v>
       </c>
       <c r="R49" s="7" t="n">
         <v>0</v>
@@ -3844,10 +3844,10 @@
         <v>0</v>
       </c>
       <c r="T49" s="5" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="U49" s="5" t="n">
-        <v>369230</v>
+        <v>210555</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="B50" s="7" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C50" s="7" t="n">
-        <v>211779</v>
+        <v>134814</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>2</v>
@@ -3869,10 +3869,10 @@
         <v>6763</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>25155</v>
+        <v>14708</v>
       </c>
       <c r="H50" s="7" t="n">
         <v>0</v>
@@ -3881,10 +3881,10 @@
         <v>0</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>292594</v>
+        <v>181912</v>
       </c>
       <c r="L50" s="7" t="n">
         <v>0</v>
@@ -3899,22 +3899,22 @@
         <v>10187</v>
       </c>
       <c r="P50" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q50" s="7" t="n">
-        <v>358</v>
+        <v>184</v>
       </c>
       <c r="R50" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S50" s="7" t="n">
-        <v>46598</v>
+        <v>15759</v>
       </c>
       <c r="T50" s="5" t="n">
-        <v>139</v>
+        <v>102</v>
       </c>
       <c r="U50" s="5" t="n">
-        <v>593434</v>
+        <v>364327</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="B51" s="7" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>282573</v>
+        <v>170966</v>
       </c>
       <c r="D51" s="7" t="n">
         <v>5</v>
@@ -3936,10 +3936,10 @@
         <v>16570</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>29869</v>
+        <v>14783</v>
       </c>
       <c r="H51" s="7" t="n">
         <v>0</v>
@@ -3948,40 +3948,40 @@
         <v>0</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>148153</v>
+        <v>72006</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>23652</v>
+        <v>11821</v>
       </c>
       <c r="N51" s="7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O51" s="7" t="n">
-        <v>32797</v>
+        <v>22312</v>
       </c>
       <c r="P51" s="7" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="Q51" s="7" t="n">
-        <v>74205</v>
+        <v>35962</v>
       </c>
       <c r="R51" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S51" s="7" t="n">
-        <v>46573</v>
+        <v>15734</v>
       </c>
       <c r="T51" s="5" t="n">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="U51" s="5" t="n">
-        <v>654392</v>
+        <v>360154</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -4003,28 +4003,28 @@
         <v>3582</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>25115</v>
+        <v>14668</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>53674</v>
+        <v>9630</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>154499</v>
+        <v>58615</v>
       </c>
       <c r="L52" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M52" s="7" t="n">
-        <v>23567</v>
+        <v>11736</v>
       </c>
       <c r="N52" s="7" t="n">
         <v>1</v>
@@ -4039,16 +4039,16 @@
         <v>3656</v>
       </c>
       <c r="R52" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S52" s="7" t="n">
-        <v>629273</v>
+        <v>213421</v>
       </c>
       <c r="T52" s="5" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="U52" s="5" t="n">
-        <v>958770</v>
+        <v>380712</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -4070,28 +4070,28 @@
         <v>3582</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>25115</v>
+        <v>14668</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I53" s="7" t="n">
-        <v>53674</v>
+        <v>9630</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>102103</v>
+        <v>29740</v>
       </c>
       <c r="L53" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53" s="7" t="n">
-        <v>23567</v>
+        <v>11736</v>
       </c>
       <c r="N53" s="7" t="n">
         <v>1</v>
@@ -4106,16 +4106,16 @@
         <v>3655</v>
       </c>
       <c r="R53" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S53" s="7" t="n">
-        <v>629314</v>
+        <v>213462</v>
       </c>
       <c r="T53" s="5" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="U53" s="5" t="n">
-        <v>909635</v>
+        <v>355098</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -4149,28 +4149,28 @@
         <v>0</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>55340</v>
+        <v>9402</v>
       </c>
       <c r="L54" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M54" s="7" t="n">
-        <v>23612</v>
+        <v>11781</v>
       </c>
       <c r="N54" s="7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O54" s="7" t="n">
-        <v>28547</v>
+        <v>18062</v>
       </c>
       <c r="P54" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q54" s="7" t="n">
-        <v>20878</v>
+        <v>10326</v>
       </c>
       <c r="R54" s="7" t="n">
         <v>0</v>
@@ -4179,10 +4179,10 @@
         <v>0</v>
       </c>
       <c r="T54" s="5" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="U54" s="5" t="n">
-        <v>137218</v>
+        <v>58412</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -4204,10 +4204,10 @@
         <v>33281</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>30339</v>
+        <v>14989</v>
       </c>
       <c r="H55" s="7" t="n">
         <v>0</v>
@@ -4216,40 +4216,40 @@
         <v>0</v>
       </c>
       <c r="J55" s="7" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>126492</v>
+        <v>43181</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>23627</v>
+        <v>11796</v>
       </c>
       <c r="N55" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O55" s="7" t="n">
-        <v>17671</v>
+        <v>11748</v>
       </c>
       <c r="P55" s="7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Q55" s="7" t="n">
-        <v>56541</v>
+        <v>28176</v>
       </c>
       <c r="R55" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S55" s="7" t="n">
-        <v>1610762</v>
+        <v>379632</v>
       </c>
       <c r="T55" s="5" t="n">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="U55" s="5" t="n">
-        <v>1952733</v>
+        <v>576823</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -4259,10 +4259,10 @@
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C56" s="7" t="n">
-        <v>439669</v>
+        <v>366373</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>25</v>
@@ -4271,52 +4271,52 @@
         <v>60109</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>252223</v>
+        <v>207281</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I56" s="7" t="n">
-        <v>64245</v>
+        <v>20201</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>185296</v>
+        <v>126942</v>
       </c>
       <c r="L56" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M56" s="7" t="n">
-        <v>35266</v>
+        <v>23435</v>
       </c>
       <c r="N56" s="7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O56" s="7" t="n">
-        <v>35238</v>
+        <v>28538</v>
       </c>
       <c r="P56" s="7" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="Q56" s="7" t="n">
-        <v>154242</v>
+        <v>125877</v>
       </c>
       <c r="R56" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S56" s="7" t="n">
-        <v>506519</v>
+        <v>172893</v>
       </c>
       <c r="T56" s="5" t="n">
-        <v>291</v>
+        <v>248</v>
       </c>
       <c r="U56" s="5" t="n">
-        <v>1732807</v>
+        <v>1131649</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -4338,10 +4338,10 @@
         <v>2669</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>7663</v>
+        <v>2132</v>
       </c>
       <c r="H57" s="7" t="n">
         <v>0</v>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="P57" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q57" s="7" t="n">
-        <v>15379</v>
+        <v>3194</v>
       </c>
       <c r="R57" s="7" t="n">
         <v>0</v>
@@ -4380,10 +4380,10 @@
         <v>0</v>
       </c>
       <c r="T57" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U57" s="5" t="n">
-        <v>25711</v>
+        <v>7995</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -4484,10 +4484,10 @@
         <v>0</v>
       </c>
       <c r="J59" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>38307</v>
+        <v>3135</v>
       </c>
       <c r="L59" s="7" t="n">
         <v>0</v>
@@ -4514,10 +4514,10 @@
         <v>0</v>
       </c>
       <c r="T59" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U59" s="5" t="n">
-        <v>38307</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -4539,10 +4539,10 @@
         <v>689</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>10594</v>
+        <v>5063</v>
       </c>
       <c r="H60" s="7" t="n">
         <v>0</v>
@@ -4569,22 +4569,22 @@
         <v>0</v>
       </c>
       <c r="P60" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q60" s="7" t="n">
+        <v>9898</v>
+      </c>
+      <c r="R60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Q60" s="7" t="n">
-        <v>17277</v>
-      </c>
-      <c r="R60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="U60" s="5" t="n">
-        <v>28560</v>
+        <v>15650</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>56942</v>
+        <v>41306</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>3</v>
@@ -4606,10 +4606,10 @@
         <v>9647</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>25071</v>
+        <v>14624</v>
       </c>
       <c r="H61" s="7" t="n">
         <v>0</v>
@@ -4618,16 +4618,16 @@
         <v>0</v>
       </c>
       <c r="J61" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>74472</v>
+        <v>13445</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M61" s="7" t="n">
-        <v>23618</v>
+        <v>11787</v>
       </c>
       <c r="N61" s="7" t="n">
         <v>3</v>
@@ -4636,22 +4636,22 @@
         <v>6587</v>
       </c>
       <c r="P61" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q61" s="7" t="n">
-        <v>25329</v>
+        <v>12393</v>
       </c>
       <c r="R61" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S61" s="7" t="n">
-        <v>43342</v>
+        <v>12503</v>
       </c>
       <c r="T61" s="5" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="U61" s="5" t="n">
-        <v>265008</v>
+        <v>122292</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -4703,10 +4703,10 @@
         <v>0</v>
       </c>
       <c r="P62" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q62" s="7" t="n">
-        <v>6805</v>
+        <v>376</v>
       </c>
       <c r="R62" s="7" t="n">
         <v>0</v>
@@ -4715,10 +4715,10 @@
         <v>0</v>
       </c>
       <c r="T62" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U62" s="5" t="n">
-        <v>9525</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
@@ -4752,10 +4752,10 @@
         <v>0</v>
       </c>
       <c r="J63" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>26148</v>
+        <v>2890</v>
       </c>
       <c r="L63" s="7" t="n">
         <v>0</v>
@@ -4782,10 +4782,10 @@
         <v>0</v>
       </c>
       <c r="T63" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U63" s="5" t="n">
-        <v>26148</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4819,10 +4819,10 @@
         <v>0</v>
       </c>
       <c r="J64" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K64" s="7" t="n">
-        <v>3530</v>
+        <v>1019</v>
       </c>
       <c r="L64" s="7" t="n">
         <v>0</v>
@@ -4849,10 +4849,10 @@
         <v>0</v>
       </c>
       <c r="T64" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U64" s="5" t="n">
-        <v>3530</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>173272</v>
+        <v>101575</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>5</v>
@@ -4874,10 +4874,10 @@
         <v>16477</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>25015</v>
+        <v>14568</v>
       </c>
       <c r="H65" s="7" t="n">
         <v>0</v>
@@ -4886,40 +4886,40 @@
         <v>0</v>
       </c>
       <c r="J65" s="7" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>123639</v>
+        <v>59379</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M65" s="7" t="n">
-        <v>23409</v>
+        <v>11578</v>
       </c>
       <c r="N65" s="7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="O65" s="7" t="n">
-        <v>43886</v>
+        <v>33401</v>
       </c>
       <c r="P65" s="7" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="Q65" s="7" t="n">
-        <v>68027</v>
+        <v>29610</v>
       </c>
       <c r="R65" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S65" s="7" t="n">
-        <v>46331</v>
+        <v>15492</v>
       </c>
       <c r="T65" s="5" t="n">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="U65" s="5" t="n">
-        <v>520056</v>
+        <v>282080</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
@@ -4941,10 +4941,10 @@
         <v>0</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>10910</v>
+        <v>5379</v>
       </c>
       <c r="H66" s="7" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="T66" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U66" s="5" t="n">
-        <v>16032</v>
+        <v>10501</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
@@ -5008,10 +5008,10 @@
         <v>0</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>10923</v>
+        <v>5392</v>
       </c>
       <c r="H67" s="7" t="n">
         <v>0</v>
@@ -5050,10 +5050,10 @@
         <v>0</v>
       </c>
       <c r="T67" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U67" s="5" t="n">
-        <v>15965</v>
+        <v>10434</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
@@ -5069,10 +5069,10 @@
         <v>5706</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>3968</v>
+        <v>3779</v>
       </c>
       <c r="F68" s="7" t="n">
         <v>0</v>
@@ -5081,10 +5081,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I68" s="7" t="n">
-        <v>53590</v>
+        <v>9546</v>
       </c>
       <c r="J68" s="7" t="n">
         <v>0</v>
@@ -5093,10 +5093,10 @@
         <v>0</v>
       </c>
       <c r="L68" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M68" s="7" t="n">
-        <v>22908</v>
+        <v>11077</v>
       </c>
       <c r="N68" s="7" t="n">
         <v>0</v>
@@ -5117,10 +5117,10 @@
         <v>0</v>
       </c>
       <c r="T68" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U68" s="5" t="n">
-        <v>88510</v>
+        <v>32446</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
@@ -5154,16 +5154,16 @@
         <v>0</v>
       </c>
       <c r="J69" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>12638</v>
+        <v>91</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M69" s="7" t="n">
-        <v>22908</v>
+        <v>11077</v>
       </c>
       <c r="N69" s="7" t="n">
         <v>1</v>
@@ -5184,10 +5184,10 @@
         <v>0</v>
       </c>
       <c r="T69" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U69" s="5" t="n">
-        <v>63270</v>
+        <v>38892</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -5215,22 +5215,22 @@
         <v>0</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I70" s="7" t="n">
-        <v>53674</v>
+        <v>9630</v>
       </c>
       <c r="J70" s="7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>54003</v>
+        <v>11134</v>
       </c>
       <c r="L70" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M70" s="7" t="n">
-        <v>23567</v>
+        <v>11736</v>
       </c>
       <c r="N70" s="7" t="n">
         <v>1</v>
@@ -5251,10 +5251,10 @@
         <v>0</v>
       </c>
       <c r="T70" s="5" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="U70" s="5" t="n">
-        <v>156610</v>
+        <v>57866</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
@@ -5282,22 +5282,22 @@
         <v>0</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>53674</v>
+        <v>9630</v>
       </c>
       <c r="J71" s="7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>39615</v>
+        <v>9851</v>
       </c>
       <c r="L71" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M71" s="7" t="n">
-        <v>23567</v>
+        <v>11736</v>
       </c>
       <c r="N71" s="7" t="n">
         <v>1</v>
@@ -5318,10 +5318,10 @@
         <v>0</v>
       </c>
       <c r="T71" s="5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="U71" s="5" t="n">
-        <v>131397</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
@@ -5349,22 +5349,22 @@
         <v>0</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I72" s="7" t="n">
-        <v>53674</v>
+        <v>9630</v>
       </c>
       <c r="J72" s="7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K72" s="7" t="n">
-        <v>39615</v>
+        <v>9851</v>
       </c>
       <c r="L72" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M72" s="7" t="n">
-        <v>23567</v>
+        <v>11736</v>
       </c>
       <c r="N72" s="7" t="n">
         <v>1</v>
@@ -5385,10 +5385,10 @@
         <v>0</v>
       </c>
       <c r="T72" s="5" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="U72" s="5" t="n">
-        <v>151227</v>
+        <v>65588</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
@@ -5422,10 +5422,10 @@
         <v>0</v>
       </c>
       <c r="J73" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>50002</v>
+        <v>14288</v>
       </c>
       <c r="L73" s="7" t="n">
         <v>0</v>
@@ -5452,10 +5452,10 @@
         <v>0</v>
       </c>
       <c r="T73" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U73" s="5" t="n">
-        <v>50002</v>
+        <v>14288</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
@@ -5507,10 +5507,10 @@
         <v>0</v>
       </c>
       <c r="P74" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q74" s="7" t="n">
-        <v>7393</v>
+        <v>964</v>
       </c>
       <c r="R74" s="7" t="n">
         <v>0</v>
@@ -5519,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="T74" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U74" s="5" t="n">
-        <v>7393</v>
+        <v>964</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="P75" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q75" s="7" t="n">
-        <v>18383</v>
+        <v>11954</v>
       </c>
       <c r="R75" s="7" t="n">
         <v>0</v>
@@ -5586,10 +5586,10 @@
         <v>0</v>
       </c>
       <c r="T75" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U75" s="5" t="n">
-        <v>43170</v>
+        <v>36741</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
@@ -5605,10 +5605,10 @@
         <v>5706</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>384</v>
+        <v>195</v>
       </c>
       <c r="F76" s="7" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
         <v>0</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I76" s="7" t="n">
-        <v>53588</v>
+        <v>9544</v>
       </c>
       <c r="J76" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>32540</v>
+        <v>5287</v>
       </c>
       <c r="L76" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M76" s="7" t="n">
-        <v>22913</v>
+        <v>11082</v>
       </c>
       <c r="N76" s="7" t="n">
         <v>0</v>
@@ -5653,10 +5653,10 @@
         <v>0</v>
       </c>
       <c r="T76" s="5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="U76" s="5" t="n">
-        <v>118362</v>
+        <v>35045</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
@@ -5696,10 +5696,10 @@
         <v>0</v>
       </c>
       <c r="L77" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M77" s="7" t="n">
-        <v>22908</v>
+        <v>11077</v>
       </c>
       <c r="N77" s="7" t="n">
         <v>0</v>
@@ -5720,10 +5720,10 @@
         <v>0</v>
       </c>
       <c r="T77" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U77" s="5" t="n">
-        <v>43933</v>
+        <v>32102</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>324</v>
+        <v>135</v>
       </c>
       <c r="F78" s="7" t="n">
         <v>0</v>
@@ -5751,10 +5751,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I78" s="7" t="n">
-        <v>53590</v>
+        <v>9546</v>
       </c>
       <c r="J78" s="7" t="n">
         <v>0</v>
@@ -5763,10 +5763,10 @@
         <v>0</v>
       </c>
       <c r="L78" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M78" s="7" t="n">
-        <v>22909</v>
+        <v>11078</v>
       </c>
       <c r="N78" s="7" t="n">
         <v>0</v>
@@ -5787,10 +5787,10 @@
         <v>0</v>
       </c>
       <c r="T78" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U78" s="5" t="n">
-        <v>79161</v>
+        <v>23097</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="B79" s="7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>47302</v>
+        <v>30411</v>
       </c>
       <c r="D79" s="7" t="n">
         <v>0</v>
@@ -5824,10 +5824,10 @@
         <v>0</v>
       </c>
       <c r="J79" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>19114</v>
+        <v>4025</v>
       </c>
       <c r="L79" s="7" t="n">
         <v>0</v>
@@ -5854,10 +5854,10 @@
         <v>1802</v>
       </c>
       <c r="T79" s="5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="U79" s="5" t="n">
-        <v>78308</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
@@ -5879,28 +5879,28 @@
         <v>3581</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>25046</v>
+        <v>14599</v>
       </c>
       <c r="H80" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="7" t="n">
+        <v>9610</v>
+      </c>
+      <c r="J80" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I80" s="7" t="n">
-        <v>53654</v>
-      </c>
-      <c r="J80" s="7" t="n">
-        <v>8</v>
-      </c>
       <c r="K80" s="7" t="n">
-        <v>35931</v>
+        <v>6167</v>
       </c>
       <c r="L80" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M80" s="7" t="n">
-        <v>23560</v>
+        <v>11729</v>
       </c>
       <c r="N80" s="7" t="n">
         <v>1</v>
@@ -5915,16 +5915,16 @@
         <v>3644</v>
       </c>
       <c r="R80" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S80" s="7" t="n">
-        <v>623065</v>
+        <v>207213</v>
       </c>
       <c r="T80" s="5" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="U80" s="5" t="n">
-        <v>809672</v>
+        <v>297734</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>32540</v>
+        <v>5287</v>
       </c>
       <c r="L81" s="7" t="n">
         <v>0</v>
@@ -5988,10 +5988,10 @@
         <v>0</v>
       </c>
       <c r="T81" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U81" s="5" t="n">
-        <v>41623</v>
+        <v>14370</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
@@ -6013,10 +6013,10 @@
         <v>6310</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>25155</v>
+        <v>14708</v>
       </c>
       <c r="H82" s="7" t="n">
         <v>0</v>
@@ -6043,10 +6043,10 @@
         <v>3839</v>
       </c>
       <c r="P82" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q82" s="7" t="n">
-        <v>18964</v>
+        <v>6980</v>
       </c>
       <c r="R82" s="7" t="n">
         <v>0</v>
@@ -6055,10 +6055,10 @@
         <v>0</v>
       </c>
       <c r="T82" s="5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="U82" s="5" t="n">
-        <v>91652</v>
+        <v>69221</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
@@ -6098,10 +6098,10 @@
         <v>0</v>
       </c>
       <c r="L83" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>23526</v>
+        <v>11695</v>
       </c>
       <c r="N83" s="7" t="n">
         <v>24</v>
@@ -6110,22 +6110,22 @@
         <v>78673</v>
       </c>
       <c r="P83" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q83" s="7" t="n">
-        <v>22435</v>
+        <v>11103</v>
       </c>
       <c r="R83" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S83" s="7" t="n">
-        <v>500439</v>
+        <v>166813</v>
       </c>
       <c r="T83" s="5" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="U83" s="5" t="n">
-        <v>684088</v>
+        <v>327299</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
@@ -6159,10 +6159,10 @@
         <v>0</v>
       </c>
       <c r="J84" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K84" s="7" t="n">
-        <v>66296</v>
+        <v>48355</v>
       </c>
       <c r="L84" s="7" t="n">
         <v>0</v>
@@ -6189,10 +6189,10 @@
         <v>0</v>
       </c>
       <c r="T84" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U84" s="5" t="n">
-        <v>66296</v>
+        <v>48355</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
@@ -6208,10 +6208,10 @@
         <v>0</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>326</v>
+        <v>163</v>
       </c>
       <c r="F85" s="7" t="n">
         <v>0</v>
@@ -6238,28 +6238,28 @@
         <v>0</v>
       </c>
       <c r="N85" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O85" s="7" t="n">
+        <v>5482</v>
+      </c>
+      <c r="P85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="O85" s="7" t="n">
-        <v>8299</v>
-      </c>
-      <c r="P85" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R85" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" s="5" t="n">
-        <v>5</v>
-      </c>
       <c r="U85" s="5" t="n">
-        <v>8625</v>
+        <v>5645</v>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="B86" s="7" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C86" s="7" t="n">
-        <v>274284</v>
+        <v>220664</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>0</v>
@@ -6293,40 +6293,40 @@
         <v>0</v>
       </c>
       <c r="J86" s="7" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>202581</v>
+        <v>84035</v>
       </c>
       <c r="L86" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M86" s="7" t="n">
-        <v>23558</v>
+        <v>11727</v>
       </c>
       <c r="N86" s="7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O86" s="7" t="n">
-        <v>65524</v>
+        <v>58824</v>
       </c>
       <c r="P86" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q86" s="7" t="n">
-        <v>22514</v>
+        <v>11182</v>
       </c>
       <c r="R86" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S86" s="7" t="n">
-        <v>500439</v>
+        <v>166813</v>
       </c>
       <c r="T86" s="5" t="n">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="U86" s="5" t="n">
-        <v>1132330</v>
+        <v>596675</v>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
@@ -6360,40 +6360,40 @@
         <v>0</v>
       </c>
       <c r="J87" s="7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>90128</v>
+        <v>33259</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>35283</v>
+        <v>23452</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>46378</v>
+        <v>39678</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q87" s="7" t="n">
-        <v>22514</v>
+        <v>11182</v>
       </c>
       <c r="R87" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S87" s="7" t="n">
-        <v>500439</v>
+        <v>166813</v>
       </c>
       <c r="T87" s="5" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="U87" s="5" t="n">
-        <v>755941</v>
+        <v>335583</v>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
@@ -6421,22 +6421,22 @@
         <v>0</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I88" s="7" t="n">
-        <v>53674</v>
+        <v>9630</v>
       </c>
       <c r="J88" s="7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K88" s="7" t="n">
-        <v>59154</v>
+        <v>14301</v>
       </c>
       <c r="L88" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M88" s="7" t="n">
-        <v>23567</v>
+        <v>11736</v>
       </c>
       <c r="N88" s="7" t="n">
         <v>1</v>
@@ -6457,10 +6457,10 @@
         <v>0</v>
       </c>
       <c r="T88" s="5" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="U88" s="5" t="n">
-        <v>161739</v>
+        <v>61011</v>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
@@ -6494,16 +6494,16 @@
         <v>0</v>
       </c>
       <c r="J89" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>32543</v>
+        <v>5290</v>
       </c>
       <c r="L89" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M89" s="7" t="n">
-        <v>23566</v>
+        <v>11735</v>
       </c>
       <c r="N89" s="7" t="n">
         <v>0</v>
@@ -6524,10 +6524,10 @@
         <v>0</v>
       </c>
       <c r="T89" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="U89" s="5" t="n">
-        <v>68125</v>
+        <v>29041</v>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
@@ -6549,10 +6549,10 @@
         <v>3529</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>13853</v>
+        <v>12652</v>
       </c>
       <c r="H90" s="7" t="n">
         <v>0</v>
@@ -6561,16 +6561,16 @@
         <v>0</v>
       </c>
       <c r="J90" s="7" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K90" s="7" t="n">
-        <v>129670</v>
+        <v>46135</v>
       </c>
       <c r="L90" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M90" s="7" t="n">
-        <v>23080</v>
+        <v>11249</v>
       </c>
       <c r="N90" s="7" t="n">
         <v>2</v>
@@ -6579,10 +6579,10 @@
         <v>6955</v>
       </c>
       <c r="P90" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q90" s="7" t="n">
-        <v>10941</v>
+        <v>5436</v>
       </c>
       <c r="R90" s="7" t="n">
         <v>6</v>
@@ -6591,10 +6591,10 @@
         <v>626832</v>
       </c>
       <c r="T90" s="5" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="U90" s="5" t="n">
-        <v>820785</v>
+        <v>718713</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
@@ -6628,10 +6628,10 @@
         <v>0</v>
       </c>
       <c r="J91" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K91" s="7" t="n">
-        <v>17171</v>
+        <v>4624</v>
       </c>
       <c r="L91" s="7" t="n">
         <v>0</v>
@@ -6658,10 +6658,10 @@
         <v>5721</v>
       </c>
       <c r="T91" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U91" s="5" t="n">
-        <v>85844</v>
+        <v>73297</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
@@ -6683,10 +6683,10 @@
         <v>16962</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>12180</v>
+        <v>7868</v>
       </c>
       <c r="H92" s="7" t="n">
         <v>0</v>
@@ -6695,10 +6695,10 @@
         <v>0</v>
       </c>
       <c r="J92" s="7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K92" s="7" t="n">
-        <v>82860</v>
+        <v>21523</v>
       </c>
       <c r="L92" s="7" t="n">
         <v>0</v>
@@ -6725,10 +6725,10 @@
         <v>338044</v>
       </c>
       <c r="T92" s="5" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="U92" s="5" t="n">
-        <v>482912</v>
+        <v>417263</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
@@ -6750,16 +6750,16 @@
         <v>0</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>10480</v>
+        <v>6413</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I93" s="7" t="n">
-        <v>64224</v>
+        <v>20180</v>
       </c>
       <c r="J93" s="7" t="n">
         <v>1</v>
@@ -6768,10 +6768,10 @@
         <v>715</v>
       </c>
       <c r="L93" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M93" s="7" t="n">
-        <v>22347</v>
+        <v>10516</v>
       </c>
       <c r="N93" s="7" t="n">
         <v>0</v>
@@ -6792,10 +6792,10 @@
         <v>0</v>
       </c>
       <c r="T93" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U93" s="5" t="n">
-        <v>97766</v>
+        <v>37824</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
@@ -6847,10 +6847,10 @@
         <v>0</v>
       </c>
       <c r="P94" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q94" s="7" t="n">
-        <v>6524</v>
+        <v>3719</v>
       </c>
       <c r="R94" s="7" t="n">
         <v>0</v>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="T94" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U94" s="5" t="n">
-        <v>6524</v>
+        <v>3719</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
@@ -6914,10 +6914,10 @@
         <v>0</v>
       </c>
       <c r="P95" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q95" s="7" t="n">
-        <v>9242</v>
+        <v>2813</v>
       </c>
       <c r="R95" s="7" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="T95" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U95" s="5" t="n">
-        <v>9242</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="B96" s="7" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C96" s="7" t="n">
-        <v>245458</v>
+        <v>133851</v>
       </c>
       <c r="D96" s="7" t="n">
         <v>2</v>
@@ -6951,10 +6951,10 @@
         <v>6897</v>
       </c>
       <c r="F96" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G96" s="7" t="n">
-        <v>11010</v>
+        <v>5479</v>
       </c>
       <c r="H96" s="7" t="n">
         <v>0</v>
@@ -6963,40 +6963,40 @@
         <v>0</v>
       </c>
       <c r="J96" s="7" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="K96" s="7" t="n">
-        <v>218271</v>
+        <v>90302</v>
       </c>
       <c r="L96" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M96" s="7" t="n">
-        <v>23653</v>
+        <v>11822</v>
       </c>
       <c r="N96" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O96" s="7" t="n">
-        <v>31460</v>
+        <v>20975</v>
       </c>
       <c r="P96" s="7" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Q96" s="7" t="n">
-        <v>68149</v>
+        <v>29732</v>
       </c>
       <c r="R96" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S96" s="7" t="n">
-        <v>46610</v>
+        <v>15771</v>
       </c>
       <c r="T96" s="5" t="n">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="U96" s="5" t="n">
-        <v>651508</v>
+        <v>314829</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="B97" s="7" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C97" s="7" t="n">
-        <v>167017</v>
+        <v>113210</v>
       </c>
       <c r="D97" s="7" t="n">
         <v>5</v>
@@ -7018,10 +7018,10 @@
         <v>16569</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>29264</v>
+        <v>14806</v>
       </c>
       <c r="H97" s="7" t="n">
         <v>0</v>
@@ -7030,40 +7030,40 @@
         <v>0</v>
       </c>
       <c r="J97" s="7" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K97" s="7" t="n">
-        <v>168009</v>
+        <v>64668</v>
       </c>
       <c r="L97" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M97" s="7" t="n">
-        <v>23653</v>
+        <v>11822</v>
       </c>
       <c r="N97" s="7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O97" s="7" t="n">
-        <v>32777</v>
+        <v>22292</v>
       </c>
       <c r="P97" s="7" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="Q97" s="7" t="n">
-        <v>67803</v>
+        <v>29560</v>
       </c>
       <c r="R97" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S97" s="7" t="n">
-        <v>46610</v>
+        <v>15771</v>
       </c>
       <c r="T97" s="5" t="n">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="U97" s="5" t="n">
-        <v>551702</v>
+        <v>288698</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="B98" s="7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C98" s="7" t="n">
-        <v>59241</v>
+        <v>42350</v>
       </c>
       <c r="D98" s="7" t="n">
         <v>2</v>
@@ -7097,10 +7097,10 @@
         <v>0</v>
       </c>
       <c r="J98" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K98" s="7" t="n">
-        <v>14391</v>
+        <v>6850</v>
       </c>
       <c r="L98" s="7" t="n">
         <v>0</v>
@@ -7127,10 +7127,10 @@
         <v>4604</v>
       </c>
       <c r="T98" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="U98" s="5" t="n">
-        <v>78313</v>
+        <v>53881</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
@@ -7152,10 +7152,10 @@
         <v>74514</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>771</v>
+        <v>143</v>
       </c>
       <c r="H99" s="7" t="n">
         <v>0</v>
@@ -7164,10 +7164,10 @@
         <v>0</v>
       </c>
       <c r="J99" s="7" t="n">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="K99" s="7" t="n">
-        <v>638568</v>
+        <v>578441</v>
       </c>
       <c r="L99" s="7" t="n">
         <v>0</v>
@@ -7176,10 +7176,10 @@
         <v>0</v>
       </c>
       <c r="N99" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O99" s="7" t="n">
-        <v>7594</v>
+        <v>3711</v>
       </c>
       <c r="P99" s="7" t="n">
         <v>7</v>
@@ -7194,10 +7194,10 @@
         <v>680137</v>
       </c>
       <c r="T99" s="5" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="U99" s="5" t="n">
-        <v>1753833</v>
+        <v>1689195</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
@@ -7219,52 +7219,52 @@
         <v>30185</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>43939</v>
+        <v>20915</v>
       </c>
       <c r="H100" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I100" s="7" t="n">
-        <v>53850</v>
+        <v>9806</v>
       </c>
       <c r="J100" s="7" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="K100" s="7" t="n">
-        <v>175209</v>
+        <v>70365</v>
       </c>
       <c r="L100" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M100" s="7" t="n">
-        <v>23633</v>
+        <v>11802</v>
       </c>
       <c r="N100" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O100" s="7" t="n">
-        <v>25409</v>
+        <v>15603</v>
       </c>
       <c r="P100" s="7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Q100" s="7" t="n">
-        <v>56543</v>
+        <v>28178</v>
       </c>
       <c r="R100" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S100" s="7" t="n">
-        <v>1619039</v>
+        <v>387909</v>
       </c>
       <c r="T100" s="5" t="n">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="U100" s="5" t="n">
-        <v>2081826</v>
+        <v>628782</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
@@ -7274,16 +7274,16 @@
         </is>
       </c>
       <c r="B101" s="7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C101" s="7" t="n">
-        <v>106654</v>
+        <v>52847</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>388</v>
+        <v>199</v>
       </c>
       <c r="F101" s="7" t="n">
         <v>0</v>
@@ -7304,10 +7304,10 @@
         <v>0</v>
       </c>
       <c r="L101" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M101" s="7" t="n">
-        <v>23626</v>
+        <v>11795</v>
       </c>
       <c r="N101" s="7" t="n">
         <v>8</v>
@@ -7316,22 +7316,22 @@
         <v>23478</v>
       </c>
       <c r="P101" s="7" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Q101" s="7" t="n">
-        <v>89497</v>
+        <v>59516</v>
       </c>
       <c r="R101" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S101" s="7" t="n">
-        <v>1610605</v>
+        <v>379475</v>
       </c>
       <c r="T101" s="5" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="U101" s="5" t="n">
-        <v>1854248</v>
+        <v>527310</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
@@ -7353,28 +7353,28 @@
         <v>3583</v>
       </c>
       <c r="F102" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>10978</v>
+        <v>5447</v>
       </c>
       <c r="H102" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I102" s="7" t="n">
-        <v>53674</v>
+        <v>9630</v>
       </c>
       <c r="J102" s="7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K102" s="7" t="n">
-        <v>60160</v>
+        <v>15307</v>
       </c>
       <c r="L102" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M102" s="7" t="n">
-        <v>22911</v>
+        <v>11080</v>
       </c>
       <c r="N102" s="7" t="n">
         <v>1</v>
@@ -7389,16 +7389,16 @@
         <v>3656</v>
       </c>
       <c r="R102" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S102" s="7" t="n">
-        <v>623680</v>
+        <v>207828</v>
       </c>
       <c r="T102" s="5" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="U102" s="5" t="n">
-        <v>825095</v>
+        <v>302984</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
@@ -7432,10 +7432,10 @@
         <v>0</v>
       </c>
       <c r="J103" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K103" s="7" t="n">
-        <v>12072</v>
+        <v>3903</v>
       </c>
       <c r="L103" s="7" t="n">
         <v>0</v>
@@ -7450,10 +7450,10 @@
         <v>0</v>
       </c>
       <c r="P103" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q103" s="7" t="n">
-        <v>7391</v>
+        <v>962</v>
       </c>
       <c r="R103" s="7" t="n">
         <v>0</v>
@@ -7462,10 +7462,10 @@
         <v>0</v>
       </c>
       <c r="T103" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="U103" s="5" t="n">
-        <v>41192</v>
+        <v>26594</v>
       </c>
     </row>
     <row r="104" ht="18" customHeight="1">
@@ -7475,64 +7475,64 @@
         </is>
       </c>
       <c r="B104" s="9" t="n">
-        <v>1167</v>
+        <v>977</v>
       </c>
       <c r="C104" s="9" t="n">
-        <v>11476318</v>
+        <v>9934033</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>551</v>
+        <v>476</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>1001601</v>
+        <v>962367</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>1341</v>
+        <v>757</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>4128699</v>
+        <v>1995420</v>
       </c>
       <c r="H104" s="9" t="n">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>2062015</v>
+        <v>860147</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>3058</v>
+        <v>2342</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>9163012</v>
+        <v>5290930</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>163</v>
+        <v>86</v>
       </c>
       <c r="M104" s="9" t="n">
-        <v>1749972</v>
+        <v>927668</v>
       </c>
       <c r="N104" s="9" t="n">
-        <v>476</v>
+        <v>359</v>
       </c>
       <c r="O104" s="9" t="n">
-        <v>1639132</v>
+        <v>1255094</v>
       </c>
       <c r="P104" s="9" t="n">
-        <v>1183</v>
+        <v>695</v>
       </c>
       <c r="Q104" s="9" t="n">
-        <v>3873029</v>
+        <v>2257837</v>
       </c>
       <c r="R104" s="9" t="n">
-        <v>353</v>
+        <v>227</v>
       </c>
       <c r="S104" s="9" t="n">
-        <v>33610590</v>
+        <v>19133425</v>
       </c>
       <c r="T104" s="9" t="n">
-        <v>8400</v>
+        <v>5970</v>
       </c>
       <c r="U104" s="9" t="n">
-        <v>68704368</v>
+        <v>42616921</v>
       </c>
     </row>
   </sheetData>
